--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Barça.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Barça.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>224.36</v>
+        <v>363.88</v>
       </c>
       <c r="C2" t="n">
-        <v>226.54</v>
+        <v>366.68</v>
       </c>
       <c r="D2" t="n">
-        <v>122.7156352079103</v>
+        <v>129.5407439729464</v>
       </c>
       <c r="E2" t="n">
-        <v>103.293016685795</v>
+        <v>106.3597687356823</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6242937853107344</v>
+        <v>0.6306451612903226</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1479289940828402</v>
+        <v>0.1320680884367051</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2289156626506024</v>
+        <v>0.3125</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3220338983050847</v>
+        <v>0.2709677419354839</v>
       </c>
       <c r="J2" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="L2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="M2" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="O2" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2645161290322581</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1807909604519774</v>
+        <v>0.2</v>
       </c>
       <c r="T2" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="U2" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1694915254237288</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="W2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.04519774011299435</v>
+        <v>0.04516129032258064</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AA2" t="n">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2711864406779661</v>
+        <v>0.2967741935483871</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.6949152542372882</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.40625</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.4833333333333333</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.625</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.5</v>
+        <v>0.4565217391304348</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.389830508474576</v>
+        <v>1.414634146341463</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.553571428571429</v>
+        <v>1.443396226415094</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.78125</v>
+        <v>0.7924528301886793</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.368421052631579</v>
+        <v>1.177777777777778</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.444444444444444</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.138888888888889</v>
+        <v>1.37037037037037</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.916666666666667</v>
+        <v>5.74074074074074</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.055555555555555</v>
+        <v>7.111111111111111</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.78666666666668</v>
+        <v>72.776</v>
       </c>
       <c r="C3" t="n">
-        <v>75.51333333333334</v>
+        <v>73.336</v>
       </c>
       <c r="D3" t="n">
-        <v>122.7156352079103</v>
+        <v>129.5407439729464</v>
       </c>
       <c r="E3" t="n">
-        <v>103.293016685795</v>
+        <v>106.3597687356823</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6242937853107344</v>
+        <v>0.6306451612903226</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1479289940828402</v>
+        <v>0.1320680884367052</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2289156626506024</v>
+        <v>0.3125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3220338983050847</v>
+        <v>0.2709677419354839</v>
       </c>
       <c r="J3" t="n">
-        <v>8.333333333333334</v>
+        <v>8.4</v>
       </c>
       <c r="K3" t="n">
-        <v>8.666666666666666</v>
+        <v>10.6</v>
       </c>
       <c r="L3" t="n">
-        <v>4.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>13.66666666666667</v>
+        <v>11.6</v>
       </c>
       <c r="O3" t="n">
-        <v>19.66666666666667</v>
+        <v>16.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.264516129032258</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.333333333333333</v>
+        <v>6.4</v>
       </c>
       <c r="R3" t="n">
-        <v>10.66666666666667</v>
+        <v>12.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1807909604519774</v>
+        <v>0.2</v>
       </c>
       <c r="T3" t="n">
-        <v>4.333333333333333</v>
+        <v>5.8</v>
       </c>
       <c r="U3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1694915254237288</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="W3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.04516129032258064</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.2967741935483871</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.7073170731707318</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5161290322580645</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.4833333333333333</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.4565217391304348</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.414634146341464</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.443396226415094</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.7924528301886793</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.177777777777778</v>
+      </c>
+      <c r="AM3" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="X3" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.04519774011299435</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.2711864406779661</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.6949152542372881</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.40625</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.4333333333333333</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.6250000000000001</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.389830508474576</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.8666666666666666</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.553571428571428</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.7812500000000001</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.368421052631579</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.444444444444444</v>
-      </c>
       <c r="AN3" t="n">
-        <v>1.138888888888889</v>
+        <v>1.37037037037037</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.916666666666667</v>
+        <v>5.74074074074074</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.055555555555556</v>
+        <v>7.111111111111111</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>228.72</v>
+        <v>369.48</v>
       </c>
       <c r="C4" t="n">
-        <v>226.54</v>
+        <v>366.68</v>
       </c>
       <c r="D4" t="n">
-        <v>103.293016685795</v>
+        <v>106.3597687356823</v>
       </c>
       <c r="E4" t="n">
-        <v>122.7156352079103</v>
+        <v>129.5407439729464</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4895287958115183</v>
+        <v>0.4968652037617555</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1276324186343331</v>
+        <v>0.1284910783553142</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1929824561403509</v>
+        <v>0.2336956521739131</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2460732984293194</v>
+        <v>0.2288401253918495</v>
       </c>
       <c r="J4" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="K4" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="M4" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="N4" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="O4" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2617801047120419</v>
+        <v>0.2382445141065831</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="R4" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1308900523560209</v>
+        <v>0.1316614420062696</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="U4" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1204188481675393</v>
+        <v>0.1880877742946709</v>
       </c>
       <c r="W4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="X4" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07853403141361257</v>
+        <v>0.08150470219435736</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AA4" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4083769633507853</v>
+        <v>0.3605015673981191</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.62</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.2833333333333333</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3205128205128205</v>
+        <v>0.2956521739130435</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.24</v>
+        <v>1.315789473684211</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.9574468085106383</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.194444444444444</v>
+        <v>0.9814814814814815</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.136363636363636</v>
+        <v>1.046511627906977</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.714285714285714</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.15625</v>
+        <v>1.320754716981132</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.96875</v>
+        <v>6.018867924528302</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.125</v>
+        <v>7.339622641509434</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76.23999999999999</v>
+        <v>73.896</v>
       </c>
       <c r="C5" t="n">
-        <v>75.51333333333334</v>
+        <v>73.336</v>
       </c>
       <c r="D5" t="n">
-        <v>103.293016685795</v>
+        <v>106.3597687356823</v>
       </c>
       <c r="E5" t="n">
-        <v>122.7156352079103</v>
+        <v>129.5407439729464</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4895287958115184</v>
+        <v>0.4968652037617555</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1276324186343331</v>
+        <v>0.1284910783553142</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1929824561403509</v>
+        <v>0.2336956521739131</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2460732984293194</v>
+        <v>0.2288401253918495</v>
       </c>
       <c r="J5" t="n">
-        <v>14.33333333333333</v>
+        <v>10.6</v>
       </c>
       <c r="K5" t="n">
-        <v>8.333333333333334</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
         <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>9.666666666666666</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>10.33333333333333</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>16.66666666666667</v>
+        <v>15.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2617801047120419</v>
+        <v>0.2382445141065831</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="R5" t="n">
-        <v>8.333333333333334</v>
+        <v>8.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0.130890052356021</v>
+        <v>0.1316614420062696</v>
       </c>
       <c r="T5" t="n">
-        <v>1.333333333333333</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>7.666666666666667</v>
+        <v>12</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1204188481675393</v>
+        <v>0.1880877742946709</v>
       </c>
       <c r="W5" t="n">
-        <v>1.333333333333333</v>
+        <v>2.2</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.07853403141361257</v>
+        <v>0.08150470219435738</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.333333333333334</v>
+        <v>6.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4083769633507854</v>
+        <v>0.3605015673981191</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.62</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.2833333333333333</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3205128205128205</v>
+        <v>0.2956521739130435</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.24</v>
+        <v>1.315789473684211</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9354838709677421</v>
+        <v>0.9574468085106383</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.194444444444444</v>
+        <v>0.9814814814814814</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.136363636363636</v>
+        <v>1.046511627906977</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.714285714285714</v>
+        <v>1.538461538461538</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.15625</v>
+        <v>1.320754716981132</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.96875</v>
+        <v>6.018867924528302</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.125</v>
+        <v>7.339622641509434</v>
       </c>
     </row>
     <row r="7">
@@ -1419,156 +1419,156 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>55</v>
+      </c>
+      <c r="D8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" t="n">
+        <v>32</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>17</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" t="n">
-        <v>36</v>
-      </c>
-      <c r="D8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>12</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>37</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
         <v>4</v>
       </c>
-      <c r="G8" t="n">
-        <v>9</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="W8" t="n">
+        <v>3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
         <v>6</v>
       </c>
-      <c r="I8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="AD8" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
         <v>3</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>25</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" t="n">
-        <v>2</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="n">
+      <c r="AJ8" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK8" t="n">
         <v>5</v>
       </c>
-      <c r="AD8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>4</v>
-      </c>
       <c r="AL8" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.571</v>
+        <v>0.357</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>71:09</t>
+          <t>115:27</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>35.08</v>
+        <v>58.84</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.517</v>
+        <v>0.469</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.511</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.026</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.207</v>
+        <v>0.184</v>
       </c>
       <c r="AU8" t="n">
         <v>2</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.243</v>
+        <v>0.249</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.041</v>
+        <v>0.036</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.059</v>
+        <v>0.075</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="9">
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -1590,10 +1590,10 @@
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1614,25 +1614,25 @@
         <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="U9" t="n">
         <v>2</v>
@@ -1683,51 +1683,51 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>48:17</t>
+          <t>76:04</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.65</v>
+        <v>0.731</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.65</v>
+        <v>0.731</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.929</v>
+        <v>1.056</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.286</v>
+        <v>0.278</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.143</v>
+        <v>0.116</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.196</v>
+        <v>0.157</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="10">
@@ -1737,43 +1737,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1785,16 +1785,16 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
+        <v>7</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
+        <v>29</v>
+      </c>
+      <c r="U10" t="n">
         <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>19</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1806,22 +1806,22 @@
         <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1836,57 +1836,57 @@
         <v>2</v>
       </c>
       <c r="AI10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="n">
         <v>2</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1</v>
-      </c>
       <c r="AM10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>37:27</t>
+          <t>71:15</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>8.76</v>
+        <v>18.64</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.125</v>
+        <v>0.654</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.955</v>
+        <v>0.671</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.256</v>
+        <v>1.127</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.342</v>
+        <v>0.161</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.5</v>
+        <v>0.308</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.115</v>
+        <v>0.128</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.225</v>
+        <v>0.183</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.032</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="11">
@@ -1896,156 +1896,156 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
       </c>
       <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>12</v>
+      </c>
+      <c r="S11" t="n">
+        <v>14</v>
+      </c>
+      <c r="T11" t="n">
+        <v>64</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" t="n">
         <v>6</v>
       </c>
-      <c r="L11" t="n">
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3</v>
       </c>
-      <c r="M11" t="n">
+      <c r="AA11" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
         <v>2</v>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S11" t="n">
-        <v>8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>33</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1</v>
-      </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>57:20</t>
+          <t>92:16</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>26.28</v>
+        <v>41.04</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.526</v>
+        <v>0.645</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.638</v>
+        <v>0.71</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.18</v>
+        <v>1.316</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.076</v>
+        <v>0.073</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.579</v>
+        <v>0.452</v>
       </c>
       <c r="AU11" t="n">
-        <v>2</v>
+        <v>1.333</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.226</v>
+        <v>0.218</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.11</v>
+        <v>0.118</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.047</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="12">
@@ -2055,40 +2055,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H12" t="n">
         <v>7</v>
       </c>
-      <c r="E12" t="n">
+      <c r="I12" t="n">
         <v>8</v>
       </c>
-      <c r="F12" t="n">
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" t="n">
         <v>5</v>
       </c>
-      <c r="G12" t="n">
-        <v>14</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2103,108 +2103,108 @@
         <v>5</v>
       </c>
       <c r="R12" t="n">
+        <v>4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>9</v>
+      </c>
+      <c r="T12" t="n">
+        <v>55</v>
+      </c>
+      <c r="U12" t="n">
+        <v>10</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AE12" t="n">
         <v>2</v>
       </c>
-      <c r="S12" t="n">
-        <v>7</v>
-      </c>
-      <c r="T12" t="n">
-        <v>31</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="AF12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI12" t="n">
         <v>3</v>
       </c>
-      <c r="V12" t="n">
-        <v>3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AK12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AL12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AM12" t="n">
         <v>0.333</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>52:29</t>
+          <t>83:18</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>29.2</v>
+        <v>44.52</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.659</v>
+        <v>0.667</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.13</v>
+        <v>1.235</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.171</v>
+        <v>0.112</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.182</v>
+        <v>0.194</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.274</v>
+        <v>0.261</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="13">
@@ -2214,22 +2214,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
@@ -2238,40 +2238,40 @@
         <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
+        <v>11</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>6</v>
+      </c>
+      <c r="R13" t="n">
         <v>9</v>
       </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3</v>
-      </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2283,31 +2283,31 @@
         <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -2322,48 +2322,48 @@
         <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>55:18</t>
+          <t>85:43</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>14.64</v>
+        <v>22.64</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.444</v>
+        <v>0.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.515</v>
+        <v>0.541</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.82</v>
+        <v>0.795</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.205</v>
+        <v>0.265</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.444</v>
+        <v>0.286</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.333</v>
+        <v>2.167</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.131</v>
+        <v>0.129</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.026</v>
+        <v>0.049</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.171</v>
+        <v>0.139</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.075</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="14">
@@ -2373,68 +2373,68 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="C14" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>14</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
         <v>2</v>
       </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
@@ -2442,10 +2442,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AA14" t="n">
         <v>0.5</v>
@@ -2488,11 +2488,11 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AP14" t="n">
         <v>0.5</v>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.135</v>
+        <v>0.271</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.198</v>
+        <v>0.231</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.433</v>
+        <v>0.361</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -2532,100 +2532,100 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>44</v>
+      </c>
+      <c r="D15" t="n">
+        <v>19</v>
+      </c>
+      <c r="E15" t="n">
+        <v>27</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>18</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
         <v>3</v>
       </c>
-      <c r="C15" t="n">
-        <v>22</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>11</v>
+      </c>
+      <c r="S15" t="n">
         <v>9</v>
       </c>
-      <c r="E15" t="n">
+      <c r="T15" t="n">
+        <v>60</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>11</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC15" t="n">
         <v>13</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>13</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>30</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>5</v>
-      </c>
       <c r="AD15" t="n">
-        <v>0.4</v>
+        <v>0.615</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2647,38 +2647,38 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>54:22</t>
+          <t>88:55</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>15.76</v>
+        <v>32.4</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.745</v>
+        <v>0.701</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.396</v>
+        <v>1.358</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.063</v>
+        <v>0.031</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.308</v>
+        <v>0.222</v>
       </c>
       <c r="AU15" t="n">
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.143</v>
+        <v>0.178</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.053</v>
+        <v>0.141</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.252</v>
+        <v>0.22</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -2691,73 +2691,73 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>39</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11</v>
+      </c>
+      <c r="G16" t="n">
+        <v>17</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>11</v>
+      </c>
+      <c r="K16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" t="n">
-        <v>14</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>9</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>37</v>
+      </c>
+      <c r="U16" t="n">
         <v>4</v>
       </c>
-      <c r="G16" t="n">
-        <v>7</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>14</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2781,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -2796,51 +2796,51 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AL16" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.571</v>
+        <v>0.647</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>43:51</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>8.880000000000001</v>
+        <v>27.64</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.857</v>
+        <v>0.868</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.888</v>
+        <v>0.901</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.577</v>
+        <v>1.411</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.113</v>
+        <v>0.217</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.286</v>
+        <v>0.316</v>
       </c>
       <c r="AU16" t="n">
-        <v>3</v>
+        <v>1.833</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.263</v>
+        <v>0.308</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.033</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -2850,61 +2850,61 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>62</v>
+      </c>
+      <c r="D17" t="n">
+        <v>11</v>
+      </c>
+      <c r="E17" t="n">
+        <v>23</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
+        <v>17</v>
+      </c>
+      <c r="H17" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>14</v>
+      </c>
+      <c r="L17" t="n">
         <v>3</v>
       </c>
-      <c r="C17" t="n">
-        <v>43</v>
-      </c>
-      <c r="D17" t="n">
-        <v>9</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="M17" t="n">
+        <v>6</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>10</v>
+      </c>
+      <c r="S17" t="n">
         <v>18</v>
       </c>
-      <c r="F17" t="n">
-        <v>6</v>
-      </c>
-      <c r="G17" t="n">
-        <v>9</v>
-      </c>
-      <c r="H17" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" t="n">
-        <v>9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>11</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7</v>
-      </c>
-      <c r="S17" t="n">
-        <v>14</v>
-      </c>
       <c r="T17" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="U17" t="n">
         <v>9</v>
@@ -2913,93 +2913,93 @@
         <v>6</v>
       </c>
       <c r="W17" t="n">
+        <v>5</v>
+      </c>
+      <c r="X17" t="n">
         <v>2</v>
       </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH17" t="n">
         <v>3</v>
       </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF17" t="n">
+      <c r="AI17" t="n">
         <v>3</v>
       </c>
-      <c r="AG17" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2</v>
-      </c>
       <c r="AJ17" t="n">
         <v>1</v>
       </c>
       <c r="AK17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AL17" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AM17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>125:37</t>
+        </is>
+      </c>
+      <c r="AO17" t="n">
+        <v>52.28</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AU17" t="n">
         <v>0.571</v>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>79:10</t>
-        </is>
-      </c>
-      <c r="AO17" t="n">
-        <v>34.96</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0.694</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AV17" t="n">
-        <v>0.218</v>
+        <v>0.204</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.018</v>
+        <v>0.033</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.146</v>
+        <v>0.121</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="18">
@@ -3009,67 +3009,67 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>58</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>27</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>20</v>
+      </c>
+      <c r="I18" t="n">
+        <v>23</v>
+      </c>
+      <c r="J18" t="n">
+        <v>12</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20</v>
+      </c>
+      <c r="L18" t="n">
+        <v>8</v>
+      </c>
+      <c r="M18" t="n">
         <v>3</v>
       </c>
-      <c r="C18" t="n">
-        <v>35</v>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="n">
-        <v>18</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="n">
-        <v>18</v>
-      </c>
-      <c r="J18" t="n">
+      <c r="N18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7</v>
+      </c>
+      <c r="R18" t="n">
         <v>6</v>
       </c>
-      <c r="K18" t="n">
-        <v>11</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>4</v>
-      </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="T18" t="n">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="W18" t="n">
         <v>2</v>
@@ -3078,31 +3078,31 @@
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z18" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.625</v>
+        <v>0.632</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -3114,51 +3114,51 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>65:44</t>
+          <t>106:15</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>30.92</v>
+        <v>50.12</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.556</v>
+        <v>0.576</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.675</v>
+        <v>0.673</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.132</v>
+        <v>1.157</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.162</v>
+        <v>0.14</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.833</v>
+        <v>0.606</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.2</v>
+        <v>1.714</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.232</v>
+        <v>0.231</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.105</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.176</v>
+        <v>0.205</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="19">
@@ -3168,40 +3168,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="G19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" t="n">
+      <c r="K19" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" t="n">
         <v>2</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>7</v>
-      </c>
-      <c r="L19" t="n">
-        <v>3</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3216,108 +3216,108 @@
         <v>2</v>
       </c>
       <c r="R19" t="n">
+        <v>7</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>42</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC19" t="n">
         <v>4</v>
       </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>28</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
+      <c r="AD19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL19" t="n">
         <v>5</v>
       </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>4</v>
-      </c>
       <c r="AM19" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>56:21</t>
+          <t>96:05</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>19.88</v>
+        <v>28.76</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.706</v>
+        <v>0.72</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.727</v>
+        <v>0.747</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.308</v>
+        <v>1.391</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.101</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.118</v>
+        <v>0.16</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.174</v>
+        <v>0.146</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.077</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.131</v>
+        <v>0.091</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="20">
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -3354,10 +3354,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3486,153 +3486,153 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>278</v>
+        <v>475</v>
       </c>
       <c r="D21" t="n">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="E21" t="n">
-        <v>121</v>
+        <v>204</v>
       </c>
       <c r="F21" t="n">
+        <v>51</v>
+      </c>
+      <c r="G21" t="n">
+        <v>106</v>
+      </c>
+      <c r="H21" t="n">
+        <v>84</v>
+      </c>
+      <c r="I21" t="n">
+        <v>102</v>
+      </c>
+      <c r="J21" t="n">
+        <v>74</v>
+      </c>
+      <c r="K21" t="n">
+        <v>141</v>
+      </c>
+      <c r="L21" t="n">
+        <v>45</v>
+      </c>
+      <c r="M21" t="n">
+        <v>27</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>50</v>
+      </c>
+      <c r="R21" t="n">
+        <v>101</v>
+      </c>
+      <c r="S21" t="n">
+        <v>103</v>
+      </c>
+      <c r="T21" t="n">
+        <v>572</v>
+      </c>
+      <c r="U21" t="n">
+        <v>42</v>
+      </c>
+      <c r="V21" t="n">
+        <v>53</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>82</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>62</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="AE21" t="n">
         <v>29</v>
       </c>
-      <c r="G21" t="n">
-        <v>56</v>
-      </c>
-      <c r="H21" t="n">
-        <v>57</v>
-      </c>
-      <c r="I21" t="n">
-        <v>69</v>
-      </c>
-      <c r="J21" t="n">
-        <v>41</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="AF21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL21" t="n">
         <v>92</v>
       </c>
-      <c r="L21" t="n">
-        <v>19</v>
-      </c>
-      <c r="M21" t="n">
-        <v>17</v>
-      </c>
-      <c r="N21" t="n">
-        <v>10</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>33</v>
-      </c>
-      <c r="R21" t="n">
-        <v>59</v>
-      </c>
-      <c r="S21" t="n">
-        <v>66</v>
-      </c>
-      <c r="T21" t="n">
-        <v>335</v>
-      </c>
-      <c r="U21" t="n">
-        <v>25</v>
-      </c>
-      <c r="V21" t="n">
-        <v>26</v>
-      </c>
-      <c r="W21" t="n">
-        <v>13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>41</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>59</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>48</v>
-      </c>
       <c r="AM21" t="n">
-        <v>0.5</v>
+        <v>0.457</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>600:00</t>
+          <t>1000:00</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>243.36</v>
+        <v>408.88</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.624</v>
+        <v>0.631</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.67</v>
+        <v>0.669</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.142</v>
+        <v>1.162</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.148</v>
+        <v>0.132</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.322</v>
+        <v>0.271</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.139</v>
+        <v>1.37</v>
       </c>
       <c r="AV21" t="n">
         <v>0.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.046</v>
+        <v>0.062</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.161</v>
+        <v>0.153</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -3645,153 +3645,153 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>234</v>
+        <v>390</v>
       </c>
       <c r="D22" t="n">
+        <v>91</v>
+      </c>
+      <c r="E22" t="n">
+        <v>178</v>
+      </c>
+      <c r="F22" t="n">
+        <v>45</v>
+      </c>
+      <c r="G22" t="n">
+        <v>141</v>
+      </c>
+      <c r="H22" t="n">
+        <v>73</v>
+      </c>
+      <c r="I22" t="n">
+        <v>92</v>
+      </c>
+      <c r="J22" t="n">
+        <v>70</v>
+      </c>
+      <c r="K22" t="n">
+        <v>99</v>
+      </c>
+      <c r="L22" t="n">
+        <v>43</v>
+      </c>
+      <c r="M22" t="n">
+        <v>27</v>
+      </c>
+      <c r="N22" t="n">
+        <v>19</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>46</v>
+      </c>
+      <c r="R22" t="n">
+        <v>108</v>
+      </c>
+      <c r="S22" t="n">
+        <v>100</v>
+      </c>
+      <c r="T22" t="n">
+        <v>385</v>
+      </c>
+      <c r="U22" t="n">
+        <v>53</v>
+      </c>
+      <c r="V22" t="n">
+        <v>45</v>
+      </c>
+      <c r="W22" t="n">
+        <v>20</v>
+      </c>
+      <c r="X22" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y22" t="n">
         <v>50</v>
       </c>
-      <c r="E22" t="n">
-        <v>98</v>
-      </c>
-      <c r="F22" t="n">
-        <v>29</v>
-      </c>
-      <c r="G22" t="n">
-        <v>93</v>
-      </c>
-      <c r="H22" t="n">
-        <v>47</v>
-      </c>
-      <c r="I22" t="n">
-        <v>63</v>
-      </c>
-      <c r="J22" t="n">
-        <v>37</v>
-      </c>
-      <c r="K22" t="n">
-        <v>64</v>
-      </c>
-      <c r="L22" t="n">
-        <v>22</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="Z22" t="n">
+        <v>76</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AE22" t="n">
         <v>17</v>
       </c>
-      <c r="N22" t="n">
-        <v>10</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>29</v>
-      </c>
-      <c r="R22" t="n">
-        <v>67</v>
-      </c>
-      <c r="S22" t="n">
-        <v>58</v>
-      </c>
-      <c r="T22" t="n">
-        <v>215</v>
-      </c>
-      <c r="U22" t="n">
-        <v>43</v>
-      </c>
-      <c r="V22" t="n">
-        <v>25</v>
-      </c>
-      <c r="W22" t="n">
-        <v>12</v>
-      </c>
-      <c r="X22" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>31</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>4</v>
-      </c>
       <c r="AF22" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.174</v>
+        <v>0.283</v>
       </c>
       <c r="AH22" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.267</v>
+        <v>0.423</v>
       </c>
       <c r="AK22" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AL22" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.321</v>
+        <v>0.296</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>600:00</t>
+          <t>1000:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>250.72</v>
+        <v>412.48</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.49</v>
+        <v>0.497</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.535</v>
+        <v>0.542</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.946</v>
       </c>
       <c r="AS22" t="n">
         <v>0.128</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.246</v>
+        <v>0.229</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.156</v>
+        <v>1.321</v>
       </c>
       <c r="AV22" t="n">
         <v>0.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.039</v>
+        <v>0.047</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.154</v>
+        <v>0.138</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -3861,43 +3861,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="E24" t="n">
-        <v>6.667</v>
+        <v>6.4</v>
       </c>
       <c r="F24" t="n">
-        <v>1.333</v>
+        <v>1.2</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.333</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>1.333</v>
+        <v>1.6</v>
       </c>
       <c r="L24" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3909,108 +3909,108 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>2.333</v>
+        <v>2.4</v>
       </c>
       <c r="S24" t="n">
-        <v>1.333</v>
+        <v>1.6</v>
       </c>
       <c r="T24" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="U24" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="V24" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="W24" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="X24" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.667</v>
+        <v>1.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.667</v>
+        <v>4.2</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.545</v>
+        <v>0.476</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.333</v>
+        <v>2.8</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.571</v>
+        <v>0.357</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>23:43</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>11.693</v>
+        <v>11.768</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.517</v>
+        <v>0.469</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.511</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.026</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.207</v>
+        <v>0.184</v>
       </c>
       <c r="AU24" t="n">
         <v>2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.243</v>
+        <v>0.249</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.041</v>
+        <v>0.036</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.059</v>
+        <v>0.075</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="25">
@@ -4020,64 +4020,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>4.333</v>
+        <v>3.8</v>
       </c>
       <c r="D25" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="E25" t="n">
-        <v>1.333</v>
+        <v>0.8</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
         <v>2</v>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.333</v>
-      </c>
       <c r="S25" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="T25" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="U25" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -4089,10 +4089,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AA25" t="n">
         <v>0.667</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -4128,48 +4128,48 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>4.667</v>
+        <v>3.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.65</v>
+        <v>0.731</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.65</v>
+        <v>0.731</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.929</v>
+        <v>1.056</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.286</v>
+        <v>0.278</v>
       </c>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.143</v>
+        <v>0.116</v>
       </c>
       <c r="AW25" t="n">
         <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.196</v>
+        <v>0.157</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="26">
@@ -4179,91 +4179,91 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>3.667</v>
+        <v>4.2</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E26" t="n">
-        <v>0.333</v>
+        <v>1.4</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H26" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="I26" t="n">
-        <v>1.333</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.667</v>
+        <v>2.4</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="T26" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="X26" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.333</v>
+        <v>1.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4275,60 +4275,60 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="AM26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>2.92</v>
+        <v>3.728</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.125</v>
+        <v>0.654</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.955</v>
+        <v>0.671</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.256</v>
+        <v>1.127</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.342</v>
+        <v>0.161</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.5</v>
+        <v>0.308</v>
       </c>
       <c r="AU26" t="n">
         <v>1</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.115</v>
+        <v>0.128</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.225</v>
+        <v>0.183</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.032</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="27">
@@ -4338,31 +4338,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>10.333</v>
+        <v>10.8</v>
       </c>
       <c r="D27" t="n">
-        <v>3.333</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="H27" t="n">
-        <v>3.667</v>
+        <v>2.8</v>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="J27" t="n">
-        <v>1.333</v>
+        <v>0.8</v>
       </c>
       <c r="K27" t="n">
         <v>2</v>
@@ -4371,123 +4371,123 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>64</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA27" t="n">
         <v>0.667</v>
       </c>
-      <c r="N27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="T27" t="n">
-        <v>33</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.667</v>
+        <v>1.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.333</v>
+        <v>1.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.714</v>
+        <v>0.778</v>
       </c>
       <c r="AE27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AO27" t="n">
+        <v>8.208</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="AU27" t="n">
         <v>1.333</v>
       </c>
-      <c r="AF27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
-      <c r="AO27" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0.638</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>2</v>
-      </c>
       <c r="AV27" t="n">
-        <v>0.226</v>
+        <v>0.218</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.11</v>
+        <v>0.118</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.047</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="28">
@@ -4497,28 +4497,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
         <v>11</v>
       </c>
       <c r="D28" t="n">
-        <v>2.333</v>
+        <v>2.4</v>
       </c>
       <c r="E28" t="n">
-        <v>2.667</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>1.667</v>
+        <v>1.6</v>
       </c>
       <c r="G28" t="n">
-        <v>4.667</v>
+        <v>4.2</v>
       </c>
       <c r="H28" t="n">
-        <v>1.333</v>
+        <v>1.4</v>
       </c>
       <c r="I28" t="n">
-        <v>1.667</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>2</v>
@@ -4527,10 +4527,10 @@
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4539,114 +4539,114 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.667</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.667</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>55</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>0.667</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="T28" t="n">
-        <v>31</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AK28" t="n">
-        <v>1.333</v>
+        <v>1.2</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AM28" t="n">
         <v>0.333</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>9.733000000000001</v>
+        <v>8.904</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.659</v>
+        <v>0.667</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.13</v>
+        <v>1.235</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.171</v>
+        <v>0.112</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.182</v>
+        <v>0.194</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.274</v>
+        <v>0.261</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="29">
@@ -4656,156 +4656,156 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D29" t="n">
-        <v>0.333</v>
+        <v>0.8</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="F29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>29</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG29" t="n">
         <v>0.667</v>
       </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="T29" t="n">
-        <v>22</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AG29" t="n">
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AO29" t="n">
+        <v>4.528</v>
+      </c>
+      <c r="AP29" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AO29" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0.444</v>
-      </c>
       <c r="AQ29" t="n">
-        <v>0.515</v>
+        <v>0.541</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.82</v>
+        <v>0.795</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.205</v>
+        <v>0.265</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.444</v>
+        <v>0.286</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.333</v>
+        <v>2.167</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.131</v>
+        <v>0.129</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.026</v>
+        <v>0.049</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.171</v>
+        <v>0.139</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.075</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="30">
@@ -4815,16 +4815,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.667</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.667</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -4842,16 +4842,16 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L30" t="n">
-        <v>0.333</v>
+        <v>0.6</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="T30" t="n">
+        <v>14</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
         <v>2</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0.667</v>
       </c>
       <c r="AA30" t="n">
         <v>0.5</v>
@@ -4930,11 +4930,11 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>02:26</t>
+          <t>03:36</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>0.667</v>
+        <v>2</v>
       </c>
       <c r="AP30" t="n">
         <v>0.5</v>
@@ -4955,13 +4955,13 @@
         <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.135</v>
+        <v>0.271</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.198</v>
+        <v>0.231</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.433</v>
+        <v>0.361</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -4974,16 +4974,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>7.333</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="E31" t="n">
-        <v>4.333</v>
+        <v>5.4</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4992,83 +4992,83 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.333</v>
+        <v>1.2</v>
       </c>
       <c r="I31" t="n">
-        <v>1.333</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>4.333</v>
+        <v>3.6</v>
       </c>
       <c r="L31" t="n">
-        <v>0.667</v>
+        <v>1.8</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T31" t="n">
+        <v>60</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG31" t="n">
         <v>0.333</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="T31" t="n">
-        <v>30</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
       <c r="AH31" t="n">
         <v>0</v>
       </c>
@@ -5089,38 +5089,38 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>5.253</v>
+        <v>6.48</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.745</v>
+        <v>0.701</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.396</v>
+        <v>1.358</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.063</v>
+        <v>0.031</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.308</v>
+        <v>0.222</v>
       </c>
       <c r="AU31" t="n">
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.143</v>
+        <v>0.178</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.053</v>
+        <v>0.141</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.252</v>
+        <v>0.22</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -5133,34 +5133,34 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>4.667</v>
+        <v>7.8</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F32" t="n">
-        <v>1.333</v>
+        <v>2.2</v>
       </c>
       <c r="G32" t="n">
-        <v>2.333</v>
+        <v>3.4</v>
       </c>
       <c r="H32" t="n">
-        <v>0.667</v>
+        <v>1.2</v>
       </c>
       <c r="I32" t="n">
-        <v>0.667</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -5175,31 +5175,31 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.333</v>
+        <v>1.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.333</v>
+        <v>1.2</v>
       </c>
       <c r="R32" t="n">
-        <v>0.667</v>
+        <v>1.8</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="T32" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -5223,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -5238,51 +5238,51 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.333</v>
+        <v>2.2</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.333</v>
+        <v>3.4</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.571</v>
+        <v>0.647</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>05:33</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>2.96</v>
+        <v>5.528</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.857</v>
+        <v>0.868</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.888</v>
+        <v>0.901</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.577</v>
+        <v>1.411</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.113</v>
+        <v>0.217</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.286</v>
+        <v>0.316</v>
       </c>
       <c r="AU32" t="n">
-        <v>3</v>
+        <v>1.833</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.263</v>
+        <v>0.308</v>
       </c>
       <c r="AW32" t="n">
         <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.033</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -5292,82 +5292,82 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>14.333</v>
+        <v>12.4</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="F33" t="n">
         <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="H33" t="n">
-        <v>2.333</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="K33" t="n">
-        <v>3.667</v>
+        <v>2.8</v>
       </c>
       <c r="L33" t="n">
-        <v>0.333</v>
+        <v>0.6</v>
       </c>
       <c r="M33" t="n">
-        <v>1.333</v>
+        <v>1.2</v>
       </c>
       <c r="N33" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.333</v>
+        <v>1.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.333</v>
+        <v>1.4</v>
       </c>
       <c r="R33" t="n">
-        <v>2.333</v>
+        <v>2</v>
       </c>
       <c r="S33" t="n">
-        <v>4.667</v>
+        <v>3.6</v>
       </c>
       <c r="T33" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="U33" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="V33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y33" t="n">
         <v>2</v>
       </c>
-      <c r="W33" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.667</v>
-      </c>
       <c r="Z33" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5379,69 +5379,69 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="AF33" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="AJ33" t="n">
         <v>1</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.333</v>
+        <v>1.4</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.333</v>
+        <v>2.8</v>
       </c>
       <c r="AM33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>25:07</t>
+        </is>
+      </c>
+      <c r="AO33" t="n">
+        <v>10.456</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AU33" t="n">
         <v>0.571</v>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>26:23</t>
-        </is>
-      </c>
-      <c r="AO33" t="n">
-        <v>11.653</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0.694</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AV33" t="n">
-        <v>0.218</v>
+        <v>0.204</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.018</v>
+        <v>0.033</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.146</v>
+        <v>0.121</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="34">
@@ -5451,156 +5451,156 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>11.667</v>
+        <v>11.6</v>
       </c>
       <c r="D34" t="n">
-        <v>3.333</v>
+        <v>3.2</v>
       </c>
       <c r="E34" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="K34" t="n">
-        <v>3.667</v>
+        <v>4</v>
       </c>
       <c r="L34" t="n">
-        <v>1.333</v>
+        <v>1.6</v>
       </c>
       <c r="M34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>96</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG34" t="n">
         <v>0.667</v>
       </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="S34" t="n">
-        <v>5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>56</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="V34" t="n">
-        <v>2</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="X34" t="n">
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM34" t="n">
         <v>0.333</v>
       </c>
-      <c r="Y34" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>10.307</v>
+        <v>10.024</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.556</v>
+        <v>0.576</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.675</v>
+        <v>0.673</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.132</v>
+        <v>1.157</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.162</v>
+        <v>0.14</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.833</v>
+        <v>0.606</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.2</v>
+        <v>1.714</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.232</v>
+        <v>0.231</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.105</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.176</v>
+        <v>0.205</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="35">
@@ -5610,40 +5610,40 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>8.667</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="E35" t="n">
-        <v>4.333</v>
+        <v>3.8</v>
       </c>
       <c r="F35" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="G35" t="n">
-        <v>1.333</v>
+        <v>1.2</v>
       </c>
       <c r="H35" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="I35" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="K35" t="n">
-        <v>2.333</v>
+        <v>1.6</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5652,25 +5652,25 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="R35" t="n">
-        <v>1.333</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="T35" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.667</v>
+        <v>1.4</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -5679,87 +5679,87 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.667</v>
+        <v>1.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.333</v>
+        <v>2.4</v>
       </c>
       <c r="AA35" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC35" t="n">
         <v>0.8</v>
       </c>
-      <c r="AB35" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AD35" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>6.627</v>
+        <v>5.752</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.706</v>
+        <v>0.72</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.727</v>
+        <v>0.747</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.308</v>
+        <v>1.391</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.101</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.118</v>
+        <v>0.16</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.174</v>
+        <v>0.146</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.077</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.131</v>
+        <v>0.091</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="36">
@@ -5769,37 +5769,37 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>3</v>
       </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2.667</v>
-      </c>
       <c r="L36" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5811,7 +5811,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -5928,118 +5928,118 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>92.667</v>
+        <v>95</v>
       </c>
       <c r="D37" t="n">
-        <v>22.333</v>
+        <v>23.8</v>
       </c>
       <c r="E37" t="n">
-        <v>40.333</v>
+        <v>40.8</v>
       </c>
       <c r="F37" t="n">
-        <v>9.667</v>
+        <v>10.2</v>
       </c>
       <c r="G37" t="n">
-        <v>18.667</v>
+        <v>21.2</v>
       </c>
       <c r="H37" t="n">
-        <v>19</v>
+        <v>16.8</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>20.4</v>
       </c>
       <c r="J37" t="n">
-        <v>13.667</v>
+        <v>14.8</v>
       </c>
       <c r="K37" t="n">
-        <v>30.667</v>
+        <v>28.2</v>
       </c>
       <c r="L37" t="n">
-        <v>6.333</v>
+        <v>9</v>
       </c>
       <c r="M37" t="n">
-        <v>5.667</v>
+        <v>5.4</v>
       </c>
       <c r="N37" t="n">
-        <v>3.333</v>
+        <v>4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>10</v>
+      </c>
+      <c r="R37" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="T37" t="n">
+        <v>572</v>
+      </c>
+      <c r="U37" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W37" t="n">
+        <v>4</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AF37" t="n">
         <v>12</v>
       </c>
-      <c r="Q37" t="n">
-        <v>11</v>
-      </c>
-      <c r="R37" t="n">
-        <v>19.667</v>
-      </c>
-      <c r="S37" t="n">
-        <v>22</v>
-      </c>
-      <c r="T37" t="n">
-        <v>335</v>
-      </c>
-      <c r="U37" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="V37" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="W37" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>13.667</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>19.667</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>10.667</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>10</v>
-      </c>
       <c r="AG37" t="n">
-        <v>0.433</v>
+        <v>0.483</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.667</v>
+        <v>1.8</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.667</v>
+        <v>2.8</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.625</v>
+        <v>0.643</v>
       </c>
       <c r="AK37" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AL37" t="n">
-        <v>16</v>
+        <v>18.4</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.5</v>
+        <v>0.457</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
@@ -6047,34 +6047,34 @@
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>81.12</v>
+        <v>81.776</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.624</v>
+        <v>0.631</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.67</v>
+        <v>0.669</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.142</v>
+        <v>1.162</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.148</v>
+        <v>0.132</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.322</v>
+        <v>0.271</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.139</v>
+        <v>1.37</v>
       </c>
       <c r="AV37" t="n">
         <v>0.2</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.046</v>
+        <v>0.062</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.161</v>
+        <v>0.153</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -6087,118 +6087,118 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C38" t="n">
         <v>78</v>
       </c>
       <c r="D38" t="n">
-        <v>16.667</v>
+        <v>18.2</v>
       </c>
       <c r="E38" t="n">
-        <v>32.667</v>
+        <v>35.6</v>
       </c>
       <c r="F38" t="n">
-        <v>9.667</v>
+        <v>9</v>
       </c>
       <c r="G38" t="n">
-        <v>31</v>
+        <v>28.2</v>
       </c>
       <c r="H38" t="n">
-        <v>15.667</v>
+        <v>14.6</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>18.4</v>
       </c>
       <c r="J38" t="n">
-        <v>12.333</v>
+        <v>14</v>
       </c>
       <c r="K38" t="n">
-        <v>21.333</v>
+        <v>19.8</v>
       </c>
       <c r="L38" t="n">
-        <v>7.333</v>
+        <v>8.6</v>
       </c>
       <c r="M38" t="n">
-        <v>5.667</v>
+        <v>5.4</v>
       </c>
       <c r="N38" t="n">
-        <v>3.333</v>
+        <v>3.8</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>10.667</v>
+        <v>10.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.667</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R38" t="n">
-        <v>22.333</v>
+        <v>21.6</v>
       </c>
       <c r="S38" t="n">
-        <v>19.333</v>
+        <v>20</v>
       </c>
       <c r="T38" t="n">
-        <v>215</v>
+        <v>385</v>
       </c>
       <c r="U38" t="n">
-        <v>14.333</v>
+        <v>10.6</v>
       </c>
       <c r="V38" t="n">
-        <v>8.333</v>
+        <v>9</v>
       </c>
       <c r="W38" t="n">
         <v>4</v>
       </c>
       <c r="X38" t="n">
-        <v>2.333</v>
+        <v>2.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>10.333</v>
+        <v>10</v>
       </c>
       <c r="Z38" t="n">
-        <v>16.667</v>
+        <v>15.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.62</v>
+        <v>0.658</v>
       </c>
       <c r="AB38" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.333</v>
+        <v>8.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.333</v>
+        <v>3.4</v>
       </c>
       <c r="AF38" t="n">
-        <v>7.667</v>
+        <v>12</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.174</v>
+        <v>0.283</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.333</v>
+        <v>2.2</v>
       </c>
       <c r="AI38" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.267</v>
+        <v>0.423</v>
       </c>
       <c r="AK38" t="n">
-        <v>8.333</v>
+        <v>6.8</v>
       </c>
       <c r="AL38" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.321</v>
+        <v>0.296</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
@@ -6206,34 +6206,34 @@
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>83.57299999999999</v>
+        <v>82.496</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.49</v>
+        <v>0.497</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.535</v>
+        <v>0.542</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.946</v>
       </c>
       <c r="AS38" t="n">
         <v>0.128</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.246</v>
+        <v>0.229</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.156</v>
+        <v>1.321</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.206</v>
+        <v>0.202</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.053</v>
+        <v>0.06</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.112</v>
+        <v>0.108</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>

--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Barça.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Barça.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>363.88</v>
+        <v>295.44</v>
       </c>
       <c r="C2" t="n">
-        <v>366.68</v>
+        <v>297.6</v>
       </c>
       <c r="D2" t="n">
-        <v>129.5407439729464</v>
+        <v>127.016129032258</v>
       </c>
       <c r="E2" t="n">
-        <v>106.3597687356823</v>
+        <v>101.1424731182796</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6306451612903226</v>
+        <v>0.6370967741935484</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1320680884367051</v>
+        <v>0.1431007185482889</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3125</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2709677419354839</v>
+        <v>0.25</v>
       </c>
       <c r="J2" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K2" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="L2" t="n">
+        <v>19</v>
+      </c>
+      <c r="M2" t="n">
+        <v>44</v>
+      </c>
+      <c r="N2" t="n">
+        <v>50</v>
+      </c>
+      <c r="O2" t="n">
+        <v>73</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.2943548387096774</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.2056451612903226</v>
+      </c>
+      <c r="T2" t="n">
         <v>20</v>
       </c>
-      <c r="M2" t="n">
-        <v>50</v>
-      </c>
-      <c r="N2" t="n">
-        <v>58</v>
-      </c>
-      <c r="O2" t="n">
-        <v>82</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.2645161290322581</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>32</v>
-      </c>
-      <c r="R2" t="n">
-        <v>62</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>29</v>
-      </c>
       <c r="U2" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.1653225806451613</v>
       </c>
       <c r="W2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.04516129032258064</v>
+        <v>0.04032258064516129</v>
       </c>
       <c r="Z2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2967741935483871</v>
+        <v>0.2943548387096774</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7073170731707317</v>
+        <v>0.684931506849315</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5161290322580645</v>
+        <v>0.4901960784313725</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4833333333333333</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4565217391304348</v>
+        <v>0.4931506849315068</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.414634146341463</v>
+        <v>1.36986301369863</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.975609756097561</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.443396226415094</v>
+        <v>1.518072289156627</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7924528301886793</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.177777777777778</v>
+        <v>1.121212121212121</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.666666666666667</v>
+        <v>1.727272727272727</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.37037037037037</v>
+        <v>1.276595744680851</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.74074074074074</v>
+        <v>5.276595744680851</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.111111111111111</v>
+        <v>6.553191489361702</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72.776</v>
+        <v>73.86</v>
       </c>
       <c r="C3" t="n">
-        <v>73.336</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>129.5407439729464</v>
+        <v>127.016129032258</v>
       </c>
       <c r="E3" t="n">
-        <v>106.3597687356823</v>
+        <v>101.1424731182796</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6306451612903226</v>
+        <v>0.6370967741935484</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1320680884367052</v>
+        <v>0.1431007185482889</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3125</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2709677419354839</v>
+        <v>0.25</v>
       </c>
       <c r="J3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>10.6</v>
+        <v>9.25</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>11.6</v>
+        <v>12.5</v>
       </c>
       <c r="O3" t="n">
-        <v>16.4</v>
+        <v>18.25</v>
       </c>
       <c r="P3" t="n">
-        <v>0.264516129032258</v>
+        <v>0.2943548387096774</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="R3" t="n">
-        <v>12.4</v>
+        <v>12.75</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2</v>
+        <v>0.2056451612903226</v>
       </c>
       <c r="T3" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="U3" t="n">
-        <v>12</v>
+        <v>10.25</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.1653225806451613</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04516129032258064</v>
+        <v>0.04032258064516129</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.4</v>
+        <v>18.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2967741935483871</v>
+        <v>0.2943548387096774</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7073170731707318</v>
+        <v>0.684931506849315</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5161290322580645</v>
+        <v>0.4901960784313725</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4833333333333333</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4565217391304348</v>
+        <v>0.4931506849315068</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.414634146341464</v>
+        <v>1.36986301369863</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.975609756097561</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.443396226415094</v>
+        <v>1.518072289156627</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7924528301886793</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.177777777777778</v>
+        <v>1.121212121212121</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.666666666666667</v>
+        <v>1.727272727272727</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.37037037037037</v>
+        <v>1.276595744680851</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.74074074074074</v>
+        <v>5.276595744680851</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.111111111111111</v>
+        <v>6.553191489361702</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>369.48</v>
+        <v>299.76</v>
       </c>
       <c r="C4" t="n">
-        <v>366.68</v>
+        <v>297.6</v>
       </c>
       <c r="D4" t="n">
-        <v>106.3597687356823</v>
+        <v>101.1424731182796</v>
       </c>
       <c r="E4" t="n">
-        <v>129.5407439729464</v>
+        <v>127.016129032258</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4968652037617555</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1284910783553142</v>
+        <v>0.1292222622911408</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2336956521739131</v>
+        <v>0.2156862745098039</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2288401253918495</v>
+        <v>0.2392156862745098</v>
       </c>
       <c r="J4" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="K4" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="L4" t="n">
         <v>20</v>
       </c>
       <c r="M4" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N4" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O4" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2382445141065831</v>
+        <v>0.2627450980392157</v>
       </c>
       <c r="Q4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="R4" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1316614420062696</v>
+        <v>0.1294117647058824</v>
       </c>
       <c r="T4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="U4" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1880877742946709</v>
+        <v>0.1725490196078431</v>
       </c>
       <c r="W4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="X4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.07450980392156863</v>
+      </c>
+      <c r="Z4" t="n">
         <v>26</v>
       </c>
-      <c r="Y4" t="n">
-        <v>0.08150470219435736</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>34</v>
-      </c>
       <c r="AA4" t="n">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3605015673981191</v>
+        <v>0.3607843137254902</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.6578947368421053</v>
+        <v>0.6417910447761194</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.2045454545454546</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4230769230769231</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2956521739130435</v>
+        <v>0.2826086956521739</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.315789473684211</v>
+        <v>1.283582089552239</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.9574468085106383</v>
+        <v>0.8648648648648649</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.9814814814814815</v>
+        <v>1</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.046511627906977</v>
+        <v>1</v>
       </c>
       <c r="AM4" t="n">
         <v>1.538461538461539</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.320754716981132</v>
+        <v>1.186046511627907</v>
       </c>
       <c r="AO4" t="n">
-        <v>6.018867924528302</v>
+        <v>5.930232558139535</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.339622641509434</v>
+        <v>7.116279069767442</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.896</v>
+        <v>74.94</v>
       </c>
       <c r="C5" t="n">
-        <v>73.336</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>106.3597687356823</v>
+        <v>101.1424731182796</v>
       </c>
       <c r="E5" t="n">
-        <v>129.5407439729464</v>
+        <v>127.016129032258</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4968652037617555</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1284910783553142</v>
+        <v>0.1292222622911408</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2336956521739131</v>
+        <v>0.2156862745098039</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2288401253918495</v>
+        <v>0.2392156862745098</v>
       </c>
       <c r="J5" t="n">
-        <v>10.6</v>
+        <v>11.75</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>8.25</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="O5" t="n">
-        <v>15.2</v>
+        <v>16.75</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2382445141065831</v>
+        <v>0.2627450980392157</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>8.4</v>
+        <v>8.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1316614420062696</v>
+        <v>0.1294117647058824</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1880877742946709</v>
+        <v>0.1725490196078431</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08150470219435738</v>
+        <v>0.07450980392156863</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA5" t="n">
         <v>23</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3605015673981191</v>
+        <v>0.3607843137254902</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6578947368421053</v>
+        <v>0.6417910447761194</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.2045454545454546</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4230769230769231</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.2956521739130435</v>
+        <v>0.2826086956521739</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.315789473684211</v>
+        <v>1.283582089552239</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9574468085106383</v>
+        <v>0.8648648648648649</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.9814814814814814</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.046511627906977</v>
+        <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.538461538461538</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.320754716981132</v>
+        <v>1.186046511627907</v>
       </c>
       <c r="AO5" t="n">
-        <v>6.018867924528302</v>
+        <v>5.930232558139535</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.339622641509434</v>
+        <v>7.116279069767442</v>
       </c>
     </row>
     <row r="7">
@@ -1419,34 +1419,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" t="n">
-        <v>17</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" t="n">
         <v>9</v>
       </c>
-      <c r="I8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J8" t="n">
-        <v>10</v>
-      </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
@@ -1455,120 +1455,120 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
         <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
         <v>5</v>
       </c>
-      <c r="AA8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>6</v>
-      </c>
       <c r="AD8" t="n">
-        <v>0.167</v>
+        <v>0.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.476</v>
+        <v>0.533</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.357</v>
+        <v>0.364</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>115:27</t>
+          <t>89:15</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>58.84</v>
+        <v>44.08</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.469</v>
+        <v>0.459</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.511</v>
+        <v>0.499</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.907</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.184</v>
+        <v>0.162</v>
       </c>
       <c r="AU8" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.249</v>
+        <v>0.241</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.036</v>
+        <v>0.047</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.067</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="9">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
         <v>19</v>
@@ -1602,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
         <v>11</v>
@@ -1626,7 +1626,7 @@
         <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>76:04</t>
+          <t>60:59</t>
         </is>
       </c>
       <c r="AO9" t="n">
@@ -1715,16 +1715,16 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.116</v>
+        <v>0.144</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.157</v>
+        <v>0.189</v>
       </c>
       <c r="AY9" t="n">
         <v>0.031</v>
@@ -1737,40 +1737,40 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
         <v>5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>21</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="n">
-        <v>7</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
         <v>4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
@@ -1785,16 +1785,16 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1806,22 +1806,22 @@
         <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>3</v>
       </c>
       <c r="AC10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1836,10 +1836,10 @@
         <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AK10" t="n">
         <v>1</v>
@@ -1852,41 +1852,41 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>71:15</t>
+          <t>57:41</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>18.64</v>
+        <v>14.76</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.654</v>
+        <v>0.75</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.671</v>
+        <v>0.723</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.127</v>
+        <v>1.152</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.161</v>
+        <v>0.203</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.308</v>
+        <v>0.2</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.128</v>
+        <v>0.125</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.183</v>
+        <v>0.181</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="11">
@@ -1896,37 +1896,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" t="n">
         <v>20</v>
       </c>
-      <c r="E11" t="n">
-        <v>29</v>
-      </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
         <v>3</v>
@@ -1944,52 +1944,52 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="S11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="AE11" t="n">
         <v>6</v>
       </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>11</v>
       </c>
-      <c r="AF11" t="n">
-        <v>17</v>
-      </c>
       <c r="AG11" t="n">
-        <v>0.647</v>
+        <v>0.545</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -2004,48 +2004,48 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>92:16</t>
+          <t>74:01</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>41.04</v>
+        <v>29.28</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.645</v>
+        <v>0.571</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.71</v>
+        <v>0.666</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.316</v>
+        <v>1.195</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.073</v>
+        <v>0.102</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.452</v>
+        <v>0.524</v>
       </c>
       <c r="AU11" t="n">
         <v>1.333</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.218</v>
+        <v>0.193</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.075</v>
+        <v>0.057</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.118</v>
+        <v>0.113</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="12">
@@ -2055,40 +2055,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" t="n">
         <v>7</v>
       </c>
-      <c r="I12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>10</v>
-      </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2103,16 +2103,16 @@
         <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="U12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
         <v>5</v>
@@ -2133,22 +2133,22 @@
         <v>1</v>
       </c>
       <c r="AB12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC12" t="n">
         <v>7</v>
       </c>
-      <c r="AC12" t="n">
-        <v>8</v>
-      </c>
       <c r="AD12" t="n">
-        <v>0.875</v>
+        <v>0.857</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AH12" t="n">
         <v>2</v>
@@ -2163,48 +2163,48 @@
         <v>6</v>
       </c>
       <c r="AL12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>83:18</t>
+          <t>69:26</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>44.52</v>
+        <v>39.64</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.667</v>
+        <v>0.719</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.696</v>
+        <v>0.736</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.235</v>
+        <v>1.287</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.112</v>
+        <v>0.126</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.194</v>
+        <v>0.156</v>
       </c>
       <c r="AU12" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.067</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="13">
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
         <v>18</v>
@@ -2229,7 +2229,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
@@ -2238,16 +2238,16 @@
         <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
@@ -2262,13 +2262,13 @@
         <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U13" t="n">
         <v>2</v>
@@ -2322,48 +2322,48 @@
         <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>85:43</t>
+          <t>71:10</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>22.64</v>
+        <v>20.64</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.5</v>
+        <v>0.583</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.541</v>
+        <v>0.615</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.795</v>
+        <v>0.872</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.265</v>
+        <v>0.291</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.167</v>
+        <v>1.667</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.129</v>
+        <v>0.141</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.049</v>
+        <v>0.039</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.139</v>
+        <v>0.147</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.079</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="14">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.271</v>
+        <v>0.27</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.231</v>
+        <v>0.233</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.361</v>
+        <v>0.347</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -2532,16 +2532,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2550,82 +2550,82 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
         <v>6</v>
       </c>
-      <c r="I15" t="n">
-        <v>10</v>
-      </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
         <v>9</v>
       </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>11</v>
-      </c>
       <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>40</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC15" t="n">
         <v>9</v>
       </c>
-      <c r="T15" t="n">
-        <v>60</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>11</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>13</v>
-      </c>
       <c r="AD15" t="n">
-        <v>0.615</v>
+        <v>0.444</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2647,23 +2647,23 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>88:55</t>
+          <t>67:06</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>32.4</v>
+        <v>21.64</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.704</v>
+        <v>0.667</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.701</v>
+        <v>0.678</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.358</v>
+        <v>1.294</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.031</v>
+        <v>0.046</v>
       </c>
       <c r="AT15" t="n">
         <v>0.222</v>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.178</v>
+        <v>0.157</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.141</v>
+        <v>0.126</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.22</v>
+        <v>0.234</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -2691,67 +2691,67 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>26</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
         <v>5</v>
       </c>
-      <c r="C16" t="n">
-        <v>39</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>11</v>
-      </c>
-      <c r="G16" t="n">
-        <v>17</v>
-      </c>
-      <c r="H16" t="n">
-        <v>6</v>
-      </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>11</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>27</v>
+      </c>
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>9</v>
-      </c>
-      <c r="S16" t="n">
-        <v>7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>37</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4</v>
-      </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>3</v>
@@ -2781,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -2796,51 +2796,51 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.647</v>
+        <v>0.571</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>43:51</t>
+          <t>33:25</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>27.64</v>
+        <v>17.88</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.868</v>
+        <v>0.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.901</v>
+        <v>0.819</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.411</v>
+        <v>1.454</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.217</v>
+        <v>0.112</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.316</v>
+        <v>0.133</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.833</v>
+        <v>4.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.308</v>
+        <v>0.261</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.074</v>
+        <v>0.063</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -2850,61 +2850,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" t="n">
         <v>11</v>
       </c>
-      <c r="E17" t="n">
-        <v>23</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>17</v>
-      </c>
       <c r="H17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>13</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
         <v>4</v>
       </c>
-      <c r="K17" t="n">
-        <v>14</v>
-      </c>
-      <c r="L17" t="n">
-        <v>3</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>6</v>
       </c>
-      <c r="N17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
         <v>7</v>
       </c>
-      <c r="Q17" t="n">
-        <v>7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>10</v>
-      </c>
       <c r="S17" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T17" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="U17" t="n">
         <v>9</v>
@@ -2919,13 +2919,13 @@
         <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.714</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2940,66 +2940,66 @@
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AH17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ17" t="n">
         <v>1</v>
       </c>
       <c r="AK17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AL17" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>125:37</t>
+          <t>99:07</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>52.28</v>
+        <v>41.96</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.65</v>
+        <v>0.641</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.186</v>
+        <v>1.144</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.134</v>
+        <v>0.143</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.25</v>
+        <v>0.219</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.571</v>
+        <v>0.333</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.204</v>
+        <v>0.206</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.033</v>
+        <v>0.028</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.121</v>
+        <v>0.137</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.027</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="18">
@@ -3009,43 +3009,43 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
       </c>
       <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>17</v>
+      </c>
+      <c r="I18" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" t="n">
+        <v>10</v>
+      </c>
+      <c r="K18" t="n">
+        <v>16</v>
+      </c>
+      <c r="L18" t="n">
         <v>6</v>
       </c>
-      <c r="H18" t="n">
-        <v>20</v>
-      </c>
-      <c r="I18" t="n">
-        <v>23</v>
-      </c>
-      <c r="J18" t="n">
-        <v>12</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20</v>
-      </c>
-      <c r="L18" t="n">
-        <v>8</v>
-      </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -3057,19 +3057,19 @@
         <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="T18" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W18" t="n">
         <v>2</v>
@@ -3078,31 +3078,31 @@
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.632</v>
+        <v>0.647</v>
       </c>
       <c r="AB18" t="n">
         <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -3117,48 +3117,48 @@
         <v>2</v>
       </c>
       <c r="AL18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>106:15</t>
+          <t>83:50</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>50.12</v>
+        <v>39.8</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.576</v>
+        <v>0.667</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.673</v>
+        <v>0.747</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.157</v>
+        <v>1.231</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.14</v>
+        <v>0.176</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.606</v>
+        <v>0.708</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.714</v>
+        <v>1.429</v>
       </c>
       <c r="AV18" t="n">
         <v>0.231</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.205</v>
+        <v>0.2</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.079</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="19">
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D19" t="n">
         <v>12</v>
@@ -3180,10 +3180,10 @@
         <v>19</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
         <v>4</v>
@@ -3216,13 +3216,13 @@
         <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -3264,13 +3264,13 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>3</v>
@@ -3283,41 +3283,41 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>96:05</t>
+          <t>78:26</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>28.76</v>
+        <v>27.76</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.72</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.747</v>
+        <v>0.718</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.391</v>
+        <v>1.333</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.16</v>
+        <v>0.167</v>
       </c>
       <c r="AU19" t="n">
         <v>1</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.146</v>
+        <v>0.172</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.091</v>
+        <v>0.107</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="20">
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -3354,10 +3354,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3486,153 +3486,153 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>475</v>
+        <v>378</v>
       </c>
       <c r="D21" t="n">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="E21" t="n">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="F21" t="n">
+        <v>42</v>
+      </c>
+      <c r="G21" t="n">
+        <v>83</v>
+      </c>
+      <c r="H21" t="n">
+        <v>62</v>
+      </c>
+      <c r="I21" t="n">
+        <v>76</v>
+      </c>
+      <c r="J21" t="n">
+        <v>60</v>
+      </c>
+      <c r="K21" t="n">
+        <v>120</v>
+      </c>
+      <c r="L21" t="n">
+        <v>33</v>
+      </c>
+      <c r="M21" t="n">
+        <v>21</v>
+      </c>
+      <c r="N21" t="n">
+        <v>16</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>44</v>
+      </c>
+      <c r="R21" t="n">
+        <v>80</v>
+      </c>
+      <c r="S21" t="n">
+        <v>81</v>
+      </c>
+      <c r="T21" t="n">
+        <v>457</v>
+      </c>
+      <c r="U21" t="n">
+        <v>32</v>
+      </c>
+      <c r="V21" t="n">
+        <v>37</v>
+      </c>
+      <c r="W21" t="n">
+        <v>19</v>
+      </c>
+      <c r="X21" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>73</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC21" t="n">
         <v>51</v>
       </c>
-      <c r="G21" t="n">
-        <v>106</v>
-      </c>
-      <c r="H21" t="n">
-        <v>84</v>
-      </c>
-      <c r="I21" t="n">
-        <v>102</v>
-      </c>
-      <c r="J21" t="n">
-        <v>74</v>
-      </c>
-      <c r="K21" t="n">
-        <v>141</v>
-      </c>
-      <c r="L21" t="n">
-        <v>45</v>
-      </c>
-      <c r="M21" t="n">
-        <v>27</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="AD21" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AE21" t="n">
         <v>20</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>54</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>50</v>
-      </c>
-      <c r="R21" t="n">
-        <v>101</v>
-      </c>
-      <c r="S21" t="n">
-        <v>103</v>
-      </c>
-      <c r="T21" t="n">
-        <v>572</v>
-      </c>
-      <c r="U21" t="n">
-        <v>42</v>
-      </c>
-      <c r="V21" t="n">
-        <v>53</v>
-      </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>82</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.707</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>62</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>29</v>
-      </c>
       <c r="AF21" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.483</v>
+        <v>0.488</v>
       </c>
       <c r="AH21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AI21" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.643</v>
+        <v>0.6</v>
       </c>
       <c r="AK21" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL21" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.457</v>
+        <v>0.493</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>1000:00</t>
+          <t>800:00</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>408.88</v>
+        <v>328.44</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.631</v>
+        <v>0.637</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.669</v>
+        <v>0.672</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.162</v>
+        <v>1.151</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.132</v>
+        <v>0.143</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.271</v>
+        <v>0.25</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.37</v>
+        <v>1.277</v>
       </c>
       <c r="AV21" t="n">
         <v>0.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.062</v>
+        <v>0.058</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.153</v>
+        <v>0.157</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -3645,67 +3645,67 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>390</v>
+        <v>301</v>
       </c>
       <c r="D22" t="n">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E22" t="n">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="F22" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="H22" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="I22" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J22" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="K22" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="L22" t="n">
+        <v>33</v>
+      </c>
+      <c r="M22" t="n">
+        <v>22</v>
+      </c>
+      <c r="N22" t="n">
+        <v>15</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>43</v>
       </c>
-      <c r="M22" t="n">
-        <v>27</v>
-      </c>
-      <c r="N22" t="n">
-        <v>19</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>53</v>
-      </c>
       <c r="Q22" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="R22" t="n">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="T22" t="n">
-        <v>385</v>
+        <v>288</v>
       </c>
       <c r="U22" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="V22" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="W22" t="n">
         <v>20</v>
@@ -3714,84 +3714,84 @@
         <v>13</v>
       </c>
       <c r="Y22" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Z22" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.658</v>
+        <v>0.642</v>
       </c>
       <c r="AB22" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AC22" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.571</v>
+        <v>0.606</v>
       </c>
       <c r="AE22" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AF22" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AG22" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>92</v>
+      </c>
+      <c r="AM22" t="n">
         <v>0.283</v>
       </c>
-      <c r="AH22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>115</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0.296</v>
-      </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>1000:00</t>
+          <t>800:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>412.48</v>
+        <v>332.76</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.497</v>
+        <v>0.471</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.542</v>
+        <v>0.519</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.946</v>
+        <v>0.905</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.128</v>
+        <v>0.129</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.229</v>
+        <v>0.239</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.321</v>
+        <v>1.186</v>
       </c>
       <c r="AV22" t="n">
         <v>0.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.047</v>
+        <v>0.043</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.138</v>
+        <v>0.142</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -3861,156 +3861,156 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="E24" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="K24" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>27</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD24" t="n">
         <v>0.2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T24" t="n">
-        <v>37</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.167</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.476</v>
+        <v>0.533</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
         <v>1</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.357</v>
+        <v>0.364</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:18</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>11.768</v>
+        <v>11.02</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.469</v>
+        <v>0.459</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.511</v>
+        <v>0.499</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.907</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.184</v>
+        <v>0.162</v>
       </c>
       <c r="AU24" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.249</v>
+        <v>0.241</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.036</v>
+        <v>0.047</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.067</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="25">
@@ -4020,22 +4020,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="G25" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -4047,37 +4047,37 @@
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="T25" t="n">
         <v>22</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -4089,10 +4089,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AA25" t="n">
         <v>0.667</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -4125,21 +4125,21 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AM25" t="n">
         <v>0.556</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AP25" t="n">
         <v>0.731</v>
@@ -4157,16 +4157,16 @@
         <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.116</v>
+        <v>0.144</v>
       </c>
       <c r="AW25" t="n">
         <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.157</v>
+        <v>0.189</v>
       </c>
       <c r="AY25" t="n">
         <v>0.031</v>
@@ -4179,156 +4179,156 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="E26" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="F26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>25</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD26" t="n">
         <v>0.6</v>
       </c>
-      <c r="G26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T26" t="n">
-        <v>29</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD26" t="n">
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AI26" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AJ26" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AL26" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0.4</v>
       </c>
       <c r="AM26" t="n">
         <v>0.5</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>3.728</v>
+        <v>3.69</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.654</v>
+        <v>0.75</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.671</v>
+        <v>0.723</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.127</v>
+        <v>1.152</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.161</v>
+        <v>0.203</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.308</v>
+        <v>0.2</v>
       </c>
       <c r="AU26" t="n">
         <v>1</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.128</v>
+        <v>0.125</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.183</v>
+        <v>0.181</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="27">
@@ -4338,100 +4338,100 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
         <v>5</v>
       </c>
-      <c r="C27" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="D27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" t="n">
-        <v>5.8</v>
-      </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="H27" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="N27" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="R27" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="U27" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="V27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="X27" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.778</v>
+        <v>0.714</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.647</v>
+        <v>0.545</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
@@ -4446,48 +4446,48 @@
         <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="AM27" t="n">
         <v>0</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>8.208</v>
+        <v>7.32</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.645</v>
+        <v>0.571</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.71</v>
+        <v>0.666</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.316</v>
+        <v>1.195</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.073</v>
+        <v>0.102</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.452</v>
+        <v>0.524</v>
       </c>
       <c r="AU27" t="n">
         <v>1.333</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.218</v>
+        <v>0.193</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.075</v>
+        <v>0.057</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.118</v>
+        <v>0.113</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="28">
@@ -4497,67 +4497,67 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>12.75</v>
       </c>
       <c r="D28" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="H28" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S28" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1.8</v>
-      </c>
       <c r="T28" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -4566,87 +4566,87 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AA28" t="n">
         <v>1</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.875</v>
+        <v>0.857</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AG28" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AH28" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH28" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AI28" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AJ28" t="n">
         <v>0.667</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>8.904</v>
+        <v>9.91</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.667</v>
+        <v>0.719</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.696</v>
+        <v>0.736</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.235</v>
+        <v>1.287</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.112</v>
+        <v>0.126</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.194</v>
+        <v>0.156</v>
       </c>
       <c r="AU28" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.067</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="29">
@@ -4656,97 +4656,97 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="K29" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="L29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="N29" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T29" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U29" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="X29" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AA29" t="n">
         <v>1</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AD29" t="n">
         <v>0.2</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AG29" t="n">
         <v>0.667</v>
@@ -4761,51 +4761,51 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AL29" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>4.528</v>
+        <v>5.16</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.5</v>
+        <v>0.583</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.541</v>
+        <v>0.615</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.795</v>
+        <v>0.872</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.265</v>
+        <v>0.291</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.167</v>
+        <v>1.667</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.129</v>
+        <v>0.141</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.049</v>
+        <v>0.039</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.139</v>
+        <v>0.147</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.079</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="30">
@@ -4815,16 +4815,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -4842,16 +4842,16 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="L30" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="T30" t="n">
         <v>14</v>
@@ -4875,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -4884,10 +4884,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AA30" t="n">
         <v>0.5</v>
@@ -4930,11 +4930,11 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>03:36</t>
+          <t>04:31</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AP30" t="n">
         <v>0.5</v>
@@ -4955,13 +4955,13 @@
         <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.271</v>
+        <v>0.27</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.231</v>
+        <v>0.233</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.361</v>
+        <v>0.347</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -4974,16 +4974,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4992,82 +4992,82 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>40</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>60</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AA31" t="n">
-        <v>0.909</v>
+        <v>0.875</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.615</v>
+        <v>0.444</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
@@ -5089,23 +5089,23 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>6.48</v>
+        <v>5.41</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.704</v>
+        <v>0.667</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.701</v>
+        <v>0.678</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.358</v>
+        <v>1.294</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.031</v>
+        <v>0.046</v>
       </c>
       <c r="AT31" t="n">
         <v>0.222</v>
@@ -5114,13 +5114,13 @@
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.178</v>
+        <v>0.157</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.141</v>
+        <v>0.126</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.22</v>
+        <v>0.234</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -5133,34 +5133,34 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="F32" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H32" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -5175,114 +5175,114 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="U32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="AO32" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="AP32" t="n">
         <v>0.8</v>
       </c>
-      <c r="V32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>08:46</t>
-        </is>
-      </c>
-      <c r="AO32" t="n">
-        <v>5.528</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0.868</v>
-      </c>
       <c r="AQ32" t="n">
-        <v>0.901</v>
+        <v>0.819</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.411</v>
+        <v>1.454</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.217</v>
+        <v>0.112</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.316</v>
+        <v>0.133</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.833</v>
+        <v>4.5</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.308</v>
+        <v>0.261</v>
       </c>
       <c r="AW32" t="n">
         <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.074</v>
+        <v>0.063</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -5292,156 +5292,156 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="D33" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="E33" t="n">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="G33" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K33" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="L33" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="S33" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T33" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="U33" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="V33" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="X33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.714</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AJ33" t="n">
         <v>1</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>25:07</t>
+          <t>24:46</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>10.456</v>
+        <v>10.49</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.65</v>
+        <v>0.641</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.186</v>
+        <v>1.144</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.134</v>
+        <v>0.143</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.25</v>
+        <v>0.219</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.571</v>
+        <v>0.333</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.204</v>
+        <v>0.206</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.033</v>
+        <v>0.028</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.121</v>
+        <v>0.137</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.027</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="34">
@@ -5451,40 +5451,40 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="I34" t="n">
         <v>5</v>
       </c>
-      <c r="C34" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="D34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E34" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H34" t="n">
-        <v>4</v>
-      </c>
-      <c r="I34" t="n">
-        <v>4.6</v>
-      </c>
       <c r="J34" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K34" t="n">
         <v>4</v>
       </c>
       <c r="L34" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M34" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
@@ -5493,114 +5493,114 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="R34" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S34" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="T34" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="U34" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="V34" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="W34" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="X34" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.632</v>
+        <v>0.647</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AM34" t="n">
         <v>0.667</v>
       </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>10.024</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.576</v>
+        <v>0.667</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.673</v>
+        <v>0.747</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.157</v>
+        <v>1.231</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.14</v>
+        <v>0.176</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.606</v>
+        <v>0.708</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.714</v>
+        <v>1.429</v>
       </c>
       <c r="AV34" t="n">
         <v>0.231</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.205</v>
+        <v>0.2</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.079</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="35">
@@ -5610,40 +5610,40 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>9.25</v>
       </c>
       <c r="D35" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="G35" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K35" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="M35" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5652,25 +5652,25 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S35" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="T35" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -5679,19 +5679,19 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AA35" t="n">
         <v>0.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD35" t="n">
         <v>0.75</v>
@@ -5700,66 +5700,66 @@
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AL35" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AM35" t="n">
         <v>0.6</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>5.752</v>
+        <v>6.94</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.72</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.747</v>
+        <v>0.718</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.391</v>
+        <v>1.333</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.16</v>
+        <v>0.167</v>
       </c>
       <c r="AU35" t="n">
         <v>1</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.146</v>
+        <v>0.172</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.091</v>
+        <v>0.107</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="36">
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -5796,10 +5796,10 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="L36" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5811,7 +5811,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -5928,40 +5928,40 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>95</v>
+        <v>94.5</v>
       </c>
       <c r="D37" t="n">
-        <v>23.8</v>
+        <v>23.75</v>
       </c>
       <c r="E37" t="n">
-        <v>40.8</v>
+        <v>41.25</v>
       </c>
       <c r="F37" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="G37" t="n">
-        <v>21.2</v>
+        <v>20.75</v>
       </c>
       <c r="H37" t="n">
-        <v>16.8</v>
+        <v>15.5</v>
       </c>
       <c r="I37" t="n">
-        <v>20.4</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="K37" t="n">
-        <v>28.2</v>
+        <v>30</v>
       </c>
       <c r="L37" t="n">
-        <v>9</v>
+        <v>8.25</v>
       </c>
       <c r="M37" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="N37" t="n">
         <v>4</v>
@@ -5970,76 +5970,76 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>10.8</v>
+        <v>11.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R37" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="S37" t="n">
-        <v>20.6</v>
+        <v>20.25</v>
       </c>
       <c r="T37" t="n">
-        <v>572</v>
+        <v>457</v>
       </c>
       <c r="U37" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="V37" t="n">
-        <v>10.6</v>
+        <v>9.25</v>
       </c>
       <c r="W37" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="X37" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="Y37" t="n">
-        <v>11.6</v>
+        <v>12.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>16.4</v>
+        <v>18.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.707</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AB37" t="n">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="AC37" t="n">
-        <v>12.4</v>
+        <v>12.75</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.516</v>
+        <v>0.49</v>
       </c>
       <c r="AE37" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="AF37" t="n">
-        <v>12</v>
+        <v>10.25</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.483</v>
+        <v>0.488</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.643</v>
+        <v>0.6</v>
       </c>
       <c r="AK37" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AL37" t="n">
-        <v>18.4</v>
+        <v>18.25</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.457</v>
+        <v>0.493</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
@@ -6047,34 +6047,34 @@
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>81.776</v>
+        <v>82.11</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.631</v>
+        <v>0.637</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.669</v>
+        <v>0.672</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.162</v>
+        <v>1.151</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.132</v>
+        <v>0.143</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.271</v>
+        <v>0.25</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.37</v>
+        <v>1.277</v>
       </c>
       <c r="AV37" t="n">
         <v>0.2</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.062</v>
+        <v>0.058</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.153</v>
+        <v>0.157</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -6087,118 +6087,118 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="D38" t="n">
+        <v>18</v>
+      </c>
+      <c r="E38" t="n">
+        <v>36</v>
+      </c>
+      <c r="F38" t="n">
+        <v>8</v>
+      </c>
+      <c r="G38" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="H38" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="I38" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="J38" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="K38" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="L38" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="R38" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="S38" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="T38" t="n">
+        <v>288</v>
+      </c>
+      <c r="U38" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="V38" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="W38" t="n">
         <v>5</v>
       </c>
-      <c r="C38" t="n">
-        <v>78</v>
-      </c>
-      <c r="D38" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="E38" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="F38" t="n">
-        <v>9</v>
-      </c>
-      <c r="G38" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="H38" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="I38" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="J38" t="n">
-        <v>14</v>
-      </c>
-      <c r="K38" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="L38" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="M38" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="R38" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S38" t="n">
-        <v>20</v>
-      </c>
-      <c r="T38" t="n">
-        <v>385</v>
-      </c>
-      <c r="U38" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V38" t="n">
-        <v>9</v>
-      </c>
-      <c r="W38" t="n">
-        <v>4</v>
-      </c>
       <c r="X38" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="Z38" t="n">
-        <v>15.2</v>
+        <v>16.75</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.658</v>
+        <v>0.642</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.4</v>
+        <v>8.25</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.571</v>
+        <v>0.606</v>
       </c>
       <c r="AE38" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="AF38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.283</v>
+        <v>0.205</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.423</v>
+        <v>0.316</v>
       </c>
       <c r="AK38" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="AL38" t="n">
         <v>23</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.296</v>
+        <v>0.283</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
@@ -6206,34 +6206,34 @@
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>82.496</v>
+        <v>83.19</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.497</v>
+        <v>0.471</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.542</v>
+        <v>0.519</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.946</v>
+        <v>0.905</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.128</v>
+        <v>0.129</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.229</v>
+        <v>0.239</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.321</v>
+        <v>1.186</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.202</v>
+        <v>0.203</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>

--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Barça.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Barça.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>295.44</v>
+        <v>436.88</v>
       </c>
       <c r="C2" t="n">
-        <v>297.6</v>
+        <v>440.48</v>
       </c>
       <c r="D2" t="n">
-        <v>127.016129032258</v>
+        <v>127.13403559753</v>
       </c>
       <c r="E2" t="n">
-        <v>101.1424731182796</v>
+        <v>105.7936796222303</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6370967741935484</v>
+        <v>0.625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1431007185482889</v>
+        <v>0.1428921368498408</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2894736842105263</v>
+        <v>0.3117647058823529</v>
       </c>
       <c r="I2" t="n">
-        <v>0.25</v>
+        <v>0.2884615384615384</v>
       </c>
       <c r="J2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" t="n">
+        <v>65</v>
+      </c>
+      <c r="L2" t="n">
+        <v>22</v>
+      </c>
+      <c r="M2" t="n">
+        <v>65</v>
+      </c>
+      <c r="N2" t="n">
+        <v>72</v>
+      </c>
+      <c r="O2" t="n">
+        <v>107</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.293956043956044</v>
+      </c>
+      <c r="Q2" t="n">
         <v>32</v>
       </c>
-      <c r="K2" t="n">
-        <v>37</v>
-      </c>
-      <c r="L2" t="n">
-        <v>19</v>
-      </c>
-      <c r="M2" t="n">
-        <v>44</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="R2" t="n">
+        <v>66</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1813186813186813</v>
+      </c>
+      <c r="T2" t="n">
+        <v>32</v>
+      </c>
+      <c r="U2" t="n">
+        <v>64</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1758241758241758</v>
+      </c>
+      <c r="W2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0467032967032967</v>
+      </c>
+      <c r="Z2" t="n">
         <v>50</v>
       </c>
-      <c r="O2" t="n">
-        <v>73</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.2943548387096774</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>25</v>
-      </c>
-      <c r="R2" t="n">
-        <v>51</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.2056451612903226</v>
-      </c>
-      <c r="T2" t="n">
-        <v>20</v>
-      </c>
-      <c r="U2" t="n">
-        <v>41</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.1653225806451613</v>
-      </c>
-      <c r="W2" t="n">
-        <v>6</v>
-      </c>
-      <c r="X2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.04032258064516129</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>36</v>
-      </c>
       <c r="AA2" t="n">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2943548387096774</v>
+        <v>0.3021978021978022</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.684931506849315</v>
+        <v>0.6728971962616822</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4901960784313725</v>
+        <v>0.4848484848484849</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.6</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4931506849315068</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.36986301369863</v>
+        <v>1.345794392523364</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.975609756097561</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.518072289156627</v>
+        <v>1.440944881889764</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7441860465116279</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.121212121212121</v>
+        <v>1.226415094339623</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.727272727272727</v>
+        <v>1.692307692307692</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.276595744680851</v>
+        <v>1.271428571428571</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.276595744680851</v>
+        <v>5.2</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.553191489361702</v>
+        <v>6.471428571428572</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73.86</v>
+        <v>72.81333333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>74.40000000000001</v>
+        <v>73.41333333333334</v>
       </c>
       <c r="D3" t="n">
-        <v>127.016129032258</v>
+        <v>127.1340355975299</v>
       </c>
       <c r="E3" t="n">
-        <v>101.1424731182796</v>
+        <v>105.7936796222303</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6370967741935484</v>
+        <v>0.625</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1431007185482889</v>
+        <v>0.1428921368498408</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2894736842105263</v>
+        <v>0.3117647058823529</v>
       </c>
       <c r="I3" t="n">
-        <v>0.25</v>
+        <v>0.2884615384615384</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="K3" t="n">
-        <v>9.25</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>4.75</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="M3" t="n">
+        <v>10.83333333333333</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" t="n">
+        <v>17.83333333333333</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.2939560439560439</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="R3" t="n">
         <v>11</v>
       </c>
-      <c r="N3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>18.25</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.2943548387096774</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R3" t="n">
-        <v>12.75</v>
-      </c>
       <c r="S3" t="n">
-        <v>0.2056451612903226</v>
+        <v>0.1813186813186813</v>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="U3" t="n">
-        <v>10.25</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1653225806451613</v>
+        <v>0.1758241758241758</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04032258064516129</v>
+        <v>0.0467032967032967</v>
       </c>
       <c r="Z3" t="n">
-        <v>9</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.25</v>
+        <v>18.33333333333333</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2943548387096774</v>
+        <v>0.3021978021978022</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.684931506849315</v>
+        <v>0.6728971962616823</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4901960784313725</v>
+        <v>0.4848484848484848</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.6</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4931506849315068</v>
+        <v>0.4545454545454546</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.36986301369863</v>
+        <v>1.345794392523365</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.975609756097561</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.518072289156627</v>
+        <v>1.440944881889764</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7441860465116279</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.121212121212121</v>
+        <v>1.226415094339623</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.727272727272727</v>
+        <v>1.692307692307692</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.276595744680851</v>
+        <v>1.271428571428572</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.276595744680851</v>
+        <v>5.200000000000001</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.553191489361702</v>
+        <v>6.471428571428572</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>299.76</v>
+        <v>444.08</v>
       </c>
       <c r="C4" t="n">
-        <v>297.6</v>
+        <v>440.48</v>
       </c>
       <c r="D4" t="n">
-        <v>101.1424731182796</v>
+        <v>105.7936796222303</v>
       </c>
       <c r="E4" t="n">
-        <v>127.016129032258</v>
+        <v>127.13403559753</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4973890339425587</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1292222622911408</v>
+        <v>0.131291912418195</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2156862745098039</v>
+        <v>0.2339449541284404</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2392156862745098</v>
+        <v>0.2219321148825065</v>
       </c>
       <c r="J4" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="K4" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M4" t="n">
+        <v>56</v>
+      </c>
+      <c r="N4" t="n">
+        <v>62</v>
+      </c>
+      <c r="O4" t="n">
+        <v>94</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2454308093994778</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>29</v>
+      </c>
+      <c r="R4" t="n">
+        <v>53</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1383812010443864</v>
+      </c>
+      <c r="T4" t="n">
+        <v>23</v>
+      </c>
+      <c r="U4" t="n">
+        <v>74</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1932114882506527</v>
+      </c>
+      <c r="W4" t="n">
+        <v>12</v>
+      </c>
+      <c r="X4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.0783289817232376</v>
+      </c>
+      <c r="Z4" t="n">
         <v>39</v>
       </c>
-      <c r="N4" t="n">
-        <v>43</v>
-      </c>
-      <c r="O4" t="n">
-        <v>67</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.2627450980392157</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>20</v>
-      </c>
-      <c r="R4" t="n">
-        <v>33</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.1294117647058824</v>
-      </c>
-      <c r="T4" t="n">
-        <v>9</v>
-      </c>
-      <c r="U4" t="n">
-        <v>44</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.1725490196078431</v>
-      </c>
-      <c r="W4" t="n">
-        <v>6</v>
-      </c>
-      <c r="X4" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.07450980392156863</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>26</v>
-      </c>
       <c r="AA4" t="n">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3607843137254902</v>
+        <v>0.3446475195822454</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.6417910447761194</v>
+        <v>0.6595744680851063</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.5471698113207547</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2045454545454546</v>
+        <v>0.3108108108108108</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2826086956521739</v>
+        <v>0.2954545454545455</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.283582089552239</v>
+        <v>1.319148936170213</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.6216216216216216</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
+        <v>0.9714285714285714</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.538461538461539</v>
+        <v>1.733333333333333</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.186046511627907</v>
+        <v>1.261538461538461</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.930232558139535</v>
+        <v>5.892307692307693</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.116279069767442</v>
+        <v>7.153846153846154</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.94</v>
+        <v>74.01333333333334</v>
       </c>
       <c r="C5" t="n">
-        <v>74.40000000000001</v>
+        <v>73.41333333333334</v>
       </c>
       <c r="D5" t="n">
-        <v>101.1424731182796</v>
+        <v>105.7936796222303</v>
       </c>
       <c r="E5" t="n">
-        <v>127.016129032258</v>
+        <v>127.1340355975299</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4973890339425587</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1292222622911408</v>
+        <v>0.131291912418195</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2156862745098039</v>
+        <v>0.2339449541284404</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2392156862745098</v>
+        <v>0.2219321148825065</v>
       </c>
       <c r="J5" t="n">
-        <v>11.75</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="L5" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9.333333333333334</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10.33333333333333</v>
+      </c>
+      <c r="O5" t="n">
+        <v>15.66666666666667</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.2454308093994778</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.833333333333333</v>
+      </c>
+      <c r="R5" t="n">
+        <v>8.833333333333334</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1383812010443864</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.833333333333333</v>
+      </c>
+      <c r="U5" t="n">
+        <v>12.33333333333333</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1932114882506527</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
         <v>5</v>
       </c>
-      <c r="M5" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="O5" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.2627450980392157</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.1294117647058824</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>11</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.1725490196078431</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.75</v>
-      </c>
       <c r="Y5" t="n">
-        <v>0.07450980392156863</v>
+        <v>0.0783289817232376</v>
       </c>
       <c r="Z5" t="n">
         <v>6.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3607843137254902</v>
+        <v>0.3446475195822454</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6417910447761194</v>
+        <v>0.6595744680851064</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.5471698113207546</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.2045454545454546</v>
+        <v>0.3108108108108108</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.2826086956521739</v>
+        <v>0.2954545454545455</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.283582089552239</v>
+        <v>1.319148936170213</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.6216216216216216</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
+        <v>0.9714285714285715</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.538461538461539</v>
+        <v>1.733333333333333</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.186046511627907</v>
+        <v>1.261538461538461</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.930232558139535</v>
+        <v>5.892307692307692</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.116279069767442</v>
+        <v>7.153846153846153</v>
       </c>
     </row>
     <row r="7">
@@ -1419,34 +1419,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E8" t="n">
+        <v>36</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>21</v>
+      </c>
+      <c r="H8" t="n">
         <v>11</v>
       </c>
-      <c r="E8" t="n">
-        <v>24</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>13</v>
       </c>
-      <c r="H8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>7</v>
-      </c>
       <c r="J8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
@@ -1455,120 +1455,120 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
+        <v>17</v>
+      </c>
+      <c r="S8" t="n">
         <v>10</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
+        <v>47</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
         <v>6</v>
       </c>
-      <c r="T8" t="n">
-        <v>27</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5</v>
-      </c>
       <c r="AD8" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AE8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK8" t="n">
         <v>8</v>
       </c>
-      <c r="AF8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>4</v>
-      </c>
       <c r="AL8" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.364</v>
+        <v>0.444</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>89:15</t>
+          <t>129:30</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>44.08</v>
+        <v>70.72</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.459</v>
+        <v>0.535</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.499</v>
+        <v>0.574</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.907</v>
+        <v>1.018</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.091</v>
+        <v>0.113</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.162</v>
+        <v>0.193</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.25</v>
+        <v>1.375</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.241</v>
+        <v>0.268</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.047</v>
+        <v>0.033</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.074</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="9">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
         <v>19</v>
@@ -1593,7 +1593,7 @@
         <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1626,7 +1626,7 @@
         <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1686,48 +1686,48 @@
         <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.556</v>
+        <v>0.5</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>60:59</t>
+          <t>84:02</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.731</v>
+        <v>0.679</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.731</v>
+        <v>0.679</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.056</v>
+        <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.278</v>
+        <v>0.263</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.144</v>
+        <v>0.111</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.189</v>
+        <v>0.157</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.031</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="10">
@@ -1737,40 +1737,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
@@ -1785,16 +1785,16 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>27</v>
+      </c>
+      <c r="U10" t="n">
         <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>25</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1806,22 +1806,22 @@
         <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AB10" t="n">
         <v>3</v>
       </c>
       <c r="AC10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1836,10 +1836,10 @@
         <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="AK10" t="n">
         <v>1</v>
@@ -1852,41 +1852,41 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>57:41</t>
+          <t>87:19</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>14.76</v>
+        <v>21.64</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.75</v>
+        <v>0.594</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.723</v>
+        <v>0.617</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.152</v>
+        <v>1.063</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.203</v>
+        <v>0.139</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.125</v>
+        <v>0.121</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.024</v>
+        <v>0.016</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.181</v>
+        <v>0.151</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.023</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="11">
@@ -1896,40 +1896,40 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>54</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" t="n">
+        <v>29</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>14</v>
+      </c>
+      <c r="I11" t="n">
+        <v>16</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>13</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" t="n">
         <v>4</v>
-      </c>
-      <c r="C11" t="n">
-        <v>35</v>
-      </c>
-      <c r="D11" t="n">
-        <v>12</v>
-      </c>
-      <c r="E11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>11</v>
-      </c>
-      <c r="I11" t="n">
-        <v>12</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3</v>
       </c>
       <c r="N11" t="n">
         <v>2</v>
@@ -1944,108 +1944,108 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
+        <v>14</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="n">
+        <v>69</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="AE11" t="n">
         <v>11</v>
       </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="n">
-        <v>41</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="AF11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
         <v>2</v>
       </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>106:54</t>
+        </is>
+      </c>
+      <c r="AO11" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="AU11" t="n">
         <v>2</v>
       </c>
-      <c r="AA11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>74:01</t>
-        </is>
-      </c>
-      <c r="AO11" t="n">
-        <v>29.28</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.195</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.333</v>
-      </c>
       <c r="AV11" t="n">
-        <v>0.193</v>
+        <v>0.188</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.057</v>
+        <v>0.066</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.113</v>
+        <v>0.134</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="12">
@@ -2055,40 +2055,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K12" t="n">
         <v>6</v>
       </c>
-      <c r="J12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4</v>
-      </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2103,16 +2103,16 @@
         <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="U12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V12" t="n">
         <v>5</v>
@@ -2133,22 +2133,22 @@
         <v>1</v>
       </c>
       <c r="AB12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.857</v>
+        <v>0.875</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AH12" t="n">
         <v>2</v>
@@ -2163,48 +2163,48 @@
         <v>6</v>
       </c>
       <c r="AL12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.375</v>
+        <v>0.286</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>69:26</t>
+          <t>93:04</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>39.64</v>
+        <v>48.4</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.719</v>
+        <v>0.615</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.736</v>
+        <v>0.645</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.287</v>
+        <v>1.157</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.126</v>
+        <v>0.103</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.156</v>
+        <v>0.205</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.278</v>
+        <v>0.255</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.06</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.059</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="13">
@@ -2214,40 +2214,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>16</v>
+      </c>
+      <c r="K13" t="n">
+        <v>15</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
         <v>2</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>10</v>
-      </c>
-      <c r="K13" t="n">
-        <v>10</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
@@ -2262,13 +2262,13 @@
         <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="U13" t="n">
         <v>2</v>
@@ -2286,10 +2286,10 @@
         <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AB13" t="n">
         <v>1</v>
@@ -2310,60 +2310,60 @@
         <v>0.667</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK13" t="n">
         <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>71:10</t>
+          <t>106:10</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>20.64</v>
+        <v>27.52</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.583</v>
+        <v>0.472</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.615</v>
+        <v>0.534</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.872</v>
+        <v>0.836</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.291</v>
+        <v>0.218</v>
       </c>
       <c r="AT13" t="n">
         <v>0.333</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.667</v>
+        <v>2.667</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.141</v>
+        <v>0.127</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.147</v>
+        <v>0.156</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.076</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2373,88 +2373,88 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9</v>
+      </c>
+      <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="C14" t="n">
-        <v>10</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>4</v>
-      </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T14" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
         <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>36:15</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>17.64</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.5</v>
+        <v>0.539</v>
       </c>
       <c r="AR14" t="n">
-        <v>1</v>
+        <v>1.077</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.27</v>
+        <v>0.238</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.233</v>
+        <v>0.156</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.347</v>
+        <v>0.273</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -2532,100 +2532,100 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>46</v>
+      </c>
+      <c r="D15" t="n">
+        <v>20</v>
+      </c>
+      <c r="E15" t="n">
+        <v>28</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>11</v>
+      </c>
+      <c r="S15" t="n">
+        <v>9</v>
+      </c>
+      <c r="T15" t="n">
+        <v>63</v>
+      </c>
+      <c r="U15" t="n">
         <v>4</v>
       </c>
-      <c r="C15" t="n">
-        <v>28</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="V15" t="n">
+        <v>11</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z15" t="n">
         <v>12</v>
       </c>
-      <c r="E15" t="n">
-        <v>18</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>15</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>9</v>
-      </c>
-      <c r="S15" t="n">
-        <v>6</v>
-      </c>
-      <c r="T15" t="n">
-        <v>40</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="AB15" t="n">
         <v>8</v>
       </c>
-      <c r="AA15" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>4</v>
-      </c>
       <c r="AC15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.444</v>
+        <v>0.615</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2647,38 +2647,38 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>67:06</t>
+          <t>95:04</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>21.64</v>
+        <v>34.4</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.678</v>
+        <v>0.71</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.294</v>
+        <v>1.337</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.046</v>
+        <v>0.058</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.222</v>
+        <v>0.214</v>
       </c>
       <c r="AU15" t="n">
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.157</v>
+        <v>0.177</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.126</v>
+        <v>0.134</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.234</v>
+        <v>0.232</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -2691,67 +2691,67 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>52</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>12</v>
+      </c>
+      <c r="G16" t="n">
+        <v>21</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12</v>
+      </c>
+      <c r="J16" t="n">
+        <v>14</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>11</v>
+      </c>
+      <c r="R16" t="n">
+        <v>10</v>
+      </c>
+      <c r="S16" t="n">
+        <v>12</v>
+      </c>
+      <c r="T16" t="n">
+        <v>53</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6</v>
+      </c>
+      <c r="V16" t="n">
         <v>4</v>
-      </c>
-      <c r="C16" t="n">
-        <v>26</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>8</v>
-      </c>
-      <c r="G16" t="n">
-        <v>14</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>9</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>5</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>27</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>3</v>
@@ -2760,19 +2760,19 @@
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2781,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -2796,51 +2796,51 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AL16" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AM16" t="n">
         <v>0.571</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>33:25</t>
+          <t>66:05</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>17.88</v>
+        <v>42.28</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.8</v>
+        <v>0.769</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.819</v>
+        <v>0.831</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.454</v>
+        <v>1.23</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.112</v>
+        <v>0.26</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.133</v>
+        <v>0.462</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.5</v>
+        <v>1.273</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.261</v>
+        <v>0.313</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.063</v>
+        <v>0.083</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="17">
@@ -2850,67 +2850,67 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
+        <v>28</v>
+      </c>
+      <c r="F17" t="n">
+        <v>13</v>
+      </c>
+      <c r="G17" t="n">
         <v>21</v>
       </c>
-      <c r="F17" t="n">
+      <c r="H17" t="n">
+        <v>14</v>
+      </c>
+      <c r="I17" t="n">
+        <v>16</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>19</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" t="n">
         <v>7</v>
       </c>
-      <c r="G17" t="n">
-        <v>11</v>
-      </c>
-      <c r="H17" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" t="n">
-        <v>9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>12</v>
+      </c>
+      <c r="R17" t="n">
         <v>13</v>
       </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7</v>
-      </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="T17" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="U17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
         <v>5</v>
@@ -2919,19 +2919,19 @@
         <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.722</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2940,66 +2940,66 @@
         <v>1</v>
       </c>
       <c r="AF17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH17" t="n">
         <v>3</v>
       </c>
-      <c r="AG17" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2</v>
-      </c>
       <c r="AI17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ17" t="n">
         <v>1</v>
       </c>
       <c r="AK17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AL17" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AM17" t="n">
         <v>0.556</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>99:07</t>
+          <t>151:33</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>41.96</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.641</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.667</v>
+        <v>0.723</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.144</v>
+        <v>1.19</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.143</v>
+        <v>0.176</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.219</v>
+        <v>0.286</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.206</v>
+        <v>0.22</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.028</v>
+        <v>0.047</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.017</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="18">
@@ -3009,67 +3009,67 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E18" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
       </c>
       <c r="G18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>23</v>
+      </c>
+      <c r="I18" t="n">
+        <v>26</v>
+      </c>
+      <c r="J18" t="n">
+        <v>12</v>
+      </c>
+      <c r="K18" t="n">
+        <v>21</v>
+      </c>
+      <c r="L18" t="n">
+        <v>11</v>
+      </c>
+      <c r="M18" t="n">
         <v>3</v>
       </c>
-      <c r="H18" t="n">
-        <v>17</v>
-      </c>
-      <c r="I18" t="n">
-        <v>20</v>
-      </c>
-      <c r="J18" t="n">
-        <v>10</v>
-      </c>
-      <c r="K18" t="n">
-        <v>16</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2</v>
-      </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8</v>
+      </c>
+      <c r="R18" t="n">
         <v>7</v>
       </c>
-      <c r="Q18" t="n">
-        <v>7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>5</v>
-      </c>
       <c r="S18" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W18" t="n">
         <v>2</v>
@@ -3078,31 +3078,31 @@
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Z18" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.647</v>
+        <v>0.571</v>
       </c>
       <c r="AB18" t="n">
         <v>2</v>
       </c>
       <c r="AC18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF18" t="n">
         <v>3</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AG18" t="n">
         <v>0.667</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -3117,48 +3117,48 @@
         <v>2</v>
       </c>
       <c r="AL18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.667</v>
+        <v>0.286</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>83:50</t>
+          <t>125:58</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>39.8</v>
+        <v>63.44</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.667</v>
+        <v>0.523</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.747</v>
+        <v>0.622</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.231</v>
+        <v>1.088</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.176</v>
+        <v>0.126</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.708</v>
+        <v>0.523</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.429</v>
+        <v>1.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.231</v>
+        <v>0.247</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.1</v>
+        <v>0.123</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.2</v>
+        <v>0.184</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.082</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D19" t="n">
         <v>12</v>
@@ -3180,10 +3180,10 @@
         <v>19</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H19" t="n">
         <v>4</v>
@@ -3192,16 +3192,16 @@
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L19" t="n">
         <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -3264,60 +3264,60 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>78:26</t>
+          <t>120:56</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>27.76</v>
+        <v>30.76</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.778</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.718</v>
+        <v>0.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.333</v>
+        <v>1.495</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.167</v>
+        <v>0.148</v>
       </c>
       <c r="AU19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.172</v>
+        <v>0.125</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.089</v>
+        <v>0.058</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="20">
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -3354,10 +3354,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3486,153 +3486,153 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>378</v>
+        <v>560</v>
       </c>
       <c r="D21" t="n">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="E21" t="n">
-        <v>165</v>
+        <v>237</v>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="G21" t="n">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="H21" t="n">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="I21" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="J21" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="K21" t="n">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="L21" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="M21" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="N21" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="Q21" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="R21" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="S21" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="T21" t="n">
-        <v>457</v>
+        <v>671</v>
       </c>
       <c r="U21" t="n">
+        <v>50</v>
+      </c>
+      <c r="V21" t="n">
+        <v>65</v>
+      </c>
+      <c r="W21" t="n">
+        <v>22</v>
+      </c>
+      <c r="X21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>72</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>107</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="AB21" t="n">
         <v>32</v>
       </c>
-      <c r="V21" t="n">
-        <v>37</v>
-      </c>
-      <c r="W21" t="n">
-        <v>19</v>
-      </c>
-      <c r="X21" t="n">
+      <c r="AC21" t="n">
+        <v>66</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>64</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH21" t="n">
         <v>11</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AI21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="AK21" t="n">
         <v>50</v>
       </c>
-      <c r="Z21" t="n">
-        <v>73</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>51</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>41</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>36</v>
-      </c>
       <c r="AL21" t="n">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.493</v>
+        <v>0.455</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>800:00</t>
+          <t>1200:00</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>328.44</v>
+        <v>489.88</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.637</v>
+        <v>0.625</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.672</v>
+        <v>0.667</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.151</v>
+        <v>1.143</v>
       </c>
       <c r="AS21" t="n">
         <v>0.143</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.25</v>
+        <v>0.288</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.277</v>
+        <v>1.271</v>
       </c>
       <c r="AV21" t="n">
         <v>0.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.058</v>
+        <v>0.062</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.157</v>
+        <v>0.153</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -3645,153 +3645,153 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>301</v>
+        <v>466</v>
       </c>
       <c r="D22" t="n">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="E22" t="n">
-        <v>144</v>
+        <v>221</v>
       </c>
       <c r="F22" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G22" t="n">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="H22" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="I22" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="J22" t="n">
+        <v>82</v>
+      </c>
+      <c r="K22" t="n">
+        <v>117</v>
+      </c>
+      <c r="L22" t="n">
         <v>51</v>
       </c>
-      <c r="K22" t="n">
-        <v>81</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>33</v>
       </c>
-      <c r="M22" t="n">
-        <v>22</v>
-      </c>
       <c r="N22" t="n">
+        <v>24</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>56</v>
+      </c>
+      <c r="R22" t="n">
+        <v>131</v>
+      </c>
+      <c r="S22" t="n">
+        <v>123</v>
+      </c>
+      <c r="T22" t="n">
+        <v>460</v>
+      </c>
+      <c r="U22" t="n">
+        <v>68</v>
+      </c>
+      <c r="V22" t="n">
+        <v>51</v>
+      </c>
+      <c r="W22" t="n">
+        <v>26</v>
+      </c>
+      <c r="X22" t="n">
         <v>15</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="Y22" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>94</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>53</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>74</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK22" t="n">
         <v>39</v>
       </c>
-      <c r="R22" t="n">
-        <v>82</v>
-      </c>
-      <c r="S22" t="n">
-        <v>79</v>
-      </c>
-      <c r="T22" t="n">
-        <v>288</v>
-      </c>
-      <c r="U22" t="n">
-        <v>47</v>
-      </c>
-      <c r="V22" t="n">
-        <v>33</v>
-      </c>
-      <c r="W22" t="n">
-        <v>20</v>
-      </c>
-      <c r="X22" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>43</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>67</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.642</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>33</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.606</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>26</v>
-      </c>
       <c r="AL22" t="n">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.283</v>
+        <v>0.295</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>800:00</t>
+          <t>1200:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>332.76</v>
+        <v>495.08</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.471</v>
+        <v>0.497</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.519</v>
+        <v>0.542</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.905</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.129</v>
+        <v>0.131</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.239</v>
+        <v>0.222</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.186</v>
+        <v>1.262</v>
       </c>
       <c r="AV22" t="n">
         <v>0.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.043</v>
+        <v>0.047</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.142</v>
+        <v>0.138</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -3861,67 +3861,67 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D24" t="n">
-        <v>2.75</v>
+        <v>2.833</v>
       </c>
       <c r="E24" t="n">
         <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G24" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5</v>
+        <v>1.833</v>
       </c>
       <c r="I24" t="n">
-        <v>1.75</v>
+        <v>2.167</v>
       </c>
       <c r="J24" t="n">
-        <v>2.25</v>
+        <v>1.833</v>
       </c>
       <c r="K24" t="n">
-        <v>1.5</v>
+        <v>1.333</v>
       </c>
       <c r="L24" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5</v>
+        <v>2.833</v>
       </c>
       <c r="S24" t="n">
-        <v>1.5</v>
+        <v>1.667</v>
       </c>
       <c r="T24" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="U24" t="n">
         <v>0.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>1.167</v>
       </c>
       <c r="W24" t="n">
         <v>0.5</v>
@@ -3933,84 +3933,84 @@
         <v>0.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>2.167</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.75</v>
+        <v>4.167</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.533</v>
+        <v>0.52</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AI24" t="n">
         <v>0.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.364</v>
+        <v>0.444</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>22:18</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>11.02</v>
+        <v>11.787</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.459</v>
+        <v>0.535</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.499</v>
+        <v>0.574</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.907</v>
+        <v>1.018</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.091</v>
+        <v>0.113</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.162</v>
+        <v>0.193</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.25</v>
+        <v>1.375</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.241</v>
+        <v>0.268</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.047</v>
+        <v>0.033</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.074</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="25">
@@ -4020,22 +4020,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>4.75</v>
+        <v>3.167</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="F25" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="G25" t="n">
-        <v>2.25</v>
+        <v>1.667</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -4044,55 +4044,55 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>1.167</v>
       </c>
       <c r="K25" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="R25" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="T25" t="n">
         <v>22</v>
       </c>
       <c r="U25" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Z25" t="n">
         <v>0.5</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0.75</v>
       </c>
       <c r="AA25" t="n">
         <v>0.667</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -4125,51 +4125,51 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.25</v>
+        <v>1.667</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.556</v>
+        <v>0.5</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>4.5</v>
+        <v>3.167</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.731</v>
+        <v>0.679</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.731</v>
+        <v>0.679</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.056</v>
+        <v>1</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.278</v>
+        <v>0.263</v>
       </c>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.144</v>
+        <v>0.111</v>
       </c>
       <c r="AW25" t="n">
         <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.189</v>
+        <v>0.157</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.031</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="26">
@@ -4179,91 +4179,91 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>4.25</v>
+        <v>3.833</v>
       </c>
       <c r="D26" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="E26" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="F26" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G26" t="n">
-        <v>1.25</v>
+        <v>1.167</v>
       </c>
       <c r="H26" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
         <v>0.5</v>
       </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.75</v>
-      </c>
       <c r="K26" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
       </c>
       <c r="N26" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>0.5</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0.75</v>
-      </c>
       <c r="Q26" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.667</v>
       </c>
       <c r="S26" t="n">
         <v>0.5</v>
       </c>
       <c r="T26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X26" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4275,60 +4275,60 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AM26" t="n">
         <v>0.5</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>3.69</v>
+        <v>3.607</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.75</v>
+        <v>0.594</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.723</v>
+        <v>0.617</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.152</v>
+        <v>1.063</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.203</v>
+        <v>0.139</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AU26" t="n">
         <v>1</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.125</v>
+        <v>0.121</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.024</v>
+        <v>0.016</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.181</v>
+        <v>0.151</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.023</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="27">
@@ -4338,100 +4338,100 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>3.333</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>4.833</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="H27" t="n">
-        <v>2.75</v>
+        <v>2.333</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>2.667</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>2.167</v>
       </c>
       <c r="L27" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="M27" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="N27" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>0.5</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0.75</v>
-      </c>
       <c r="Q27" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="R27" t="n">
-        <v>2.75</v>
+        <v>2.333</v>
       </c>
       <c r="S27" t="n">
         <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="X27" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="Z27" t="n">
         <v>0.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.25</v>
+        <v>1.167</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.714</v>
+        <v>0.778</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.5</v>
+        <v>1.833</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.75</v>
+        <v>2.833</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.545</v>
+        <v>0.647</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
@@ -4446,48 +4446,48 @@
         <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AM27" t="n">
         <v>0</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>7.32</v>
+        <v>6.84</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.571</v>
+        <v>0.645</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.666</v>
+        <v>0.71</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.195</v>
+        <v>1.316</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.102</v>
+        <v>0.073</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.524</v>
+        <v>0.452</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.333</v>
+        <v>2</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.193</v>
+        <v>0.188</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.057</v>
+        <v>0.066</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.113</v>
+        <v>0.134</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="28">
@@ -4497,40 +4497,40 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" t="n">
+        <v>9.333</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="G28" t="n">
         <v>4</v>
       </c>
-      <c r="C28" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" t="n">
-        <v>4.75</v>
-      </c>
       <c r="H28" t="n">
-        <v>1.25</v>
+        <v>1.333</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>1.667</v>
       </c>
       <c r="J28" t="n">
-        <v>1.75</v>
+        <v>1.833</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4539,25 +4539,25 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="R28" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="T28" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="V28" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -4566,87 +4566,87 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AA28" t="n">
         <v>1</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.5</v>
+        <v>1.167</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.75</v>
+        <v>1.333</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.857</v>
+        <v>0.875</v>
       </c>
       <c r="AE28" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AG28" t="n">
         <v>0.5</v>
       </c>
-      <c r="AF28" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0.667</v>
-      </c>
       <c r="AH28" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AI28" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0.75</v>
       </c>
       <c r="AJ28" t="n">
         <v>0.667</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.375</v>
+        <v>0.286</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>9.91</v>
+        <v>8.067</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.719</v>
+        <v>0.615</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.736</v>
+        <v>0.645</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.287</v>
+        <v>1.157</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.126</v>
+        <v>0.103</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.156</v>
+        <v>0.205</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.278</v>
+        <v>0.255</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.06</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.059</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="29">
@@ -4656,31 +4656,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>4.5</v>
+        <v>3.833</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="E29" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>0.5</v>
       </c>
       <c r="G29" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.333</v>
       </c>
       <c r="J29" t="n">
-        <v>2.5</v>
+        <v>2.667</v>
       </c>
       <c r="K29" t="n">
         <v>2.5</v>
@@ -4689,123 +4689,123 @@
         <v>0.5</v>
       </c>
       <c r="M29" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="T29" t="n">
+        <v>37</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AA29" t="n">
         <v>0.25</v>
       </c>
-      <c r="N29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T29" t="n">
-        <v>27</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1</v>
-      </c>
       <c r="AB29" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="AD29" t="n">
         <v>0.2</v>
       </c>
       <c r="AE29" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF29" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0.75</v>
       </c>
       <c r="AG29" t="n">
         <v>0.667</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>5.16</v>
+        <v>4.587</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.583</v>
+        <v>0.472</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.615</v>
+        <v>0.534</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.872</v>
+        <v>0.836</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.291</v>
+        <v>0.218</v>
       </c>
       <c r="AT29" t="n">
         <v>0.333</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.667</v>
+        <v>2.667</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.141</v>
+        <v>0.127</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.147</v>
+        <v>0.156</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.076</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -4815,13 +4815,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>2.5</v>
+        <v>3.167</v>
       </c>
       <c r="D30" t="n">
-        <v>1.25</v>
+        <v>1.333</v>
       </c>
       <c r="E30" t="n">
         <v>2.5</v>
@@ -4833,10 +4833,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4845,13 +4845,13 @@
         <v>1.5</v>
       </c>
       <c r="L30" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="N30" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4863,40 +4863,40 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="S30" t="n">
-        <v>0.75</v>
+        <v>1.167</v>
       </c>
       <c r="T30" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="V30" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>1.333</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.5</v>
+        <v>2.333</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4930,38 +4930,38 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>04:31</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.5</v>
+        <v>0.539</v>
       </c>
       <c r="AR30" t="n">
-        <v>1</v>
+        <v>1.077</v>
       </c>
       <c r="AS30" t="n">
         <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AU30" t="n">
         <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.27</v>
+        <v>0.238</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.233</v>
+        <v>0.156</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.347</v>
+        <v>0.273</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -4974,16 +4974,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>7.667</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>3.333</v>
       </c>
       <c r="E31" t="n">
-        <v>4.5</v>
+        <v>4.667</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4995,19 +4995,19 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>1.667</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>3.75</v>
+        <v>3.333</v>
       </c>
       <c r="L31" t="n">
         <v>1.5</v>
       </c>
       <c r="M31" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="N31" t="n">
         <v>0.5</v>
@@ -5016,25 +5016,25 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="R31" t="n">
-        <v>2.25</v>
+        <v>1.833</v>
       </c>
       <c r="S31" t="n">
         <v>1.5</v>
       </c>
       <c r="T31" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="U31" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>1.833</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -5043,31 +5043,31 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.75</v>
+        <v>1.833</v>
       </c>
       <c r="Z31" t="n">
         <v>2</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.875</v>
+        <v>0.917</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>2.167</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.444</v>
+        <v>0.615</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
@@ -5089,38 +5089,38 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>5.41</v>
+        <v>5.733</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.678</v>
+        <v>0.71</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.294</v>
+        <v>1.337</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.046</v>
+        <v>0.058</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.222</v>
+        <v>0.214</v>
       </c>
       <c r="AU31" t="n">
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.157</v>
+        <v>0.177</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.126</v>
+        <v>0.134</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.234</v>
+        <v>0.232</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -5133,16 +5133,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>6.5</v>
+        <v>8.667</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="E32" t="n">
-        <v>0.25</v>
+        <v>0.833</v>
       </c>
       <c r="F32" t="n">
         <v>2</v>
@@ -5151,70 +5151,70 @@
         <v>3.5</v>
       </c>
       <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>0.5</v>
       </c>
-      <c r="I32" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>53</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="W32" t="n">
         <v>0.5</v>
       </c>
-      <c r="J32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1</v>
-      </c>
-      <c r="T32" t="n">
-        <v>27</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.75</v>
-      </c>
       <c r="X32" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -5223,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -5248,41 +5248,41 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>4.47</v>
+        <v>7.047</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.8</v>
+        <v>0.769</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.819</v>
+        <v>0.831</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.454</v>
+        <v>1.23</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.112</v>
+        <v>0.26</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.133</v>
+        <v>0.462</v>
       </c>
       <c r="AU32" t="n">
-        <v>4.5</v>
+        <v>1.273</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.261</v>
+        <v>0.313</v>
       </c>
       <c r="AW32" t="n">
         <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.063</v>
+        <v>0.083</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="33">
@@ -5292,40 +5292,40 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.5</v>
+        <v>2.333</v>
       </c>
       <c r="E33" t="n">
-        <v>5.25</v>
+        <v>4.667</v>
       </c>
       <c r="F33" t="n">
-        <v>1.75</v>
+        <v>2.167</v>
       </c>
       <c r="G33" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="H33" t="n">
-        <v>1.75</v>
+        <v>2.333</v>
       </c>
       <c r="I33" t="n">
-        <v>2.25</v>
+        <v>2.667</v>
       </c>
       <c r="J33" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>3.25</v>
+        <v>3.167</v>
       </c>
       <c r="L33" t="n">
-        <v>0.5</v>
+        <v>0.833</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>1.167</v>
       </c>
       <c r="N33" t="n">
         <v>0.5</v>
@@ -5334,58 +5334,58 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.75</v>
+        <v>2.167</v>
       </c>
       <c r="S33" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T33" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="U33" t="n">
-        <v>2.25</v>
+        <v>2.167</v>
       </c>
       <c r="V33" t="n">
-        <v>1.5</v>
+        <v>1.333</v>
       </c>
       <c r="W33" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="X33" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.25</v>
+        <v>2.167</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.722</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
       </c>
       <c r="AE33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AG33" t="n">
         <v>0.25</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.333</v>
       </c>
       <c r="AH33" t="n">
         <v>0.5</v>
@@ -5397,51 +5397,51 @@
         <v>1</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.25</v>
+        <v>1.667</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AM33" t="n">
         <v>0.556</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>24:46</t>
+          <t>25:15</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>10.49</v>
+        <v>11.34</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.641</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.667</v>
+        <v>0.723</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.144</v>
+        <v>1.19</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.143</v>
+        <v>0.176</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.219</v>
+        <v>0.286</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.206</v>
+        <v>0.22</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.028</v>
+        <v>0.047</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.017</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="34">
@@ -5451,101 +5451,101 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>12.25</v>
+        <v>11.5</v>
       </c>
       <c r="D34" t="n">
-        <v>3.25</v>
+        <v>3.333</v>
       </c>
       <c r="E34" t="n">
-        <v>5.25</v>
+        <v>6.167</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="G34" t="n">
-        <v>0.75</v>
+        <v>1.167</v>
       </c>
       <c r="H34" t="n">
-        <v>4.25</v>
+        <v>3.833</v>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>4.333</v>
       </c>
       <c r="J34" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="L34" t="n">
-        <v>1.5</v>
+        <v>1.833</v>
       </c>
       <c r="M34" t="n">
         <v>0.5</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.75</v>
+        <v>1.333</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.75</v>
+        <v>1.333</v>
       </c>
       <c r="R34" t="n">
-        <v>1.25</v>
+        <v>1.167</v>
       </c>
       <c r="S34" t="n">
-        <v>4.25</v>
+        <v>4.167</v>
       </c>
       <c r="T34" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="U34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF34" t="n">
         <v>0.5</v>
       </c>
-      <c r="V34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AD34" t="n">
+      <c r="AG34" t="n">
         <v>0.667</v>
       </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
       <c r="AH34" t="n">
         <v>0</v>
       </c>
@@ -5556,51 +5556,51 @@
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.75</v>
+        <v>1.167</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.667</v>
+        <v>0.286</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>9.949999999999999</v>
+        <v>10.573</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.667</v>
+        <v>0.523</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.747</v>
+        <v>0.622</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.231</v>
+        <v>1.088</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.176</v>
+        <v>0.126</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.708</v>
+        <v>0.523</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.429</v>
+        <v>1.5</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.231</v>
+        <v>0.247</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.1</v>
+        <v>0.123</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.2</v>
+        <v>0.184</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.082</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -5610,37 +5610,37 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>9.25</v>
+        <v>7.667</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>4.75</v>
+        <v>3.167</v>
       </c>
       <c r="F35" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>1.25</v>
+        <v>1.333</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="J35" t="n">
         <v>0.5</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="L35" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="M35" t="n">
         <v>0.5</v>
@@ -5652,46 +5652,46 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="R35" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="T35" t="n">
+        <v>53</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.5</v>
       </c>
-      <c r="S35" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T35" t="n">
-        <v>40</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Z35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA35" t="n">
         <v>0.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AD35" t="n">
         <v>0.75</v>
@@ -5700,66 +5700,66 @@
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>6.94</v>
+        <v>5.127</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.778</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.718</v>
+        <v>0.8</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.333</v>
+        <v>1.495</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.167</v>
+        <v>0.148</v>
       </c>
       <c r="AU35" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.172</v>
+        <v>0.125</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.089</v>
+        <v>0.058</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="36">
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -5796,10 +5796,10 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>2.75</v>
+        <v>2.667</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5811,7 +5811,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -5928,118 +5928,118 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>94.5</v>
+        <v>93.333</v>
       </c>
       <c r="D37" t="n">
-        <v>23.75</v>
+        <v>22.667</v>
       </c>
       <c r="E37" t="n">
-        <v>41.25</v>
+        <v>39.5</v>
       </c>
       <c r="F37" t="n">
-        <v>10.5</v>
+        <v>10.167</v>
       </c>
       <c r="G37" t="n">
-        <v>20.75</v>
+        <v>21.167</v>
       </c>
       <c r="H37" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>21.167</v>
       </c>
       <c r="J37" t="n">
-        <v>15</v>
+        <v>14.833</v>
       </c>
       <c r="K37" t="n">
-        <v>30</v>
+        <v>27.833</v>
       </c>
       <c r="L37" t="n">
-        <v>8.25</v>
+        <v>8.833</v>
       </c>
       <c r="M37" t="n">
-        <v>5.25</v>
+        <v>5.833</v>
       </c>
       <c r="N37" t="n">
-        <v>4</v>
+        <v>4.167</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>11.75</v>
+        <v>11.667</v>
       </c>
       <c r="Q37" t="n">
+        <v>10.833</v>
+      </c>
+      <c r="R37" t="n">
+        <v>20.667</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20.833</v>
+      </c>
+      <c r="T37" t="n">
+        <v>671</v>
+      </c>
+      <c r="U37" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="V37" t="n">
+        <v>10.833</v>
+      </c>
+      <c r="W37" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>17.833</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="AC37" t="n">
         <v>11</v>
       </c>
-      <c r="R37" t="n">
-        <v>20</v>
-      </c>
-      <c r="S37" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="T37" t="n">
-        <v>457</v>
-      </c>
-      <c r="U37" t="n">
-        <v>8</v>
-      </c>
-      <c r="V37" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="W37" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>18.25</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>12.75</v>
-      </c>
       <c r="AD37" t="n">
-        <v>0.49</v>
+        <v>0.485</v>
       </c>
       <c r="AE37" t="n">
-        <v>5</v>
+        <v>5.333</v>
       </c>
       <c r="AF37" t="n">
-        <v>10.25</v>
+        <v>10.667</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.488</v>
+        <v>0.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.5</v>
+        <v>1.833</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.5</v>
+        <v>2.833</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.6</v>
+        <v>0.647</v>
       </c>
       <c r="AK37" t="n">
-        <v>9</v>
+        <v>8.333</v>
       </c>
       <c r="AL37" t="n">
-        <v>18.25</v>
+        <v>18.333</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.493</v>
+        <v>0.455</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
@@ -6047,34 +6047,34 @@
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>82.11</v>
+        <v>81.64700000000001</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.637</v>
+        <v>0.625</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.672</v>
+        <v>0.667</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.151</v>
+        <v>1.143</v>
       </c>
       <c r="AS37" t="n">
         <v>0.143</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.25</v>
+        <v>0.288</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.277</v>
+        <v>1.271</v>
       </c>
       <c r="AV37" t="n">
         <v>0.2</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.058</v>
+        <v>0.062</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.157</v>
+        <v>0.153</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -6087,118 +6087,118 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>75.25</v>
+        <v>77.667</v>
       </c>
       <c r="D38" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E38" t="n">
-        <v>36</v>
+        <v>36.833</v>
       </c>
       <c r="F38" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G38" t="n">
-        <v>27.75</v>
+        <v>27</v>
       </c>
       <c r="H38" t="n">
-        <v>15.25</v>
+        <v>14.167</v>
       </c>
       <c r="I38" t="n">
-        <v>19.75</v>
+        <v>17.833</v>
       </c>
       <c r="J38" t="n">
-        <v>12.75</v>
+        <v>13.667</v>
       </c>
       <c r="K38" t="n">
-        <v>20.25</v>
+        <v>19.5</v>
       </c>
       <c r="L38" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="M38" t="n">
         <v>5.5</v>
       </c>
       <c r="N38" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>10.75</v>
+        <v>10.833</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.75</v>
+        <v>9.333</v>
       </c>
       <c r="R38" t="n">
+        <v>21.833</v>
+      </c>
+      <c r="S38" t="n">
         <v>20.5</v>
       </c>
-      <c r="S38" t="n">
-        <v>19.75</v>
-      </c>
       <c r="T38" t="n">
-        <v>288</v>
+        <v>460</v>
       </c>
       <c r="U38" t="n">
-        <v>11.75</v>
+        <v>11.333</v>
       </c>
       <c r="V38" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="W38" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>10.333</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>15.667</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>4.833</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.833</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>12.333</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI38" t="n">
         <v>5</v>
       </c>
-      <c r="X38" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.642</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0.606</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>4.75</v>
-      </c>
       <c r="AJ38" t="n">
-        <v>0.316</v>
+        <v>0.4</v>
       </c>
       <c r="AK38" t="n">
         <v>6.5</v>
       </c>
       <c r="AL38" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.283</v>
+        <v>0.295</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
@@ -6206,34 +6206,34 @@
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>83.19</v>
+        <v>82.51300000000001</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.471</v>
+        <v>0.497</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.519</v>
+        <v>0.542</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.905</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.129</v>
+        <v>0.131</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.239</v>
+        <v>0.222</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.186</v>
+        <v>1.262</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.203</v>
+        <v>0.202</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.106</v>
+        <v>0.107</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>

--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Barça.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Barça.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>436.88</v>
+        <v>524.12</v>
       </c>
       <c r="C2" t="n">
-        <v>440.48</v>
+        <v>527.38</v>
       </c>
       <c r="D2" t="n">
-        <v>127.13403559753</v>
+        <v>127.6119685994918</v>
       </c>
       <c r="E2" t="n">
-        <v>105.7936796222303</v>
+        <v>109.5983920512723</v>
       </c>
       <c r="F2" t="n">
-        <v>0.625</v>
+        <v>0.6309794988610479</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1428921368498408</v>
+        <v>0.1384331419196062</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3117647058823529</v>
+        <v>0.2946859903381642</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2884615384615384</v>
+        <v>0.2710706150341686</v>
       </c>
       <c r="J2" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="K2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="L2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="N2" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="O2" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="P2" t="n">
-        <v>0.293956043956044</v>
+        <v>0.2847380410022779</v>
       </c>
       <c r="Q2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R2" t="n">
+        <v>80</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1822323462414579</v>
+      </c>
+      <c r="T2" t="n">
+        <v>34</v>
+      </c>
+      <c r="U2" t="n">
+        <v>69</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1571753986332574</v>
+      </c>
+      <c r="W2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X2" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.05239179954441914</v>
+      </c>
+      <c r="Z2" t="n">
         <v>66</v>
       </c>
-      <c r="S2" t="n">
-        <v>0.1813186813186813</v>
-      </c>
-      <c r="T2" t="n">
-        <v>32</v>
-      </c>
-      <c r="U2" t="n">
-        <v>64</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.1758241758241758</v>
-      </c>
-      <c r="W2" t="n">
-        <v>11</v>
-      </c>
-      <c r="X2" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0467032967032967</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>50</v>
-      </c>
       <c r="AA2" t="n">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3021978021978022</v>
+        <v>0.3234624145785877</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.6728971962616822</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4848484848484849</v>
+        <v>0.4625</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.5</v>
+        <v>0.4927536231884058</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4647887323943662</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.345794392523364</v>
+        <v>1.376</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>0.9855072463768116</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.440944881889764</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8428571428571429</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.226415094339623</v>
+        <v>1.147540983606557</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.692307692307692</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.271428571428571</v>
+        <v>1.37037037037037</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.2</v>
+        <v>5.419753086419753</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.471428571428572</v>
+        <v>6.790123456790123</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72.81333333333333</v>
+        <v>74.87428571428572</v>
       </c>
       <c r="C3" t="n">
-        <v>73.41333333333334</v>
+        <v>75.34</v>
       </c>
       <c r="D3" t="n">
-        <v>127.1340355975299</v>
+        <v>127.6119685994918</v>
       </c>
       <c r="E3" t="n">
-        <v>105.7936796222303</v>
+        <v>109.5983920512723</v>
       </c>
       <c r="F3" t="n">
-        <v>0.625</v>
+        <v>0.6309794988610478</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1428921368498408</v>
+        <v>0.1384331419196062</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3117647058823529</v>
+        <v>0.2946859903381642</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2884615384615384</v>
+        <v>0.2710706150341685</v>
       </c>
       <c r="J3" t="n">
-        <v>8.333333333333334</v>
+        <v>8.428571428571429</v>
       </c>
       <c r="K3" t="n">
-        <v>10.83333333333333</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>3.666666666666667</v>
+        <v>3.428571428571428</v>
       </c>
       <c r="M3" t="n">
-        <v>10.83333333333333</v>
+        <v>10.71428571428571</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>12.28571428571429</v>
       </c>
       <c r="O3" t="n">
-        <v>17.83333333333333</v>
+        <v>17.85714285714286</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2939560439560439</v>
+        <v>0.2847380410022779</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.333333333333333</v>
+        <v>5.285714285714286</v>
       </c>
       <c r="R3" t="n">
-        <v>11</v>
+        <v>11.42857142857143</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1813186813186813</v>
+        <v>0.1822323462414578</v>
       </c>
       <c r="T3" t="n">
-        <v>5.333333333333333</v>
+        <v>4.857142857142857</v>
       </c>
       <c r="U3" t="n">
-        <v>10.66666666666667</v>
+        <v>9.857142857142858</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1758241758241758</v>
+        <v>0.1571753986332574</v>
       </c>
       <c r="W3" t="n">
-        <v>1.833333333333333</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>2.833333333333333</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0467032967032967</v>
+        <v>0.05239179954441912</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.333333333333334</v>
+        <v>9.428571428571429</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.33333333333333</v>
+        <v>20.28571428571428</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3021978021978022</v>
+        <v>0.3234624145785877</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.6728971962616823</v>
+        <v>0.6880000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.4625</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5</v>
+        <v>0.4927536231884057</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.6470588235294117</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4545454545454546</v>
+        <v>0.4647887323943662</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.345794392523365</v>
+        <v>1.376</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>0.9855072463768114</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.440944881889764</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8428571428571429</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.226415094339623</v>
+        <v>1.147540983606558</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.692307692307692</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.271428571428572</v>
+        <v>1.37037037037037</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.200000000000001</v>
+        <v>5.419753086419754</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.471428571428572</v>
+        <v>6.790123456790124</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>444.08</v>
+        <v>530.6400000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>440.48</v>
+        <v>527.38</v>
       </c>
       <c r="D4" t="n">
-        <v>105.7936796222303</v>
+        <v>109.5983920512723</v>
       </c>
       <c r="E4" t="n">
-        <v>127.13403559753</v>
+        <v>127.6119685994918</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4973890339425587</v>
+        <v>0.5096774193548387</v>
       </c>
       <c r="G4" t="n">
-        <v>0.131291912418195</v>
+        <v>0.1181155507559395</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2339449541284404</v>
+        <v>0.2450592885375494</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2219321148825065</v>
+        <v>0.2236559139784946</v>
       </c>
       <c r="J4" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="K4" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M4" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="N4" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="O4" t="n">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2454308093994778</v>
+        <v>0.2709677419354839</v>
       </c>
       <c r="Q4" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="R4" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1383812010443864</v>
+        <v>0.1483870967741935</v>
       </c>
       <c r="T4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="U4" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1932114882506527</v>
+        <v>0.1763440860215054</v>
       </c>
       <c r="W4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0783289817232376</v>
+        <v>0.07311827956989247</v>
       </c>
       <c r="Z4" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AA4" t="n">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3446475195822454</v>
+        <v>0.3311827956989247</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.6595744680851063</v>
+        <v>0.6825396825396826</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5471698113207547</v>
+        <v>0.5362318840579711</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3108108108108108</v>
+        <v>0.3292682926829268</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4</v>
+        <v>0.3823529411764706</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2954545454545455</v>
+        <v>0.2922077922077922</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.319148936170213</v>
+        <v>1.365079365079365</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6216216216216216</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.925531914893617</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.9714285714285714</v>
+        <v>0.9382716049382716</v>
       </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>1.016129032258065</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.733333333333333</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.261538461538461</v>
+        <v>1.442857142857143</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.892307692307693</v>
+        <v>6.642857142857143</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.153846153846154</v>
+        <v>8.085714285714285</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.01333333333334</v>
+        <v>75.8057142857143</v>
       </c>
       <c r="C5" t="n">
-        <v>73.41333333333334</v>
+        <v>75.34</v>
       </c>
       <c r="D5" t="n">
-        <v>105.7936796222303</v>
+        <v>109.5983920512723</v>
       </c>
       <c r="E5" t="n">
-        <v>127.1340355975299</v>
+        <v>127.6119685994918</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4973890339425587</v>
+        <v>0.5096774193548388</v>
       </c>
       <c r="G5" t="n">
-        <v>0.131291912418195</v>
+        <v>0.1181155507559395</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2339449541284404</v>
+        <v>0.2450592885375494</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2219321148825065</v>
+        <v>0.2236559139784946</v>
       </c>
       <c r="J5" t="n">
-        <v>11.33333333333333</v>
+        <v>10.85714285714286</v>
       </c>
       <c r="K5" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>4.333333333333333</v>
+        <v>5.142857142857143</v>
       </c>
       <c r="M5" t="n">
-        <v>9.333333333333334</v>
+        <v>8.714285714285714</v>
       </c>
       <c r="N5" t="n">
-        <v>10.33333333333333</v>
+        <v>12.28571428571429</v>
       </c>
       <c r="O5" t="n">
-        <v>15.66666666666667</v>
+        <v>18</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2454308093994778</v>
+        <v>0.2709677419354838</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.833333333333333</v>
+        <v>5.285714285714286</v>
       </c>
       <c r="R5" t="n">
-        <v>8.833333333333334</v>
+        <v>9.857142857142858</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1383812010443864</v>
+        <v>0.1483870967741935</v>
       </c>
       <c r="T5" t="n">
-        <v>3.833333333333333</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="U5" t="n">
-        <v>12.33333333333333</v>
+        <v>11.71428571428571</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1932114882506527</v>
+        <v>0.1763440860215054</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>4.857142857142857</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0783289817232376</v>
+        <v>0.07311827956989246</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.5</v>
+        <v>6.428571428571429</v>
       </c>
       <c r="AA5" t="n">
         <v>22</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3446475195822454</v>
+        <v>0.3311827956989247</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6595744680851064</v>
+        <v>0.6825396825396826</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5471698113207546</v>
+        <v>0.536231884057971</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3108108108108108</v>
+        <v>0.3292682926829268</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4</v>
+        <v>0.3823529411764706</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.2954545454545455</v>
+        <v>0.2922077922077922</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.319148936170213</v>
+        <v>1.365079365079365</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6216216216216216</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9255319148936172</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.9714285714285715</v>
+        <v>0.9382716049382717</v>
       </c>
       <c r="AL5" t="n">
-        <v>1</v>
+        <v>1.016129032258065</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.733333333333333</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.261538461538461</v>
+        <v>1.442857142857143</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.892307692307692</v>
+        <v>6.642857142857143</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.153846153846153</v>
+        <v>8.085714285714285</v>
       </c>
     </row>
     <row r="7">
@@ -1419,34 +1419,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
+        <v>11</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I8" t="n">
+        <v>15</v>
+      </c>
+      <c r="J8" t="n">
+        <v>15</v>
+      </c>
+      <c r="K8" t="n">
         <v>9</v>
-      </c>
-      <c r="G8" t="n">
-        <v>21</v>
-      </c>
-      <c r="H8" t="n">
-        <v>11</v>
-      </c>
-      <c r="I8" t="n">
-        <v>13</v>
-      </c>
-      <c r="J8" t="n">
-        <v>11</v>
-      </c>
-      <c r="K8" t="n">
-        <v>8</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
@@ -1461,22 +1461,22 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V8" t="n">
         <v>7</v>
@@ -1488,87 +1488,87 @@
         <v>3</v>
       </c>
       <c r="Y8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6</v>
+        <v>0.714</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.167</v>
+        <v>0.222</v>
       </c>
       <c r="AE8" t="n">
         <v>13</v>
       </c>
       <c r="AF8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.444</v>
+        <v>0.476</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>129:30</t>
+          <t>161:29</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>70.72</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.535</v>
+        <v>0.545</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.574</v>
+        <v>0.584</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.018</v>
+        <v>1.029</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.113</v>
+        <v>0.12</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.193</v>
+        <v>0.194</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.375</v>
+        <v>1.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.268</v>
+        <v>0.252</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.033</v>
+        <v>0.026</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.068</v>
+        <v>0.063</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.064</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="9">
@@ -1578,22 +1578,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1620,13 +1620,13 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1659,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1683,51 +1683,51 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AM9" t="n">
         <v>0.5</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>84:02</t>
+          <t>95:55</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.679</v>
+        <v>0.647</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.679</v>
+        <v>0.647</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>0.957</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.263</v>
+        <v>0.261</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.111</v>
+        <v>0.117</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.157</v>
+        <v>0.153</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.037</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="10">
@@ -1737,34 +1737,34 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" t="n">
         <v>6</v>
       </c>
-      <c r="C10" t="n">
-        <v>23</v>
-      </c>
-      <c r="D10" t="n">
-        <v>5</v>
-      </c>
       <c r="E10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="n">
         <v>9</v>
       </c>
-      <c r="F10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" t="n">
-        <v>7</v>
-      </c>
       <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="n">
         <v>4</v>
       </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -1785,13 +1785,13 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="U10" t="n">
         <v>2</v>
@@ -1806,22 +1806,22 @@
         <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.667</v>
+        <v>0.75</v>
       </c>
       <c r="AB10" t="n">
         <v>3</v>
       </c>
       <c r="AC10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1836,57 +1836,57 @@
         <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>87:19</t>
+          <t>103:10</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>21.64</v>
+        <v>26.52</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.594</v>
+        <v>0.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.617</v>
+        <v>0.638</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.063</v>
+        <v>1.131</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.139</v>
+        <v>0.113</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.121</v>
+        <v>0.125</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.151</v>
+        <v>0.142</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="11">
@@ -1896,16 +1896,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1914,25 +1914,25 @@
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
         <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
         <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1944,13 +1944,13 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T11" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
         <v>4</v>
@@ -1965,31 +1965,31 @@
         <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.778</v>
+        <v>0.727</v>
       </c>
       <c r="AE11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.647</v>
+        <v>0.632</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -2011,41 +2011,41 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>106:54</t>
+          <t>135:17</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>41.04</v>
+        <v>47.92</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.645</v>
+        <v>0.622</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.316</v>
+        <v>1.294</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.073</v>
+        <v>0.063</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.452</v>
+        <v>0.432</v>
       </c>
       <c r="AU11" t="n">
         <v>2</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.188</v>
+        <v>0.173</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.066</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.134</v>
+        <v>0.142</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.034</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="12">
@@ -2055,22 +2055,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H12" t="n">
         <v>8</v>
@@ -2088,7 +2088,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2103,19 +2103,19 @@
         <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="U12" t="n">
         <v>10</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2136,19 +2136,19 @@
         <v>7</v>
       </c>
       <c r="AC12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.875</v>
+        <v>0.778</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AH12" t="n">
         <v>2</v>
@@ -2160,51 +2160,51 @@
         <v>0.667</v>
       </c>
       <c r="AK12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AL12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.286</v>
+        <v>0.346</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>93:04</t>
+          <t>118:40</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>48.4</v>
+        <v>55.4</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.645</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.157</v>
+        <v>1.173</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.103</v>
+        <v>0.09</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.205</v>
+        <v>0.174</v>
       </c>
       <c r="AU12" t="n">
         <v>2.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.255</v>
+        <v>0.227</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.057</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.062</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="13">
@@ -2354,16 +2354,16 @@
         <v>2.667</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.127</v>
+        <v>0.126</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.156</v>
+        <v>0.159</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>19</v>
@@ -2382,7 +2382,7 @@
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2424,10 +2424,10 @@
         <v>5</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
@@ -2445,10 +2445,10 @@
         <v>8</v>
       </c>
       <c r="Z14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.571</v>
+        <v>0.533</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>36:15</t>
+          <t>51:12</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>17.64</v>
+        <v>18.64</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.539</v>
+        <v>0.51</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.077</v>
+        <v>1.019</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.238</v>
+        <v>0.177</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.156</v>
+        <v>0.108</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.273</v>
+        <v>0.198</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -2528,20 +2528,20 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>#19 Y. FALL</t>
+          <t>#17 J. NÚÑEZ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2550,241 +2550,241 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>04:03</t>
+        </is>
+      </c>
+      <c r="AO15" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>11</v>
-      </c>
-      <c r="S15" t="n">
-        <v>9</v>
-      </c>
-      <c r="T15" t="n">
-        <v>63</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>11</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>95:04</t>
-        </is>
-      </c>
-      <c r="AO15" t="n">
-        <v>34.4</v>
-      </c>
       <c r="AP15" t="n">
-        <v>0.714</v>
+        <v>0.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.337</v>
+        <v>1</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.058</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.177</v>
+        <v>0.241</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.134</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.232</v>
+        <v>0.278</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>#20 N. LAPROVITTOLA</t>
+          <t>#19 Y. FALL</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" t="n">
+        <v>46</v>
+      </c>
+      <c r="D16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" t="n">
+        <v>28</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>52</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>12</v>
-      </c>
-      <c r="G16" t="n">
-        <v>21</v>
-      </c>
-      <c r="H16" t="n">
-        <v>12</v>
       </c>
       <c r="I16" t="n">
         <v>12</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
         <v>3</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>12</v>
+      </c>
+      <c r="S16" t="n">
         <v>11</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="T16" t="n">
+        <v>66</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
+      </c>
+      <c r="V16" t="n">
         <v>11</v>
       </c>
-      <c r="R16" t="n">
-        <v>10</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z16" t="n">
         <v>12</v>
       </c>
-      <c r="T16" t="n">
-        <v>53</v>
-      </c>
-      <c r="U16" t="n">
-        <v>6</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4</v>
-      </c>
-      <c r="W16" t="n">
+      <c r="AA16" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
         <v>3</v>
       </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1</v>
-      </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -2796,598 +2796,598 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>66:05</t>
+          <t>101:41</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>42.28</v>
+        <v>36.28</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.769</v>
+        <v>0.714</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.831</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.23</v>
+        <v>1.268</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.26</v>
+        <v>0.083</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.462</v>
+        <v>0.214</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.273</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.313</v>
+        <v>0.174</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.083</v>
+        <v>0.255</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>#21 W. CLYBURN</t>
+          <t>#20 N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G17" t="n">
+        <v>28</v>
+      </c>
+      <c r="H17" t="n">
+        <v>16</v>
+      </c>
+      <c r="I17" t="n">
+        <v>18</v>
+      </c>
+      <c r="J17" t="n">
+        <v>21</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>14</v>
       </c>
-      <c r="E17" t="n">
-        <v>28</v>
-      </c>
-      <c r="F17" t="n">
-        <v>13</v>
-      </c>
-      <c r="G17" t="n">
-        <v>21</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="Q17" t="n">
         <v>14</v>
-      </c>
-      <c r="I17" t="n">
-        <v>16</v>
-      </c>
-      <c r="J17" t="n">
-        <v>6</v>
-      </c>
-      <c r="K17" t="n">
-        <v>19</v>
-      </c>
-      <c r="L17" t="n">
-        <v>5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>7</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>12</v>
       </c>
       <c r="R17" t="n">
         <v>13</v>
       </c>
       <c r="S17" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="T17" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2</v>
       </c>
-      <c r="Y17" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>6</v>
-      </c>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ17" t="n">
         <v>1</v>
       </c>
       <c r="AK17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AL17" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AM17" t="n">
         <v>0.556</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>151:33</t>
+          <t>104:49</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>68.04000000000001</v>
+        <v>56.92</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.723</v>
+        <v>0.839</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.19</v>
+        <v>1.265</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.176</v>
+        <v>0.246</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.286</v>
+        <v>0.457</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.22</v>
+        <v>0.265</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.138</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.035</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>#23 T. SHENGELIA</t>
+          <t>#21 W. CLYBURN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="D18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>30</v>
+      </c>
+      <c r="F18" t="n">
+        <v>18</v>
+      </c>
+      <c r="G18" t="n">
+        <v>34</v>
+      </c>
+      <c r="H18" t="n">
+        <v>16</v>
+      </c>
+      <c r="I18" t="n">
+        <v>19</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>22</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>8</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>13</v>
+      </c>
+      <c r="R18" t="n">
+        <v>15</v>
+      </c>
+      <c r="S18" t="n">
+        <v>24</v>
+      </c>
+      <c r="T18" t="n">
+        <v>111</v>
+      </c>
+      <c r="U18" t="n">
+        <v>18</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z18" t="n">
         <v>20</v>
       </c>
-      <c r="E18" t="n">
-        <v>37</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7</v>
-      </c>
-      <c r="H18" t="n">
-        <v>23</v>
-      </c>
-      <c r="I18" t="n">
-        <v>26</v>
-      </c>
-      <c r="J18" t="n">
-        <v>12</v>
-      </c>
-      <c r="K18" t="n">
-        <v>21</v>
-      </c>
-      <c r="L18" t="n">
-        <v>11</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" t="n">
-        <v>8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7</v>
-      </c>
-      <c r="S18" t="n">
-        <v>25</v>
-      </c>
-      <c r="T18" t="n">
-        <v>109</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" t="n">
-        <v>15</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>28</v>
-      </c>
       <c r="AA18" t="n">
-        <v>0.571</v>
+        <v>0.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>6</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH18" t="n">
         <v>3</v>
       </c>
-      <c r="AG18" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AL18" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.286</v>
+        <v>0.5</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>125:58</t>
+          <t>188:27</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>63.44</v>
+        <v>85.36</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.523</v>
+        <v>0.672</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.622</v>
+        <v>0.705</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.088</v>
+        <v>1.195</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.126</v>
+        <v>0.152</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.523</v>
+        <v>0.25</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.5</v>
+        <v>0.538</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.247</v>
+        <v>0.221</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.123</v>
+        <v>0.037</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.184</v>
+        <v>0.132</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>#44 J. PARRA</t>
+          <t>#23 T. SHENGELIA</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E19" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R19" t="n">
         <v>8</v>
       </c>
       <c r="S19" t="n">
+        <v>27</v>
+      </c>
+      <c r="T19" t="n">
+        <v>125</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" t="n">
+        <v>17</v>
+      </c>
+      <c r="W19" t="n">
         <v>4</v>
       </c>
-      <c r="T19" t="n">
-        <v>53</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>7</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="Z19" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.75</v>
+        <v>0.576</v>
       </c>
       <c r="AB19" t="n">
         <v>3</v>
       </c>
       <c r="AC19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF19" t="n">
         <v>4</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AG19" t="n">
         <v>0.75</v>
       </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
       <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
         <v>2</v>
       </c>
-      <c r="AI19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>4</v>
-      </c>
       <c r="AL19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.667</v>
+        <v>0.222</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>120:56</t>
+          <t>154:57</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>30.76</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.778</v>
+        <v>0.519</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.8</v>
+        <v>0.599</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.495</v>
+        <v>1.042</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.065</v>
+        <v>0.13</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.148</v>
+        <v>0.444</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.125</v>
+        <v>0.241</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.058</v>
+        <v>0.124</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.1</v>
+        <v>0.167</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.017</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>#44 J. PARRA</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L20" t="n">
         <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>10</v>
+      </c>
+      <c r="S20" t="n">
         <v>5</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -3396,243 +3396,243 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>0.786</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>152:50</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>39.2</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>0.843</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.633</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>19</v>
+      </c>
+      <c r="L21" t="n">
         <v>6</v>
       </c>
-      <c r="C21" t="n">
-        <v>560</v>
-      </c>
-      <c r="D21" t="n">
-        <v>136</v>
-      </c>
-      <c r="E21" t="n">
-        <v>237</v>
-      </c>
-      <c r="F21" t="n">
-        <v>61</v>
-      </c>
-      <c r="G21" t="n">
-        <v>127</v>
-      </c>
-      <c r="H21" t="n">
-        <v>105</v>
-      </c>
-      <c r="I21" t="n">
-        <v>127</v>
-      </c>
-      <c r="J21" t="n">
-        <v>89</v>
-      </c>
-      <c r="K21" t="n">
-        <v>167</v>
-      </c>
-      <c r="L21" t="n">
-        <v>53</v>
-      </c>
       <c r="M21" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="Q21" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>671</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.673</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.485</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.647</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.455</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>1200:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>489.88</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.143</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.288</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.271</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -3641,157 +3641,157 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>466</v>
+        <v>673</v>
       </c>
       <c r="D22" t="n">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="E22" t="n">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="F22" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="G22" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H22" t="n">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="I22" t="n">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="J22" t="n">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="K22" t="n">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="L22" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M22" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="N22" t="n">
+        <v>34</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>75</v>
+      </c>
+      <c r="R22" t="n">
+        <v>147</v>
+      </c>
+      <c r="S22" t="n">
+        <v>147</v>
+      </c>
+      <c r="T22" t="n">
+        <v>797</v>
+      </c>
+      <c r="U22" t="n">
+        <v>59</v>
+      </c>
+      <c r="V22" t="n">
+        <v>70</v>
+      </c>
+      <c r="W22" t="n">
         <v>24</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>65</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>56</v>
-      </c>
-      <c r="R22" t="n">
-        <v>131</v>
-      </c>
-      <c r="S22" t="n">
-        <v>123</v>
-      </c>
-      <c r="T22" t="n">
-        <v>460</v>
-      </c>
-      <c r="U22" t="n">
-        <v>68</v>
-      </c>
-      <c r="V22" t="n">
-        <v>51</v>
-      </c>
-      <c r="W22" t="n">
-        <v>26</v>
-      </c>
       <c r="X22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="Z22" t="n">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.66</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AB22" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="AC22" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.547</v>
+        <v>0.462</v>
       </c>
       <c r="AE22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>69</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI22" t="n">
         <v>23</v>
       </c>
-      <c r="AF22" t="n">
-        <v>74</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0.311</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>30</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>0.4</v>
+        <v>0.609</v>
       </c>
       <c r="AK22" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="AL22" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.295</v>
+        <v>0.465</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>1200:00</t>
+          <t>1425:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>495.08</v>
+        <v>585.12</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.497</v>
+        <v>0.631</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.542</v>
+        <v>0.667</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.9409999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.131</v>
+        <v>0.138</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.222</v>
+        <v>0.271</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.262</v>
+        <v>1.37</v>
       </c>
       <c r="AV22" t="n">
         <v>0.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.047</v>
+        <v>0.059</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.138</v>
+        <v>0.151</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -3800,1190 +3800,1190 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="inlineStr"/>
+          <t>Rival</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" t="n">
+        <v>578</v>
+      </c>
+      <c r="D23" t="n">
+        <v>150</v>
+      </c>
+      <c r="E23" t="n">
+        <v>277</v>
+      </c>
+      <c r="F23" t="n">
+        <v>58</v>
+      </c>
+      <c r="G23" t="n">
+        <v>188</v>
+      </c>
+      <c r="H23" t="n">
+        <v>104</v>
+      </c>
+      <c r="I23" t="n">
+        <v>131</v>
+      </c>
+      <c r="J23" t="n">
+        <v>101</v>
+      </c>
+      <c r="K23" t="n">
+        <v>146</v>
+      </c>
+      <c r="L23" t="n">
+        <v>62</v>
+      </c>
+      <c r="M23" t="n">
+        <v>43</v>
+      </c>
+      <c r="N23" t="n">
+        <v>33</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>61</v>
+      </c>
+      <c r="R23" t="n">
+        <v>153</v>
+      </c>
+      <c r="S23" t="n">
+        <v>146</v>
+      </c>
+      <c r="T23" t="n">
+        <v>602</v>
+      </c>
+      <c r="U23" t="n">
+        <v>76</v>
+      </c>
+      <c r="V23" t="n">
+        <v>63</v>
+      </c>
+      <c r="W23" t="n">
+        <v>36</v>
+      </c>
+      <c r="X23" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>86</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>126</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>37</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>69</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>82</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>45</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>154</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>1425:00</t>
+        </is>
+      </c>
+      <c r="AO23" t="n">
+        <v>592.64</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.443</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>#0 K. PUNTER (Per Game)</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>6</v>
-      </c>
-      <c r="C24" t="n">
-        <v>12</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.833</v>
-      </c>
-      <c r="E24" t="n">
-        <v>6</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.833</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="T24" t="n">
-        <v>47</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="AO24" t="n">
-        <v>11.787</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0.574</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.018</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0.268</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0.064</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>#2 J. MARCOS (Per Game)</t>
+          <t>#0 K. PUNTER (Per Game)</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>12.286</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.857</v>
+      </c>
+      <c r="E25" t="n">
         <v>6</v>
       </c>
-      <c r="C25" t="n">
-        <v>3.167</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.667</v>
-      </c>
       <c r="F25" t="n">
-        <v>0.833</v>
+        <v>1.571</v>
       </c>
       <c r="G25" t="n">
-        <v>1.667</v>
+        <v>3.571</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1.857</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2.143</v>
       </c>
       <c r="J25" t="n">
-        <v>1.167</v>
+        <v>2.143</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>1.286</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="M25" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0.333</v>
+        <v>0.143</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.833</v>
+        <v>1.429</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.833</v>
+        <v>1.429</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>2.714</v>
       </c>
       <c r="S25" t="n">
-        <v>0.333</v>
+        <v>1.857</v>
       </c>
       <c r="T25" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="U25" t="n">
-        <v>0.333</v>
+        <v>0.857</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.333</v>
+        <v>0.714</v>
       </c>
       <c r="Z25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>3.714</v>
+      </c>
+      <c r="AG25" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA25" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.833</v>
+        <v>1.429</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.667</v>
+        <v>3</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.5</v>
+        <v>0.476</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>3.167</v>
+        <v>11.943</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.679</v>
+        <v>0.545</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.679</v>
+        <v>0.584</v>
       </c>
       <c r="AR25" t="n">
-        <v>1</v>
+        <v>1.029</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.263</v>
+        <v>0.12</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.111</v>
+        <v>0.252</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.157</v>
+        <v>0.063</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.037</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>#3 M. CALE (Per Game)</t>
+          <t>#2 J. MARCOS (Per Game)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>3.833</v>
+        <v>3.143</v>
       </c>
       <c r="D26" t="n">
-        <v>0.833</v>
+        <v>0.286</v>
       </c>
       <c r="E26" t="n">
-        <v>1.5</v>
+        <v>0.714</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5</v>
+        <v>0.857</v>
       </c>
       <c r="G26" t="n">
-        <v>1.167</v>
+        <v>1.714</v>
       </c>
       <c r="H26" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5</v>
+        <v>1.286</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>1.857</v>
       </c>
       <c r="L26" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0.571</v>
       </c>
       <c r="N26" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5</v>
+        <v>0.857</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.5</v>
+        <v>0.857</v>
       </c>
       <c r="R26" t="n">
-        <v>1.667</v>
+        <v>2.143</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5</v>
+        <v>0.286</v>
       </c>
       <c r="T26" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="U26" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AA26" t="n">
         <v>0.667</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>0.143</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.167</v>
+        <v>0.857</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.333</v>
+        <v>1.714</v>
       </c>
       <c r="AM26" t="n">
         <v>0.5</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>3.607</v>
+        <v>3.286</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.594</v>
+        <v>0.647</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.617</v>
+        <v>0.647</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.063</v>
+        <v>0.957</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.139</v>
+        <v>0.261</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.121</v>
+        <v>0.117</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.151</v>
+        <v>0.153</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.016</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#6 J. VESELY (Per Game)</t>
+          <t>#3 M. CALE (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>4.286</v>
       </c>
       <c r="D27" t="n">
-        <v>3.333</v>
+        <v>0.857</v>
       </c>
       <c r="E27" t="n">
-        <v>4.833</v>
+        <v>1.571</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="G27" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="T27" t="n">
+        <v>33</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>0.333</v>
       </c>
-      <c r="H27" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="AK27" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AM27" t="n">
         <v>0.667</v>
       </c>
-      <c r="N27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>69</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.833</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>6.84</v>
+        <v>3.789</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.645</v>
+        <v>0.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.71</v>
+        <v>0.638</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.316</v>
+        <v>1.131</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.073</v>
+        <v>0.113</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.452</v>
+        <v>0.3</v>
       </c>
       <c r="AU27" t="n">
-        <v>2</v>
+        <v>1.333</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.188</v>
+        <v>0.125</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.066</v>
+        <v>0.013</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.134</v>
+        <v>0.142</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.034</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#8 D. BRIZUELA (Per Game)</t>
+          <t>#6 J. VESELY (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>9.333</v>
+        <v>8.856999999999999</v>
       </c>
       <c r="D28" t="n">
+        <v>3.286</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.286</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="T28" t="n">
+        <v>80</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.714</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AO28" t="n">
+        <v>6.846</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="AU28" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="G28" t="n">
-        <v>4</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="T28" t="n">
-        <v>53</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AO28" t="n">
-        <v>8.067</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.157</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AV28" t="n">
-        <v>0.255</v>
+        <v>0.173</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.015</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.062</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#13 T. SATORANSKY (Per Game)</t>
+          <t>#8 D. BRIZUELA (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" t="n">
-        <v>3.833</v>
+        <v>9.286</v>
       </c>
       <c r="D29" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4.143</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.429</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="T29" t="n">
+        <v>57</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.429</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>0.667</v>
       </c>
-      <c r="E29" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="T29" t="n">
-        <v>37</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1</v>
-      </c>
       <c r="AK29" t="n">
-        <v>0.333</v>
+        <v>1.286</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.833</v>
+        <v>3.714</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.4</v>
+        <v>0.346</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>4.587</v>
+        <v>7.914</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.472</v>
+        <v>0.62</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.534</v>
+        <v>0.645</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.836</v>
+        <v>1.173</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.218</v>
+        <v>0.09</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.333</v>
+        <v>0.174</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.667</v>
+        <v>2.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.127</v>
+        <v>0.227</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.04</v>
+        <v>0.012</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.156</v>
+        <v>0.057</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#14 W. HERNANGÓMEZ (Per Game)</t>
+          <t>#13 T. SATORANSKY (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>3.167</v>
+        <v>3.833</v>
       </c>
       <c r="D30" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
         <v>1.333</v>
       </c>
-      <c r="E30" t="n">
+      <c r="J30" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="K30" t="n">
         <v>2.5</v>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
+      <c r="L30" t="n">
         <v>0.5</v>
       </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.667</v>
-      </c>
       <c r="M30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N30" t="n">
         <v>0.167</v>
       </c>
-      <c r="N30" t="n">
-        <v>0.5</v>
-      </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.833</v>
+        <v>1.833</v>
       </c>
       <c r="S30" t="n">
         <v>1.167</v>
       </c>
       <c r="T30" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="U30" t="n">
         <v>0.333</v>
       </c>
       <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE30" t="n">
         <v>0.333</v>
       </c>
-      <c r="W30" t="n">
+      <c r="AF30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK30" t="n">
         <v>0.333</v>
       </c>
-      <c r="X30" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>2.94</v>
+        <v>4.587</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.533</v>
+        <v>0.472</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.539</v>
+        <v>0.534</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.077</v>
+        <v>0.836</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>0.218</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.238</v>
+        <v>0.126</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.156</v>
+        <v>0.039</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.273</v>
+        <v>0.159</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#19 Y. FALL (Per Game)</t>
+          <t>#14 W. HERNANGÓMEZ (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31" t="n">
-        <v>7.667</v>
+        <v>2.714</v>
       </c>
       <c r="D31" t="n">
-        <v>3.333</v>
+        <v>1.143</v>
       </c>
       <c r="E31" t="n">
-        <v>4.667</v>
+        <v>2.286</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4992,123 +4992,123 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0.429</v>
       </c>
       <c r="I31" t="n">
-        <v>1.667</v>
+        <v>0.857</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>3.333</v>
+        <v>1.286</v>
       </c>
       <c r="L31" t="n">
-        <v>1.5</v>
+        <v>0.571</v>
       </c>
       <c r="M31" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="N31" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="T31" t="n">
+        <v>29</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.143</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="AO31" t="n">
+        <v>2.663</v>
+      </c>
+      <c r="AP31" t="n">
         <v>0.5</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>63</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AO31" t="n">
-        <v>5.733</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0.714</v>
-      </c>
       <c r="AQ31" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.337</v>
+        <v>1.019</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.058</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.214</v>
+        <v>0.188</v>
       </c>
       <c r="AU31" t="n">
         <v>0</v>
@@ -5117,10 +5117,10 @@
         <v>0.177</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.134</v>
+        <v>0.108</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.232</v>
+        <v>0.198</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -5129,740 +5129,740 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#20 N. LAPROVITTOLA (Per Game)</t>
+          <t>#17 J. NÚÑEZ (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>8.667</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.833</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>04:03</t>
+        </is>
+      </c>
+      <c r="AO32" t="n">
         <v>2</v>
       </c>
-      <c r="G32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="AP32" t="n">
         <v>0.5</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>53</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="W32" t="n">
+      <c r="AQ32" t="n">
         <v>0.5</v>
       </c>
-      <c r="X32" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AO32" t="n">
-        <v>7.047</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0.831</v>
-      </c>
       <c r="AR32" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.273</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.313</v>
+        <v>0.241</v>
       </c>
       <c r="AW32" t="n">
         <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.083</v>
+        <v>0.278</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.077</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#21 W. CLYBURN (Per Game)</t>
+          <t>#19 Y. FALL (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33" t="n">
-        <v>13.5</v>
+        <v>6.571</v>
       </c>
       <c r="D33" t="n">
-        <v>2.333</v>
+        <v>2.857</v>
       </c>
       <c r="E33" t="n">
-        <v>4.667</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>2.167</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.333</v>
+        <v>0.857</v>
       </c>
       <c r="I33" t="n">
-        <v>2.667</v>
+        <v>1.714</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>3.167</v>
+        <v>3.286</v>
       </c>
       <c r="L33" t="n">
-        <v>0.833</v>
+        <v>1.571</v>
       </c>
       <c r="M33" t="n">
-        <v>1.167</v>
+        <v>0.143</v>
       </c>
       <c r="N33" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>0.429</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>0.429</v>
       </c>
       <c r="R33" t="n">
-        <v>2.167</v>
+        <v>1.714</v>
       </c>
       <c r="S33" t="n">
-        <v>3.5</v>
+        <v>1.571</v>
       </c>
       <c r="T33" t="n">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="U33" t="n">
-        <v>2.167</v>
+        <v>0.571</v>
       </c>
       <c r="V33" t="n">
-        <v>1.333</v>
+        <v>1.571</v>
       </c>
       <c r="W33" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AG33" t="n">
         <v>0.333</v>
       </c>
-      <c r="Y33" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AH33" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>25:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>11.34</v>
+        <v>5.183</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.714</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.723</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.19</v>
+        <v>1.268</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.176</v>
+        <v>0.083</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.286</v>
+        <v>0.214</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.22</v>
+        <v>0.174</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.047</v>
+        <v>0.149</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.138</v>
+        <v>0.255</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#23 T. SHENGELIA (Per Game)</t>
+          <t>#20 N. LAPROVITTOLA (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34" t="n">
-        <v>11.5</v>
+        <v>10.286</v>
       </c>
       <c r="D34" t="n">
-        <v>3.333</v>
+        <v>0.571</v>
       </c>
       <c r="E34" t="n">
-        <v>6.167</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.333</v>
+        <v>2.286</v>
       </c>
       <c r="G34" t="n">
-        <v>1.167</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>3.833</v>
+        <v>2.286</v>
       </c>
       <c r="I34" t="n">
-        <v>4.333</v>
+        <v>2.571</v>
       </c>
       <c r="J34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
         <v>2</v>
       </c>
-      <c r="K34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.333</v>
-      </c>
       <c r="Q34" t="n">
-        <v>1.333</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.167</v>
+        <v>1.857</v>
       </c>
       <c r="S34" t="n">
-        <v>4.167</v>
+        <v>2.429</v>
       </c>
       <c r="T34" t="n">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="U34" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>2.5</v>
+        <v>0.571</v>
       </c>
       <c r="W34" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="X34" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.667</v>
+        <v>0.571</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.667</v>
+        <v>0.571</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.571</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1</v>
+        <v>0.286</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.5</v>
+        <v>0.143</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.333</v>
+        <v>2.143</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.167</v>
+        <v>3.857</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.286</v>
+        <v>0.556</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>10.573</v>
+        <v>8.131</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.523</v>
+        <v>0.8</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.622</v>
+        <v>0.839</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.088</v>
+        <v>1.265</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.126</v>
+        <v>0.246</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.523</v>
+        <v>0.457</v>
       </c>
       <c r="AU34" t="n">
         <v>1.5</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.247</v>
+        <v>0.265</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.184</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#44 J. PARRA (Per Game)</t>
+          <t>#21 W. CLYBURN (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C35" t="n">
-        <v>7.667</v>
+        <v>14.571</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>2.286</v>
       </c>
       <c r="E35" t="n">
-        <v>3.167</v>
+        <v>4.286</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>2.571</v>
       </c>
       <c r="G35" t="n">
-        <v>1.333</v>
+        <v>4.857</v>
       </c>
       <c r="H35" t="n">
-        <v>0.667</v>
+        <v>2.286</v>
       </c>
       <c r="I35" t="n">
-        <v>0.667</v>
+        <v>2.714</v>
       </c>
       <c r="J35" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>1.833</v>
+        <v>3.143</v>
       </c>
       <c r="L35" t="n">
-        <v>0.833</v>
+        <v>0.714</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5</v>
+        <v>1.143</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.333</v>
+        <v>1.857</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.333</v>
+        <v>1.857</v>
       </c>
       <c r="R35" t="n">
-        <v>1.333</v>
+        <v>2.143</v>
       </c>
       <c r="S35" t="n">
-        <v>0.667</v>
+        <v>3.429</v>
       </c>
       <c r="T35" t="n">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.571</v>
       </c>
       <c r="V35" t="n">
-        <v>1.167</v>
+        <v>1.143</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.5</v>
+        <v>2.143</v>
       </c>
       <c r="Z35" t="n">
-        <v>2</v>
+        <v>2.857</v>
       </c>
       <c r="AA35" t="n">
         <v>0.75</v>
       </c>
       <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>2.143</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>4.286</v>
+      </c>
+      <c r="AM35" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC35" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0.667</v>
-      </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>26:55</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>5.127</v>
+        <v>12.194</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.778</v>
+        <v>0.672</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.8</v>
+        <v>0.705</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.495</v>
+        <v>1.195</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.065</v>
+        <v>0.152</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.148</v>
+        <v>0.25</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.5</v>
+        <v>0.538</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.125</v>
+        <v>0.221</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.058</v>
+        <v>0.037</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.1</v>
+        <v>0.132</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.017</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>#23 T. SHENGELIA (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>11.429</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>3.571</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>6.429</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1.286</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>3.429</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>4.143</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>2.286</v>
       </c>
       <c r="K36" t="n">
-        <v>2.667</v>
+        <v>3.286</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.714</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.833</v>
+        <v>1.429</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.429</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.143</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.857</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2.429</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.714</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>4.714</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>0.576</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.143</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
@@ -5874,368 +5874,686 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.286</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>10.966</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>0.519</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>0.599</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.042</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>0.241</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>0.124</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>TOTAL (Per Game)</t>
+          <t>#44 J. PARRA (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>93.333</v>
+        <v>9.143000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>22.667</v>
+        <v>2.286</v>
       </c>
       <c r="E37" t="n">
-        <v>39.5</v>
+        <v>3.429</v>
       </c>
       <c r="F37" t="n">
-        <v>10.167</v>
+        <v>1.286</v>
       </c>
       <c r="G37" t="n">
-        <v>21.167</v>
+        <v>1.571</v>
       </c>
       <c r="H37" t="n">
-        <v>17.5</v>
+        <v>0.714</v>
       </c>
       <c r="I37" t="n">
-        <v>21.167</v>
+        <v>0.714</v>
       </c>
       <c r="J37" t="n">
-        <v>14.833</v>
+        <v>0.714</v>
       </c>
       <c r="K37" t="n">
-        <v>27.833</v>
+        <v>1.857</v>
       </c>
       <c r="L37" t="n">
-        <v>8.833</v>
+        <v>0.857</v>
       </c>
       <c r="M37" t="n">
-        <v>5.833</v>
+        <v>0.571</v>
       </c>
       <c r="N37" t="n">
-        <v>4.167</v>
+        <v>0.143</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>11.667</v>
+        <v>0.286</v>
       </c>
       <c r="Q37" t="n">
-        <v>10.833</v>
+        <v>0.286</v>
       </c>
       <c r="R37" t="n">
-        <v>20.667</v>
+        <v>1.429</v>
       </c>
       <c r="S37" t="n">
-        <v>20.833</v>
+        <v>0.714</v>
       </c>
       <c r="T37" t="n">
-        <v>671</v>
+        <v>76</v>
       </c>
       <c r="U37" t="n">
-        <v>8.333</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>10.833</v>
+        <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>3.667</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.167</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>12</v>
+        <v>1.571</v>
       </c>
       <c r="Z37" t="n">
-        <v>17.833</v>
+        <v>2</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.673</v>
+        <v>0.786</v>
       </c>
       <c r="AB37" t="n">
-        <v>5.333</v>
+        <v>0.714</v>
       </c>
       <c r="AC37" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.485</v>
+        <v>0.714</v>
       </c>
       <c r="AE37" t="n">
-        <v>5.333</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>10.667</v>
+        <v>0.429</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.833</v>
+        <v>0.571</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.833</v>
+        <v>0.571</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.647</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="n">
-        <v>8.333</v>
+        <v>0.714</v>
       </c>
       <c r="AL37" t="n">
-        <v>18.333</v>
+        <v>1</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.455</v>
+        <v>0.714</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>200:00</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>81.64700000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.625</v>
+        <v>0.843</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.667</v>
+        <v>0.86</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.143</v>
+        <v>1.633</v>
       </c>
       <c r="AS37" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="AT37" t="n">
         <v>0.143</v>
       </c>
-      <c r="AT37" t="n">
-        <v>0.288</v>
-      </c>
       <c r="AU37" t="n">
-        <v>1.271</v>
+        <v>2.5</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.2</v>
+        <v>0.125</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.062</v>
+        <v>0.054</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.153</v>
+        <v>0.096</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
+          <t>Equip (Per Game)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.714</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL (Per Game)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" t="n">
+        <v>96.143</v>
+      </c>
+      <c r="D39" t="n">
+        <v>22.429</v>
+      </c>
+      <c r="E39" t="n">
+        <v>39.143</v>
+      </c>
+      <c r="F39" t="n">
+        <v>11.429</v>
+      </c>
+      <c r="G39" t="n">
+        <v>23.571</v>
+      </c>
+      <c r="H39" t="n">
+        <v>17</v>
+      </c>
+      <c r="I39" t="n">
+        <v>21.143</v>
+      </c>
+      <c r="J39" t="n">
+        <v>15.857</v>
+      </c>
+      <c r="K39" t="n">
+        <v>27.286</v>
+      </c>
+      <c r="L39" t="n">
+        <v>8.714</v>
+      </c>
+      <c r="M39" t="n">
+        <v>5.571</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4.857</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>11.571</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>10.714</v>
+      </c>
+      <c r="R39" t="n">
+        <v>21</v>
+      </c>
+      <c r="S39" t="n">
+        <v>21</v>
+      </c>
+      <c r="T39" t="n">
+        <v>797</v>
+      </c>
+      <c r="U39" t="n">
+        <v>8.429</v>
+      </c>
+      <c r="V39" t="n">
+        <v>10</v>
+      </c>
+      <c r="W39" t="n">
+        <v>3.429</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>12.286</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>17.857</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>5.286</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>11.429</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>4.857</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>9.856999999999999</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>3.286</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>9.429</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>20.286</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>203:34</t>
+        </is>
+      </c>
+      <c r="AO39" t="n">
+        <v>83.589</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
           <t>Rival (Per Game)</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>6</v>
-      </c>
-      <c r="C38" t="n">
-        <v>77.667</v>
-      </c>
-      <c r="D38" t="n">
-        <v>19</v>
-      </c>
-      <c r="E38" t="n">
-        <v>36.833</v>
-      </c>
-      <c r="F38" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G38" t="n">
-        <v>27</v>
-      </c>
-      <c r="H38" t="n">
-        <v>14.167</v>
-      </c>
-      <c r="I38" t="n">
-        <v>17.833</v>
-      </c>
-      <c r="J38" t="n">
-        <v>13.667</v>
-      </c>
-      <c r="K38" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="L38" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M38" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>4</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>10.833</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="R38" t="n">
-        <v>21.833</v>
-      </c>
-      <c r="S38" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T38" t="n">
-        <v>460</v>
-      </c>
-      <c r="U38" t="n">
-        <v>11.333</v>
-      </c>
-      <c r="V38" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W38" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>10.333</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>15.667</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>4.833</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>8.833</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>3.833</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>12.333</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.311</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AL38" t="n">
+      <c r="B40" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" t="n">
+        <v>82.571</v>
+      </c>
+      <c r="D40" t="n">
+        <v>21.429</v>
+      </c>
+      <c r="E40" t="n">
+        <v>39.571</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8.286</v>
+      </c>
+      <c r="G40" t="n">
+        <v>26.857</v>
+      </c>
+      <c r="H40" t="n">
+        <v>14.857</v>
+      </c>
+      <c r="I40" t="n">
+        <v>18.714</v>
+      </c>
+      <c r="J40" t="n">
+        <v>14.429</v>
+      </c>
+      <c r="K40" t="n">
+        <v>20.857</v>
+      </c>
+      <c r="L40" t="n">
+        <v>8.856999999999999</v>
+      </c>
+      <c r="M40" t="n">
+        <v>6.143</v>
+      </c>
+      <c r="N40" t="n">
+        <v>4.714</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>8.714</v>
+      </c>
+      <c r="R40" t="n">
+        <v>21.857</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20.857</v>
+      </c>
+      <c r="T40" t="n">
+        <v>602</v>
+      </c>
+      <c r="U40" t="n">
+        <v>10.857</v>
+      </c>
+      <c r="V40" t="n">
+        <v>9</v>
+      </c>
+      <c r="W40" t="n">
+        <v>5.143</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>12.286</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>5.286</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>9.856999999999999</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>3.857</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>11.714</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>4.857</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>6.429</v>
+      </c>
+      <c r="AL40" t="n">
         <v>22</v>
       </c>
-      <c r="AM38" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO38" t="n">
-        <v>82.51300000000001</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>1.262</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="AW38" t="n">
+      <c r="AM40" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>203:34</t>
+        </is>
+      </c>
+      <c r="AO40" t="n">
+        <v>84.663</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1.443</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="AW40" t="n">
         <v>0.06</v>
       </c>
-      <c r="AX38" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="AY38" t="n">
+      <c r="AX40" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AY40" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Barça.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Barça.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>524.12</v>
+        <v>599.6</v>
       </c>
       <c r="C2" t="n">
-        <v>527.38</v>
+        <v>601.96</v>
       </c>
       <c r="D2" t="n">
-        <v>127.6119685994918</v>
+        <v>124.2607482224733</v>
       </c>
       <c r="E2" t="n">
-        <v>109.5983920512723</v>
+        <v>112.9643165658848</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6309794988610479</v>
+        <v>0.6023391812865497</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1384331419196062</v>
+        <v>0.1319300326119182</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2946859903381642</v>
+        <v>0.2976190476190476</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2710706150341686</v>
+        <v>0.253411306042885</v>
       </c>
       <c r="J2" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="K2" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="L2" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="M2" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="N2" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="O2" t="n">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2847380410022779</v>
+        <v>0.304093567251462</v>
       </c>
       <c r="Q2" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="R2" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1822323462414579</v>
+        <v>0.189083820662768</v>
       </c>
       <c r="T2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U2" t="n">
+        <v>74</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1442495126705653</v>
+      </c>
+      <c r="W2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X2" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.050682261208577</v>
+      </c>
+      <c r="Z2" t="n">
         <v>69</v>
       </c>
-      <c r="V2" t="n">
-        <v>0.1571753986332574</v>
-      </c>
-      <c r="W2" t="n">
-        <v>14</v>
-      </c>
-      <c r="X2" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.05239179954441914</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>66</v>
-      </c>
       <c r="AA2" t="n">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3234624145785877</v>
+        <v>0.3118908382066277</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6794871794871795</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4625</v>
+        <v>0.4329896907216495</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4927536231884058</v>
+        <v>0.472972972972973</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4647887323943662</v>
+        <v>0.43125</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.376</v>
+        <v>1.358974358974359</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.9855072463768116</v>
+        <v>0.9459459459459459</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.454545454545455</v>
+        <v>1.354838709677419</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8428571428571429</v>
+        <v>0.8765432098765432</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.147540983606557</v>
+        <v>1.093333333333333</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.714285714285714</v>
+        <v>1.684210526315789</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.37037037037037</v>
+        <v>1.415730337078652</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.419753086419753</v>
+        <v>5.764044943820225</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.790123456790123</v>
+        <v>7.179775280898877</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.87428571428572</v>
+        <v>74.95</v>
       </c>
       <c r="C3" t="n">
-        <v>75.34</v>
+        <v>75.245</v>
       </c>
       <c r="D3" t="n">
-        <v>127.6119685994918</v>
+        <v>124.2607482224733</v>
       </c>
       <c r="E3" t="n">
-        <v>109.5983920512723</v>
+        <v>112.9643165658848</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6309794988610478</v>
+        <v>0.6023391812865497</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1384331419196062</v>
+        <v>0.1319300326119182</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2946859903381642</v>
+        <v>0.2976190476190476</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2710706150341685</v>
+        <v>0.253411306042885</v>
       </c>
       <c r="J3" t="n">
-        <v>8.428571428571429</v>
+        <v>8.875</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="L3" t="n">
-        <v>3.428571428571428</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>10.71428571428571</v>
+        <v>9.875</v>
       </c>
       <c r="N3" t="n">
-        <v>12.28571428571429</v>
+        <v>13.25</v>
       </c>
       <c r="O3" t="n">
-        <v>17.85714285714286</v>
+        <v>19.5</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2847380410022779</v>
+        <v>0.304093567251462</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.285714285714286</v>
+        <v>5.25</v>
       </c>
       <c r="R3" t="n">
-        <v>11.42857142857143</v>
+        <v>12.125</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1822323462414578</v>
+        <v>0.189083820662768</v>
       </c>
       <c r="T3" t="n">
-        <v>4.857142857142857</v>
+        <v>4.375</v>
       </c>
       <c r="U3" t="n">
-        <v>9.857142857142858</v>
+        <v>9.25</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1571753986332574</v>
+        <v>0.1442495126705653</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1.875</v>
       </c>
       <c r="X3" t="n">
-        <v>3.285714285714286</v>
+        <v>3.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.05239179954441912</v>
+        <v>0.050682261208577</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.428571428571429</v>
+        <v>8.625</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.28571428571428</v>
+        <v>20</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3234624145785877</v>
+        <v>0.3118908382066277</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.6880000000000001</v>
+        <v>0.6794871794871795</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4625</v>
+        <v>0.4329896907216495</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4927536231884057</v>
+        <v>0.472972972972973</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4647887323943662</v>
+        <v>0.43125</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.376</v>
+        <v>1.358974358974359</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.9855072463768114</v>
+        <v>0.9459459459459459</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.454545454545455</v>
+        <v>1.354838709677419</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8428571428571429</v>
+        <v>0.8765432098765432</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.147540983606558</v>
+        <v>1.093333333333333</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.714285714285714</v>
+        <v>1.684210526315789</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.37037037037037</v>
+        <v>1.415730337078652</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.419753086419754</v>
+        <v>5.764044943820225</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.790123456790124</v>
+        <v>7.179775280898877</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>530.6400000000001</v>
+        <v>604.3200000000002</v>
       </c>
       <c r="C4" t="n">
-        <v>527.38</v>
+        <v>601.96</v>
       </c>
       <c r="D4" t="n">
-        <v>109.5983920512723</v>
+        <v>112.9643165658848</v>
       </c>
       <c r="E4" t="n">
-        <v>127.6119685994918</v>
+        <v>124.2607482224733</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5096774193548387</v>
+        <v>0.5264650283553876</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1181155507559395</v>
+        <v>0.1195889682867773</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2450592885375494</v>
+        <v>0.2570422535211268</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2236559139784946</v>
+        <v>0.2325141776937618</v>
       </c>
       <c r="J4" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K4" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="N4" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="O4" t="n">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2709677419354839</v>
+        <v>0.279773156899811</v>
       </c>
       <c r="Q4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="R4" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1483870967741935</v>
+        <v>0.1512287334593573</v>
       </c>
       <c r="T4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="U4" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1763440860215054</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="W4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="X4" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07311827956989247</v>
+        <v>0.08128544423440454</v>
       </c>
       <c r="Z4" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AA4" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3311827956989247</v>
+        <v>0.3137996219281664</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.6825396825396826</v>
+        <v>0.6891891891891891</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5362318840579711</v>
+        <v>0.5125</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3292682926829268</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3823529411764706</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2922077922077922</v>
+        <v>0.3072289156626506</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.365079365079365</v>
+        <v>1.378378378378378</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.925531914893617</v>
+        <v>0.9904306220095693</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.9382716049382716</v>
+        <v>0.9662921348314607</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.016129032258065</v>
+        <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.714285714285714</v>
+        <v>1.62962962962963</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.442857142857143</v>
+        <v>1.493827160493827</v>
       </c>
       <c r="AO4" t="n">
-        <v>6.642857142857143</v>
+        <v>6.530864197530864</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.085714285714285</v>
+        <v>8.024691358024691</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75.8057142857143</v>
+        <v>75.54000000000002</v>
       </c>
       <c r="C5" t="n">
-        <v>75.34</v>
+        <v>75.245</v>
       </c>
       <c r="D5" t="n">
-        <v>109.5983920512723</v>
+        <v>112.9643165658848</v>
       </c>
       <c r="E5" t="n">
-        <v>127.6119685994918</v>
+        <v>124.2607482224733</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5096774193548388</v>
+        <v>0.5264650283553876</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1181155507559395</v>
+        <v>0.1195889682867773</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2450592885375494</v>
+        <v>0.2570422535211268</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2236559139784946</v>
+        <v>0.2325141776937618</v>
       </c>
       <c r="J5" t="n">
-        <v>10.85714285714286</v>
+        <v>10.75</v>
       </c>
       <c r="K5" t="n">
+        <v>9.125</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" t="n">
-        <v>5.142857142857143</v>
-      </c>
-      <c r="M5" t="n">
-        <v>8.714285714285714</v>
-      </c>
       <c r="N5" t="n">
-        <v>12.28571428571429</v>
+        <v>12.75</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2709677419354838</v>
+        <v>0.279773156899811</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.285714285714286</v>
+        <v>5.125</v>
       </c>
       <c r="R5" t="n">
-        <v>9.857142857142858</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1483870967741935</v>
+        <v>0.1512287334593573</v>
       </c>
       <c r="T5" t="n">
-        <v>3.857142857142857</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>11.71428571428571</v>
+        <v>11.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1763440860215054</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="W5" t="n">
-        <v>1.857142857142857</v>
+        <v>2.25</v>
       </c>
       <c r="X5" t="n">
-        <v>4.857142857142857</v>
+        <v>5.375</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.07311827956989246</v>
+        <v>0.08128544423440454</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.428571428571429</v>
+        <v>6.375</v>
       </c>
       <c r="AA5" t="n">
-        <v>22</v>
+        <v>20.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3311827956989247</v>
+        <v>0.3137996219281664</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6825396825396826</v>
+        <v>0.6891891891891891</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.536231884057971</v>
+        <v>0.5125</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3292682926829268</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3823529411764706</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.2922077922077922</v>
+        <v>0.3072289156626506</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.365079365079365</v>
+        <v>1.378378378378378</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9255319148936172</v>
+        <v>0.9904306220095693</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.9382716049382717</v>
+        <v>0.9662921348314607</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.016129032258065</v>
+        <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.714285714285714</v>
+        <v>1.62962962962963</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.442857142857143</v>
+        <v>1.493827160493827</v>
       </c>
       <c r="AO5" t="n">
-        <v>6.642857142857143</v>
+        <v>6.530864197530864</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.085714285714285</v>
+        <v>8.024691358024691</v>
       </c>
     </row>
     <row r="7">
@@ -1419,22 +1419,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H8" t="n">
         <v>13</v>
@@ -1443,40 +1443,40 @@
         <v>15</v>
       </c>
       <c r="J8" t="n">
+        <v>16</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>12</v>
+      </c>
+      <c r="R8" t="n">
+        <v>20</v>
+      </c>
+      <c r="S8" t="n">
         <v>15</v>
       </c>
-      <c r="K8" t="n">
-        <v>9</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>10</v>
-      </c>
-      <c r="R8" t="n">
-        <v>19</v>
-      </c>
-      <c r="S8" t="n">
-        <v>13</v>
-      </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="U8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V8" t="n">
         <v>7</v>
@@ -1488,87 +1488,87 @@
         <v>3</v>
       </c>
       <c r="Y8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.714</v>
+        <v>0.6</v>
       </c>
       <c r="AB8" t="n">
         <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.222</v>
+        <v>0.167</v>
       </c>
       <c r="AE8" t="n">
         <v>13</v>
       </c>
       <c r="AF8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.5</v>
+        <v>0.481</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK8" t="n">
         <v>10</v>
       </c>
       <c r="AL8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.476</v>
+        <v>0.455</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>161:29</t>
+          <t>184:51</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>83.59999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.545</v>
+        <v>0.493</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.584</v>
+        <v>0.533</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.029</v>
+        <v>0.93</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.12</v>
+        <v>0.127</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.194</v>
+        <v>0.171</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.5</v>
+        <v>1.333</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.252</v>
+        <v>0.247</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.063</v>
+        <v>0.062</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.073</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="9">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
         <v>22</v>
@@ -1587,7 +1587,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
@@ -1629,7 +1629,7 @@
         <v>15</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
         <v>22</v>
@@ -1650,10 +1650,10 @@
         <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1693,23 +1693,23 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>95:55</t>
+          <t>99:25</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.647</v>
+        <v>0.611</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.647</v>
+        <v>0.611</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.957</v>
+        <v>0.917</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.261</v>
+        <v>0.25</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
@@ -1718,16 +1718,16 @@
         <v>1.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.117</v>
+        <v>0.116</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.153</v>
+        <v>0.15</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.039</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="10">
@@ -1737,37 +1737,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
         <v>6</v>
@@ -1785,13 +1785,13 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="U10" t="n">
         <v>2</v>
@@ -1800,34 +1800,34 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -1845,48 +1845,48 @@
         <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>103:10</t>
+          <t>125:56</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>26.52</v>
+        <v>32.4</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.638</v>
+        <v>0.595</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.131</v>
+        <v>1.08</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.113</v>
+        <v>0.093</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="AU10" t="n">
         <v>1.333</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.125</v>
+        <v>0.124</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.013</v>
+        <v>0.031</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.142</v>
+        <v>0.154</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="11">
@@ -1896,16 +1896,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1914,10 +1914,10 @@
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
         <v>6</v>
@@ -1926,7 +1926,7 @@
         <v>17</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M11" t="n">
         <v>4</v>
@@ -1944,19 +1944,19 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U11" t="n">
         <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
@@ -1965,31 +1965,31 @@
         <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.6</v>
+        <v>0.714</v>
       </c>
       <c r="AB11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.727</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AE11" t="n">
         <v>12</v>
       </c>
       <c r="AF11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.632</v>
+        <v>0.6</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -2011,41 +2011,41 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>135:17</t>
+          <t>149:01</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>47.92</v>
+        <v>53.8</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.622</v>
+        <v>0.619</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.679</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.294</v>
+        <v>1.283</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.063</v>
+        <v>0.056</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.432</v>
+        <v>0.405</v>
       </c>
       <c r="AU11" t="n">
         <v>2</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.173</v>
+        <v>0.174</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.142</v>
+        <v>0.131</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="12">
@@ -2055,34 +2055,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" t="n">
+        <v>22</v>
+      </c>
+      <c r="F12" t="n">
         <v>12</v>
       </c>
-      <c r="E12" t="n">
-        <v>17</v>
-      </c>
-      <c r="F12" t="n">
-        <v>11</v>
-      </c>
       <c r="G12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K12" t="n">
         <v>10</v>
-      </c>
-      <c r="J12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K12" t="n">
-        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -2091,7 +2091,7 @@
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2103,52 +2103,52 @@
         <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="U12" t="n">
         <v>10</v>
       </c>
       <c r="V12" t="n">
+        <v>10</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB12" t="n">
         <v>8</v>
       </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
+      <c r="AC12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="AE12" t="n">
         <v>3</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2</v>
-      </c>
       <c r="AF12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AH12" t="n">
         <v>2</v>
@@ -2160,51 +2160,51 @@
         <v>0.667</v>
       </c>
       <c r="AK12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.346</v>
+        <v>0.333</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>118:40</t>
+          <t>139:27</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>55.4</v>
+        <v>65.28</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.645</v>
+        <v>0.622</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.173</v>
+        <v>1.149</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.09</v>
+        <v>0.077</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.174</v>
+        <v>0.164</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.227</v>
+        <v>0.226</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.012</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.057</v>
+        <v>0.082</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.051</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="13">
@@ -2214,40 +2214,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J13" t="n">
+        <v>18</v>
+      </c>
+      <c r="K13" t="n">
         <v>16</v>
-      </c>
-      <c r="K13" t="n">
-        <v>15</v>
       </c>
       <c r="L13" t="n">
         <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
@@ -2262,13 +2262,13 @@
         <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U13" t="n">
         <v>2</v>
@@ -2277,19 +2277,19 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AB13" t="n">
         <v>1</v>
@@ -2322,48 +2322,48 @@
         <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.4</v>
+        <v>0.222</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>106:10</t>
+          <t>126:38</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>27.52</v>
+        <v>33.4</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.472</v>
+        <v>0.413</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.534</v>
+        <v>0.474</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.836</v>
+        <v>0.778</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.218</v>
+        <v>0.18</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.333</v>
+        <v>0.304</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.667</v>
+        <v>3</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.126</v>
+        <v>0.127</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.039</v>
+        <v>0.031</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.159</v>
+        <v>0.145</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2373,16 +2373,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2397,13 +2397,13 @@
         <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
@@ -2415,19 +2415,19 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
@@ -2442,87 +2442,87 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.533</v>
+        <v>0.526</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>63:22</t>
+        </is>
+      </c>
+      <c r="AO14" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AU14" t="n">
         <v>1</v>
       </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>51:12</t>
-        </is>
-      </c>
-      <c r="AO14" t="n">
-        <v>18.64</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.019</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
       <c r="AV14" t="n">
-        <v>0.177</v>
+        <v>0.187</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.108</v>
+        <v>0.142</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.198</v>
+        <v>0.217</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="15">
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.241</v>
+        <v>0.238</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.278</v>
+        <v>0.283</v>
       </c>
       <c r="AY15" t="n">
         <v>0.004</v>
@@ -2691,43 +2691,43 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>49</v>
+      </c>
+      <c r="D16" t="n">
+        <v>21</v>
+      </c>
+      <c r="E16" t="n">
+        <v>29</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>7</v>
       </c>
-      <c r="C16" t="n">
-        <v>46</v>
-      </c>
-      <c r="D16" t="n">
-        <v>20</v>
-      </c>
-      <c r="E16" t="n">
-        <v>28</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>6</v>
-      </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L16" t="n">
         <v>11</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2739,16 +2739,16 @@
         <v>3</v>
       </c>
       <c r="R16" t="n">
+        <v>14</v>
+      </c>
+      <c r="S16" t="n">
         <v>12</v>
       </c>
-      <c r="S16" t="n">
-        <v>11</v>
-      </c>
       <c r="T16" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="U16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V16" t="n">
         <v>11</v>
@@ -2769,13 +2769,13 @@
         <v>0.917</v>
       </c>
       <c r="AB16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.615</v>
+        <v>0.643</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2806,38 +2806,38 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>101:41</t>
+          <t>111:14</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>36.28</v>
+        <v>38.16</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.714</v>
+        <v>0.724</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.697</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.268</v>
+        <v>1.284</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.083</v>
+        <v>0.079</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.214</v>
+        <v>0.241</v>
       </c>
       <c r="AU16" t="n">
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.174</v>
+        <v>0.165</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.149</v>
+        <v>0.128</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.255</v>
+        <v>0.247</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -2850,31 +2850,31 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" t="n">
+        <v>86</v>
+      </c>
+      <c r="D17" t="n">
         <v>7</v>
       </c>
-      <c r="C17" t="n">
-        <v>72</v>
-      </c>
-      <c r="D17" t="n">
-        <v>4</v>
-      </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H17" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K17" t="n">
         <v>8</v>
@@ -2886,7 +2886,7 @@
         <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2898,13 +2898,13 @@
         <v>14</v>
       </c>
       <c r="R17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S17" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="T17" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="U17" t="n">
         <v>7</v>
@@ -2913,19 +2913,19 @@
         <v>4</v>
       </c>
       <c r="W17" t="n">
+        <v>6</v>
+      </c>
+      <c r="X17" t="n">
         <v>3</v>
       </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
       <c r="Y17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1</v>
+        <v>0.778</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2955,51 +2955,51 @@
         <v>1</v>
       </c>
       <c r="AK17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL17" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.556</v>
+        <v>0.533</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>104:49</t>
+          <t>118:08</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>56.92</v>
+        <v>67.12</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.8</v>
+        <v>0.756</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.839</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.265</v>
+        <v>1.281</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.246</v>
+        <v>0.209</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.457</v>
+        <v>0.488</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.5</v>
+        <v>1.786</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.265</v>
+        <v>0.274</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.097</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="18">
@@ -3009,22 +3009,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F18" t="n">
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H18" t="n">
         <v>16</v>
@@ -3036,10 +3036,10 @@
         <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M18" t="n">
         <v>8</v>
@@ -3057,19 +3057,19 @@
         <v>13</v>
       </c>
       <c r="R18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S18" t="n">
         <v>24</v>
       </c>
       <c r="T18" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="U18" t="n">
         <v>18</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W18" t="n">
         <v>5</v>
@@ -3078,13 +3078,13 @@
         <v>2</v>
       </c>
       <c r="Y18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.75</v>
+        <v>0.762</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -3099,10 +3099,10 @@
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AH18" t="n">
         <v>3</v>
@@ -3117,48 +3117,48 @@
         <v>15</v>
       </c>
       <c r="AL18" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>188:27</t>
+          <t>204:21</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>85.36</v>
+        <v>90.36</v>
       </c>
       <c r="AP18" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>0.672</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>0.705</v>
-      </c>
       <c r="AR18" t="n">
-        <v>1.195</v>
+        <v>1.151</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.152</v>
+        <v>0.144</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.25</v>
+        <v>0.232</v>
       </c>
       <c r="AU18" t="n">
         <v>0.538</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.221</v>
+        <v>0.213</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.037</v>
+        <v>0.05</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.132</v>
+        <v>0.134</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="19">
@@ -3168,16 +3168,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -3186,16 +3186,16 @@
         <v>9</v>
       </c>
       <c r="H19" t="n">
+        <v>25</v>
+      </c>
+      <c r="I19" t="n">
+        <v>31</v>
+      </c>
+      <c r="J19" t="n">
+        <v>18</v>
+      </c>
+      <c r="K19" t="n">
         <v>24</v>
-      </c>
-      <c r="I19" t="n">
-        <v>29</v>
-      </c>
-      <c r="J19" t="n">
-        <v>16</v>
-      </c>
-      <c r="K19" t="n">
-        <v>23</v>
       </c>
       <c r="L19" t="n">
         <v>14</v>
@@ -3204,7 +3204,7 @@
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3219,13 +3219,13 @@
         <v>8</v>
       </c>
       <c r="S19" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="T19" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V19" t="n">
         <v>17</v>
@@ -3237,22 +3237,22 @@
         <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Z19" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.576</v>
+        <v>0.59</v>
       </c>
       <c r="AB19" t="n">
         <v>3</v>
       </c>
       <c r="AC19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="AE19" t="n">
         <v>3</v>
@@ -3283,38 +3283,38 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>154:57</t>
+          <t>175:51</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>76.76000000000001</v>
+        <v>87.64</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.519</v>
+        <v>0.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.599</v>
+        <v>0.573</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.042</v>
+        <v>1.016</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.13</v>
+        <v>0.114</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.444</v>
+        <v>0.391</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.241</v>
+        <v>0.24</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.124</v>
+        <v>0.103</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.167</v>
+        <v>0.156</v>
       </c>
       <c r="AY19" t="n">
         <v>0.076</v>
@@ -3327,22 +3327,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H20" t="n">
         <v>5</v>
@@ -3354,64 +3354,64 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L20" t="n">
+        <v>8</v>
+      </c>
+      <c r="M20" t="n">
         <v>6</v>
       </c>
-      <c r="M20" t="n">
-        <v>4</v>
-      </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
       </c>
       <c r="T20" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.786</v>
+        <v>0.789</v>
       </c>
       <c r="AB20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3423,60 +3423,60 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AK20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>152:50</t>
+          <t>176:33</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>39.2</v>
+        <v>51.2</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.843</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.633</v>
+        <v>1.563</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.051</v>
+        <v>0.059</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.143</v>
+        <v>0.109</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.5</v>
+        <v>1.667</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.125</v>
+        <v>0.14</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.054</v>
+        <v>0.058</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.096</v>
+        <v>0.091</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.024</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="21">
@@ -3486,38 +3486,38 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>21</v>
+      </c>
+      <c r="L21" t="n">
         <v>7</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>19</v>
-      </c>
-      <c r="L21" t="n">
-        <v>6</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -3528,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3645,153 +3645,153 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>673</v>
+        <v>748</v>
       </c>
       <c r="D22" t="n">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="E22" t="n">
-        <v>274</v>
+        <v>327</v>
       </c>
       <c r="F22" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G22" t="n">
+        <v>186</v>
+      </c>
+      <c r="H22" t="n">
+        <v>130</v>
+      </c>
+      <c r="I22" t="n">
         <v>165</v>
       </c>
-      <c r="H22" t="n">
-        <v>119</v>
-      </c>
-      <c r="I22" t="n">
-        <v>148</v>
-      </c>
       <c r="J22" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="K22" t="n">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="L22" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="M22" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N22" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="Q22" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="R22" t="n">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="S22" t="n">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="T22" t="n">
-        <v>797</v>
+        <v>878</v>
       </c>
       <c r="U22" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="V22" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="W22" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="X22" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Y22" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="Z22" t="n">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.679</v>
       </c>
       <c r="AB22" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AC22" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.462</v>
+        <v>0.433</v>
       </c>
       <c r="AE22" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AF22" t="n">
+        <v>74</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="AK22" t="n">
         <v>69</v>
       </c>
-      <c r="AG22" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>66</v>
-      </c>
       <c r="AL22" t="n">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.465</v>
+        <v>0.431</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>1425:00</t>
+          <t>1625:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>585.12</v>
+        <v>674.6</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.631</v>
+        <v>0.602</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.667</v>
+        <v>0.639</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.15</v>
+        <v>1.109</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.138</v>
+        <v>0.132</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.271</v>
+        <v>0.253</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.37</v>
+        <v>1.416</v>
       </c>
       <c r="AV22" t="n">
         <v>0.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.151</v>
+        <v>0.149</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -3804,153 +3804,153 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>578</v>
+        <v>680</v>
       </c>
       <c r="D23" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="E23" t="n">
-        <v>277</v>
+        <v>320</v>
       </c>
       <c r="F23" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="G23" t="n">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="H23" t="n">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="I23" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="J23" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="K23" t="n">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="L23" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="M23" t="n">
+        <v>46</v>
+      </c>
+      <c r="N23" t="n">
+        <v>40</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>72</v>
+      </c>
+      <c r="R23" t="n">
+        <v>172</v>
+      </c>
+      <c r="S23" t="n">
+        <v>164</v>
+      </c>
+      <c r="T23" t="n">
+        <v>733</v>
+      </c>
+      <c r="U23" t="n">
+        <v>86</v>
+      </c>
+      <c r="V23" t="n">
+        <v>73</v>
+      </c>
+      <c r="W23" t="n">
+        <v>44</v>
+      </c>
+      <c r="X23" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>102</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>148</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>41</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>92</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI23" t="n">
         <v>43</v>
       </c>
-      <c r="N23" t="n">
-        <v>33</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>61</v>
-      </c>
-      <c r="R23" t="n">
-        <v>153</v>
-      </c>
-      <c r="S23" t="n">
-        <v>146</v>
-      </c>
-      <c r="T23" t="n">
-        <v>602</v>
-      </c>
-      <c r="U23" t="n">
-        <v>76</v>
-      </c>
-      <c r="V23" t="n">
-        <v>63</v>
-      </c>
-      <c r="W23" t="n">
-        <v>36</v>
-      </c>
-      <c r="X23" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>86</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>126</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>37</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>69</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>82</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>34</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>0.382</v>
+        <v>0.419</v>
       </c>
       <c r="AK23" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AL23" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.292</v>
+        <v>0.307</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>1425:00</t>
+          <t>1625:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>592.64</v>
+        <v>677.3200000000001</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.51</v>
+        <v>0.526</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.553</v>
+        <v>0.57</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.975</v>
+        <v>1.004</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.118</v>
+        <v>0.12</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.224</v>
+        <v>0.233</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.443</v>
+        <v>1.494</v>
       </c>
       <c r="AV23" t="n">
         <v>0.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.141</v>
+        <v>0.14</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -4020,156 +4020,156 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" t="n">
-        <v>12.286</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>2.857</v>
+        <v>2.625</v>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>6.125</v>
       </c>
       <c r="F25" t="n">
-        <v>1.571</v>
+        <v>1.375</v>
       </c>
       <c r="G25" t="n">
-        <v>3.571</v>
+        <v>3.375</v>
       </c>
       <c r="H25" t="n">
-        <v>1.857</v>
+        <v>1.625</v>
       </c>
       <c r="I25" t="n">
-        <v>2.143</v>
+        <v>1.875</v>
       </c>
       <c r="J25" t="n">
-        <v>2.143</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>1.286</v>
+        <v>1.25</v>
       </c>
       <c r="L25" t="n">
-        <v>0.429</v>
+        <v>0.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N25" t="n">
-        <v>0.143</v>
+        <v>0.25</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.429</v>
+        <v>1.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.429</v>
+        <v>1.5</v>
       </c>
       <c r="R25" t="n">
-        <v>2.714</v>
+        <v>2.5</v>
       </c>
       <c r="S25" t="n">
-        <v>1.857</v>
+        <v>1.875</v>
       </c>
       <c r="T25" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="U25" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="W25" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="X25" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.714</v>
+        <v>0.75</v>
       </c>
       <c r="Z25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.714</v>
+        <v>0.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.286</v>
+        <v>1.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.222</v>
+        <v>0.167</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.857</v>
+        <v>1.625</v>
       </c>
       <c r="AF25" t="n">
-        <v>3.714</v>
+        <v>3.375</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.5</v>
+        <v>0.481</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.571</v>
+        <v>0.625</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.429</v>
+        <v>1.25</v>
       </c>
       <c r="AL25" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.476</v>
+        <v>0.455</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>23:06</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>11.943</v>
+        <v>11.825</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.545</v>
+        <v>0.493</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.584</v>
+        <v>0.533</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.029</v>
+        <v>0.93</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.12</v>
+        <v>0.127</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.194</v>
+        <v>0.171</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.5</v>
+        <v>1.333</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.252</v>
+        <v>0.247</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.063</v>
+        <v>0.062</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.073</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="26">
@@ -4179,22 +4179,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" t="n">
-        <v>3.143</v>
+        <v>2.75</v>
       </c>
       <c r="D26" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="E26" t="n">
-        <v>0.714</v>
+        <v>0.75</v>
       </c>
       <c r="F26" t="n">
-        <v>0.857</v>
+        <v>0.75</v>
       </c>
       <c r="G26" t="n">
-        <v>1.714</v>
+        <v>1.5</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -4203,40 +4203,40 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1.286</v>
+        <v>1.125</v>
       </c>
       <c r="K26" t="n">
-        <v>1.857</v>
+        <v>1.625</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.857</v>
+        <v>0.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.857</v>
+        <v>0.75</v>
       </c>
       <c r="R26" t="n">
-        <v>2.143</v>
+        <v>1.875</v>
       </c>
       <c r="S26" t="n">
-        <v>0.286</v>
+        <v>0.375</v>
       </c>
       <c r="T26" t="n">
         <v>22</v>
       </c>
       <c r="U26" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4248,19 +4248,19 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.429</v>
+        <v>0.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -4284,33 +4284,33 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.857</v>
+        <v>0.75</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.714</v>
+        <v>1.5</v>
       </c>
       <c r="AM26" t="n">
         <v>0.5</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>3.286</v>
+        <v>3</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.647</v>
+        <v>0.611</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.647</v>
+        <v>0.611</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.957</v>
+        <v>0.917</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.261</v>
+        <v>0.25</v>
       </c>
       <c r="AT26" t="n">
         <v>0</v>
@@ -4319,16 +4319,16 @@
         <v>1.5</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.117</v>
+        <v>0.116</v>
       </c>
       <c r="AW26" t="n">
         <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.153</v>
+        <v>0.15</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.039</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="27">
@@ -4338,156 +4338,156 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>4.286</v>
+        <v>4.375</v>
       </c>
       <c r="D27" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>1.571</v>
+        <v>1.875</v>
       </c>
       <c r="F27" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="G27" t="n">
-        <v>1.286</v>
+        <v>1.25</v>
       </c>
       <c r="H27" t="n">
-        <v>0.857</v>
+        <v>0.875</v>
       </c>
       <c r="I27" t="n">
-        <v>1.143</v>
+        <v>1.25</v>
       </c>
       <c r="J27" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="K27" t="n">
-        <v>1.857</v>
+        <v>2.125</v>
       </c>
       <c r="L27" t="n">
-        <v>0.143</v>
+        <v>0.375</v>
       </c>
       <c r="M27" t="n">
-        <v>0.857</v>
+        <v>0.75</v>
       </c>
       <c r="N27" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="R27" t="n">
-        <v>1.714</v>
+        <v>1.625</v>
       </c>
       <c r="S27" t="n">
-        <v>0.571</v>
+        <v>0.625</v>
       </c>
       <c r="T27" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="U27" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0.429</v>
+        <v>0.625</v>
       </c>
       <c r="X27" t="n">
-        <v>0.143</v>
+        <v>0.25</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.429</v>
+        <v>0.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.571</v>
+        <v>0.625</v>
       </c>
       <c r="AA27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI27" t="n">
         <v>0.75</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0.857</v>
       </c>
       <c r="AJ27" t="n">
         <v>0.333</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.429</v>
+        <v>0.5</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>3.789</v>
+        <v>4.05</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.638</v>
+        <v>0.595</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.131</v>
+        <v>1.08</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.113</v>
+        <v>0.093</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="AU27" t="n">
         <v>1.333</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.125</v>
+        <v>0.124</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.013</v>
+        <v>0.031</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.142</v>
+        <v>0.154</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="28">
@@ -4497,13 +4497,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C28" t="n">
-        <v>8.856999999999999</v>
+        <v>8.625</v>
       </c>
       <c r="D28" t="n">
-        <v>3.286</v>
+        <v>3.25</v>
       </c>
       <c r="E28" t="n">
         <v>5</v>
@@ -4512,86 +4512,86 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="H28" t="n">
-        <v>2.286</v>
+        <v>2.125</v>
       </c>
       <c r="I28" t="n">
-        <v>2.571</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.857</v>
+        <v>0.75</v>
       </c>
       <c r="K28" t="n">
-        <v>2.429</v>
+        <v>2.125</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="M28" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="R28" t="n">
-        <v>2.571</v>
+        <v>2.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.571</v>
+        <v>2.375</v>
       </c>
       <c r="T28" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U28" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="V28" t="n">
-        <v>0.857</v>
+        <v>1.25</v>
       </c>
       <c r="W28" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="X28" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.429</v>
+        <v>0.625</v>
       </c>
       <c r="Z28" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AA28" t="n">
         <v>0.714</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AB28" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG28" t="n">
         <v>0.6</v>
       </c>
-      <c r="AB28" t="n">
-        <v>1.143</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.571</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.714</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.714</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0.632</v>
-      </c>
       <c r="AH28" t="n">
         <v>0</v>
       </c>
@@ -4605,48 +4605,48 @@
         <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AM28" t="n">
         <v>0</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>6.846</v>
+        <v>6.725</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.622</v>
+        <v>0.619</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.679</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.294</v>
+        <v>1.283</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.063</v>
+        <v>0.056</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.432</v>
+        <v>0.405</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.173</v>
+        <v>0.174</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.142</v>
+        <v>0.131</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="29">
@@ -4656,67 +4656,67 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C29" t="n">
-        <v>9.286</v>
+        <v>9.375</v>
       </c>
       <c r="D29" t="n">
-        <v>1.714</v>
+        <v>1.875</v>
       </c>
       <c r="E29" t="n">
-        <v>2.429</v>
+        <v>2.75</v>
       </c>
       <c r="F29" t="n">
-        <v>1.571</v>
+        <v>1.5</v>
       </c>
       <c r="G29" t="n">
-        <v>4.143</v>
+        <v>4.125</v>
       </c>
       <c r="H29" t="n">
-        <v>1.143</v>
+        <v>1.125</v>
       </c>
       <c r="I29" t="n">
-        <v>1.429</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
-        <v>1.571</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.857</v>
+        <v>1.25</v>
       </c>
       <c r="L29" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="M29" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.714</v>
+        <v>0.625</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.714</v>
+        <v>0.625</v>
       </c>
       <c r="R29" t="n">
-        <v>1.286</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>1.571</v>
+        <v>1.5</v>
       </c>
       <c r="T29" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="U29" t="n">
-        <v>1.429</v>
+        <v>1.25</v>
       </c>
       <c r="V29" t="n">
-        <v>1.143</v>
+        <v>1.25</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -4725,87 +4725,87 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.429</v>
+        <v>0.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.429</v>
+        <v>0.625</v>
       </c>
       <c r="AA29" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AB29" t="n">
         <v>1</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.286</v>
+        <v>1.375</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.778</v>
+        <v>0.727</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.286</v>
+        <v>0.375</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.714</v>
+        <v>0.75</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="AJ29" t="n">
         <v>0.667</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.286</v>
+        <v>1.25</v>
       </c>
       <c r="AL29" t="n">
-        <v>3.714</v>
+        <v>3.75</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.346</v>
+        <v>0.333</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>7.914</v>
+        <v>8.16</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.645</v>
+        <v>0.622</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.173</v>
+        <v>1.149</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.09</v>
+        <v>0.077</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.174</v>
+        <v>0.164</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.227</v>
+        <v>0.226</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.012</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.057</v>
+        <v>0.082</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.051</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="30">
@@ -4815,156 +4815,156 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C30" t="n">
-        <v>3.833</v>
+        <v>3.714</v>
       </c>
       <c r="D30" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1.857</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>1.429</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>1.333</v>
+        <v>1.429</v>
       </c>
       <c r="J30" t="n">
-        <v>2.667</v>
+        <v>2.571</v>
       </c>
       <c r="K30" t="n">
-        <v>2.5</v>
+        <v>2.286</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="M30" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="N30" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="R30" t="n">
-        <v>1.833</v>
+        <v>1.857</v>
       </c>
       <c r="S30" t="n">
-        <v>1.167</v>
+        <v>1.286</v>
       </c>
       <c r="T30" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U30" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="X30" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.167</v>
+        <v>0.286</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.833</v>
+        <v>0.714</v>
       </c>
       <c r="AD30" t="n">
         <v>0.2</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AG30" t="n">
         <v>0.667</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AJ30" t="n">
         <v>1</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.833</v>
+        <v>1.286</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.4</v>
+        <v>0.222</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>4.587</v>
+        <v>4.771</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.472</v>
+        <v>0.413</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.534</v>
+        <v>0.474</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.836</v>
+        <v>0.778</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.218</v>
+        <v>0.18</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.333</v>
+        <v>0.304</v>
       </c>
       <c r="AU30" t="n">
-        <v>2.667</v>
+        <v>3</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.126</v>
+        <v>0.127</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.039</v>
+        <v>0.031</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.159</v>
+        <v>0.145</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.082</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="31">
@@ -4974,16 +4974,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C31" t="n">
-        <v>2.714</v>
+        <v>2.875</v>
       </c>
       <c r="D31" t="n">
-        <v>1.143</v>
+        <v>1.25</v>
       </c>
       <c r="E31" t="n">
-        <v>2.286</v>
+        <v>2.625</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4992,138 +4992,138 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="I31" t="n">
-        <v>0.857</v>
+        <v>0.75</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="K31" t="n">
-        <v>1.286</v>
+        <v>1.5</v>
       </c>
       <c r="L31" t="n">
-        <v>0.571</v>
+        <v>0.875</v>
       </c>
       <c r="M31" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T31" t="n">
+        <v>37</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="AO31" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AT31" t="n">
         <v>0.143</v>
       </c>
-      <c r="N31" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1.143</v>
-      </c>
-      <c r="T31" t="n">
-        <v>29</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.143</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.143</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="AO31" t="n">
-        <v>2.663</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.019</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0.188</v>
-      </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.177</v>
+        <v>0.187</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.108</v>
+        <v>0.142</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.198</v>
+        <v>0.217</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="32">
@@ -5273,16 +5273,16 @@
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.241</v>
+        <v>0.238</v>
       </c>
       <c r="AW32" t="n">
         <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.278</v>
+        <v>0.283</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="33">
@@ -5292,16 +5292,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33" t="n">
-        <v>6.571</v>
+        <v>6.125</v>
       </c>
       <c r="D33" t="n">
-        <v>2.857</v>
+        <v>2.625</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>3.625</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -5310,49 +5310,49 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.857</v>
+        <v>0.875</v>
       </c>
       <c r="I33" t="n">
-        <v>1.714</v>
+        <v>1.75</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>3.286</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>1.571</v>
+        <v>1.375</v>
       </c>
       <c r="M33" t="n">
-        <v>0.143</v>
+        <v>0.25</v>
       </c>
       <c r="N33" t="n">
-        <v>0.429</v>
+        <v>0.5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="R33" t="n">
-        <v>1.714</v>
+        <v>1.75</v>
       </c>
       <c r="S33" t="n">
-        <v>1.571</v>
+        <v>1.5</v>
       </c>
       <c r="T33" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="U33" t="n">
-        <v>0.571</v>
+        <v>0.625</v>
       </c>
       <c r="V33" t="n">
-        <v>1.571</v>
+        <v>1.375</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -5361,28 +5361,28 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.571</v>
+        <v>1.375</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.714</v>
+        <v>1.5</v>
       </c>
       <c r="AA33" t="n">
         <v>0.917</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.143</v>
+        <v>1.125</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.857</v>
+        <v>1.75</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.615</v>
+        <v>0.643</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="AG33" t="n">
         <v>0.333</v>
@@ -5407,38 +5407,38 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>5.183</v>
+        <v>4.77</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.714</v>
+        <v>0.724</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.697</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.268</v>
+        <v>1.284</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.083</v>
+        <v>0.079</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.214</v>
+        <v>0.241</v>
       </c>
       <c r="AU33" t="n">
         <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.174</v>
+        <v>0.165</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.149</v>
+        <v>0.128</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.255</v>
+        <v>0.247</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -5451,88 +5451,88 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C34" t="n">
-        <v>10.286</v>
+        <v>10.75</v>
       </c>
       <c r="D34" t="n">
-        <v>0.571</v>
+        <v>0.875</v>
       </c>
       <c r="E34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.875</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="K34" t="n">
         <v>1</v>
       </c>
-      <c r="F34" t="n">
-        <v>2.286</v>
-      </c>
-      <c r="G34" t="n">
-        <v>4</v>
-      </c>
-      <c r="H34" t="n">
-        <v>2.286</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.571</v>
-      </c>
-      <c r="J34" t="n">
-        <v>3</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1.143</v>
-      </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R34" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" t="n">
-        <v>2</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.857</v>
-      </c>
       <c r="S34" t="n">
-        <v>2.429</v>
+        <v>2.75</v>
       </c>
       <c r="T34" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="V34" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="W34" t="n">
-        <v>0.429</v>
+        <v>0.75</v>
       </c>
       <c r="X34" t="n">
-        <v>0.143</v>
+        <v>0.375</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.571</v>
+        <v>0.875</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.571</v>
+        <v>1.125</v>
       </c>
       <c r="AA34" t="n">
-        <v>1</v>
+        <v>0.778</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -5541,66 +5541,66 @@
         <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="AJ34" t="n">
         <v>1</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.143</v>
+        <v>2</v>
       </c>
       <c r="AL34" t="n">
-        <v>3.857</v>
+        <v>3.75</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.556</v>
+        <v>0.533</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>8.131</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.8</v>
+        <v>0.756</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.839</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.265</v>
+        <v>1.281</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.246</v>
+        <v>0.209</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.457</v>
+        <v>0.488</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.5</v>
+        <v>1.786</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.265</v>
+        <v>0.274</v>
       </c>
       <c r="AW34" t="n">
         <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.097</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="35">
@@ -5610,156 +5610,156 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C35" t="n">
-        <v>14.571</v>
+        <v>13</v>
       </c>
       <c r="D35" t="n">
-        <v>2.286</v>
+        <v>2.125</v>
       </c>
       <c r="E35" t="n">
-        <v>4.286</v>
+        <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>2.571</v>
+        <v>2.25</v>
       </c>
       <c r="G35" t="n">
-        <v>4.857</v>
+        <v>4.625</v>
       </c>
       <c r="H35" t="n">
-        <v>2.286</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>2.714</v>
+        <v>2.375</v>
       </c>
       <c r="J35" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>3.143</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.714</v>
-      </c>
       <c r="M35" t="n">
-        <v>1.143</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.857</v>
+        <v>1.625</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.857</v>
+        <v>1.625</v>
       </c>
       <c r="R35" t="n">
-        <v>2.143</v>
+        <v>2.125</v>
       </c>
       <c r="S35" t="n">
-        <v>3.429</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="U35" t="n">
-        <v>2.571</v>
+        <v>2.25</v>
       </c>
       <c r="V35" t="n">
-        <v>1.143</v>
+        <v>1.25</v>
       </c>
       <c r="W35" t="n">
-        <v>0.714</v>
+        <v>0.625</v>
       </c>
       <c r="X35" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.143</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.857</v>
+        <v>2.625</v>
       </c>
       <c r="AA35" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
         <v>0.75</v>
       </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0.857</v>
-      </c>
       <c r="AD35" t="n">
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.571</v>
+        <v>0.625</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="AJ35" t="n">
         <v>0.75</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.143</v>
+        <v>1.875</v>
       </c>
       <c r="AL35" t="n">
-        <v>4.286</v>
+        <v>4.125</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>26:55</t>
+          <t>25:32</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>12.194</v>
+        <v>11.295</v>
       </c>
       <c r="AP35" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="AQ35" t="n">
         <v>0.672</v>
       </c>
-      <c r="AQ35" t="n">
-        <v>0.705</v>
-      </c>
       <c r="AR35" t="n">
-        <v>1.195</v>
+        <v>1.151</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.152</v>
+        <v>0.144</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.25</v>
+        <v>0.232</v>
       </c>
       <c r="AU35" t="n">
         <v>0.538</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.221</v>
+        <v>0.213</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.037</v>
+        <v>0.05</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.132</v>
+        <v>0.134</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="36">
@@ -5769,97 +5769,97 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C36" t="n">
-        <v>11.429</v>
+        <v>11.125</v>
       </c>
       <c r="D36" t="n">
-        <v>3.571</v>
+        <v>3.625</v>
       </c>
       <c r="E36" t="n">
-        <v>6.429</v>
+        <v>6.875</v>
       </c>
       <c r="F36" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="G36" t="n">
-        <v>1.286</v>
+        <v>1.125</v>
       </c>
       <c r="H36" t="n">
-        <v>3.429</v>
+        <v>3.125</v>
       </c>
       <c r="I36" t="n">
-        <v>4.143</v>
+        <v>3.875</v>
       </c>
       <c r="J36" t="n">
-        <v>2.286</v>
+        <v>2.25</v>
       </c>
       <c r="K36" t="n">
-        <v>3.286</v>
+        <v>3</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="M36" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="N36" t="n">
-        <v>1.714</v>
+        <v>1.75</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.429</v>
+        <v>1.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.429</v>
+        <v>1.25</v>
       </c>
       <c r="R36" t="n">
-        <v>1.143</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>3.857</v>
+        <v>3.75</v>
       </c>
       <c r="T36" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="U36" t="n">
-        <v>0.286</v>
+        <v>0.75</v>
       </c>
       <c r="V36" t="n">
-        <v>2.429</v>
+        <v>2.125</v>
       </c>
       <c r="W36" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="X36" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.714</v>
+        <v>2.875</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.714</v>
+        <v>4.875</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.576</v>
+        <v>0.59</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.143</v>
+        <v>1.5</v>
       </c>
       <c r="AD36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE36" t="n">
         <v>0.375</v>
       </c>
-      <c r="AE36" t="n">
-        <v>0.429</v>
-      </c>
       <c r="AF36" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="AG36" t="n">
         <v>0.75</v>
@@ -5874,48 +5874,48 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.286</v>
+        <v>1.125</v>
       </c>
       <c r="AM36" t="n">
         <v>0.222</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>10.966</v>
+        <v>10.955</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.519</v>
+        <v>0.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.599</v>
+        <v>0.573</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.042</v>
+        <v>1.016</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.13</v>
+        <v>0.114</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.444</v>
+        <v>0.391</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.241</v>
+        <v>0.24</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.124</v>
+        <v>0.103</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.167</v>
+        <v>0.156</v>
       </c>
       <c r="AY36" t="n">
         <v>0.076</v>
@@ -5928,156 +5928,156 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C37" t="n">
-        <v>9.143000000000001</v>
+        <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>2.286</v>
+        <v>2.625</v>
       </c>
       <c r="E37" t="n">
-        <v>3.429</v>
+        <v>3.875</v>
       </c>
       <c r="F37" t="n">
-        <v>1.286</v>
+        <v>1.375</v>
       </c>
       <c r="G37" t="n">
-        <v>1.571</v>
+        <v>1.875</v>
       </c>
       <c r="H37" t="n">
-        <v>0.714</v>
+        <v>0.625</v>
       </c>
       <c r="I37" t="n">
-        <v>0.714</v>
+        <v>0.625</v>
       </c>
       <c r="J37" t="n">
-        <v>0.714</v>
+        <v>0.625</v>
       </c>
       <c r="K37" t="n">
-        <v>1.857</v>
+        <v>1.75</v>
       </c>
       <c r="L37" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0.571</v>
+        <v>0.75</v>
       </c>
       <c r="N37" t="n">
-        <v>0.143</v>
+        <v>0.25</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.286</v>
+        <v>0.375</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.286</v>
+        <v>0.375</v>
       </c>
       <c r="R37" t="n">
-        <v>1.429</v>
+        <v>1.5</v>
       </c>
       <c r="S37" t="n">
-        <v>0.714</v>
+        <v>0.625</v>
       </c>
       <c r="T37" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.571</v>
+        <v>1.875</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>2.375</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.786</v>
+        <v>0.789</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.714</v>
+        <v>0.75</v>
       </c>
       <c r="AC37" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.571</v>
+        <v>0.625</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.571</v>
+        <v>0.75</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.714</v>
+        <v>0.75</v>
       </c>
       <c r="AL37" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.843</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.633</v>
+        <v>1.563</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.051</v>
+        <v>0.059</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.143</v>
+        <v>0.109</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.5</v>
+        <v>1.667</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.125</v>
+        <v>0.14</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.054</v>
+        <v>0.058</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.096</v>
+        <v>0.091</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.024</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="38">
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -6114,10 +6114,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2.714</v>
+        <v>2.625</v>
       </c>
       <c r="L38" t="n">
-        <v>0.857</v>
+        <v>0.875</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -6129,7 +6129,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.857</v>
+        <v>1.25</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6246,153 +6246,153 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>96.143</v>
+        <v>93.5</v>
       </c>
       <c r="D39" t="n">
-        <v>22.429</v>
+        <v>22.875</v>
       </c>
       <c r="E39" t="n">
-        <v>39.143</v>
+        <v>40.875</v>
       </c>
       <c r="F39" t="n">
-        <v>11.429</v>
+        <v>10.5</v>
       </c>
       <c r="G39" t="n">
-        <v>23.571</v>
+        <v>23.25</v>
       </c>
       <c r="H39" t="n">
-        <v>17</v>
+        <v>16.25</v>
       </c>
       <c r="I39" t="n">
-        <v>21.143</v>
+        <v>20.625</v>
       </c>
       <c r="J39" t="n">
-        <v>15.857</v>
+        <v>15.75</v>
       </c>
       <c r="K39" t="n">
-        <v>27.286</v>
+        <v>26.375</v>
       </c>
       <c r="L39" t="n">
-        <v>8.714</v>
+        <v>9.375</v>
       </c>
       <c r="M39" t="n">
-        <v>5.571</v>
+        <v>5.625</v>
       </c>
       <c r="N39" t="n">
-        <v>4.857</v>
+        <v>5.125</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>11.571</v>
+        <v>11.125</v>
       </c>
       <c r="Q39" t="n">
-        <v>10.714</v>
+        <v>9.875</v>
       </c>
       <c r="R39" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="S39" t="n">
-        <v>21</v>
+        <v>20.75</v>
       </c>
       <c r="T39" t="n">
-        <v>797</v>
+        <v>878</v>
       </c>
       <c r="U39" t="n">
-        <v>8.429</v>
+        <v>8.875</v>
       </c>
       <c r="V39" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="W39" t="n">
-        <v>3.429</v>
+        <v>4</v>
       </c>
       <c r="X39" t="n">
-        <v>2</v>
+        <v>2.375</v>
       </c>
       <c r="Y39" t="n">
-        <v>12.286</v>
+        <v>13.25</v>
       </c>
       <c r="Z39" t="n">
-        <v>17.857</v>
+        <v>19.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.679</v>
       </c>
       <c r="AB39" t="n">
-        <v>5.286</v>
+        <v>5.25</v>
       </c>
       <c r="AC39" t="n">
-        <v>11.429</v>
+        <v>12.125</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.462</v>
+        <v>0.433</v>
       </c>
       <c r="AE39" t="n">
-        <v>4.857</v>
+        <v>4.375</v>
       </c>
       <c r="AF39" t="n">
-        <v>9.856999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.493</v>
+        <v>0.473</v>
       </c>
       <c r="AH39" t="n">
-        <v>2</v>
+        <v>1.875</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.286</v>
+        <v>3.25</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.609</v>
+        <v>0.577</v>
       </c>
       <c r="AK39" t="n">
-        <v>9.429</v>
+        <v>8.625</v>
       </c>
       <c r="AL39" t="n">
-        <v>20.286</v>
+        <v>20</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.465</v>
+        <v>0.431</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>203:34</t>
+          <t>203:07</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>83.589</v>
+        <v>84.325</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.631</v>
+        <v>0.602</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.667</v>
+        <v>0.639</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.15</v>
+        <v>1.109</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.138</v>
+        <v>0.132</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.271</v>
+        <v>0.253</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.37</v>
+        <v>1.416</v>
       </c>
       <c r="AV39" t="n">
         <v>0.2</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.151</v>
+        <v>0.149</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -6405,153 +6405,153 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C40" t="n">
-        <v>82.571</v>
+        <v>85</v>
       </c>
       <c r="D40" t="n">
-        <v>21.429</v>
+        <v>21.875</v>
       </c>
       <c r="E40" t="n">
-        <v>39.571</v>
+        <v>40</v>
       </c>
       <c r="F40" t="n">
-        <v>8.286</v>
+        <v>8.625</v>
       </c>
       <c r="G40" t="n">
-        <v>26.857</v>
+        <v>26.125</v>
       </c>
       <c r="H40" t="n">
-        <v>14.857</v>
+        <v>15.375</v>
       </c>
       <c r="I40" t="n">
-        <v>18.714</v>
+        <v>19.125</v>
       </c>
       <c r="J40" t="n">
-        <v>14.429</v>
+        <v>15.125</v>
       </c>
       <c r="K40" t="n">
-        <v>20.857</v>
+        <v>22.125</v>
       </c>
       <c r="L40" t="n">
-        <v>8.856999999999999</v>
+        <v>9.125</v>
       </c>
       <c r="M40" t="n">
-        <v>6.143</v>
+        <v>5.75</v>
       </c>
       <c r="N40" t="n">
-        <v>4.714</v>
+        <v>5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
+        <v>10.125</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>9</v>
+      </c>
+      <c r="R40" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T40" t="n">
+        <v>733</v>
+      </c>
+      <c r="U40" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="V40" t="n">
+        <v>9.125</v>
+      </c>
+      <c r="W40" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>5.125</v>
+      </c>
+      <c r="AC40" t="n">
         <v>10</v>
       </c>
-      <c r="Q40" t="n">
-        <v>8.714</v>
-      </c>
-      <c r="R40" t="n">
-        <v>21.857</v>
-      </c>
-      <c r="S40" t="n">
-        <v>20.857</v>
-      </c>
-      <c r="T40" t="n">
-        <v>602</v>
-      </c>
-      <c r="U40" t="n">
-        <v>10.857</v>
-      </c>
-      <c r="V40" t="n">
-        <v>9</v>
-      </c>
-      <c r="W40" t="n">
-        <v>5.143</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>12.286</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>5.286</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>9.856999999999999</v>
-      </c>
       <c r="AD40" t="n">
-        <v>0.536</v>
+        <v>0.512</v>
       </c>
       <c r="AE40" t="n">
-        <v>3.857</v>
+        <v>4</v>
       </c>
       <c r="AF40" t="n">
-        <v>11.714</v>
+        <v>11.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.329</v>
+        <v>0.348</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.857</v>
+        <v>2.25</v>
       </c>
       <c r="AI40" t="n">
-        <v>4.857</v>
+        <v>5.375</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.382</v>
+        <v>0.419</v>
       </c>
       <c r="AK40" t="n">
-        <v>6.429</v>
+        <v>6.375</v>
       </c>
       <c r="AL40" t="n">
-        <v>22</v>
+        <v>20.75</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.292</v>
+        <v>0.307</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>203:34</t>
+          <t>203:07</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>84.663</v>
+        <v>84.66500000000001</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.51</v>
+        <v>0.526</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.553</v>
+        <v>0.57</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.975</v>
+        <v>1.004</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.118</v>
+        <v>0.12</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.224</v>
+        <v>0.233</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.443</v>
+        <v>1.494</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.203</v>
+        <v>0.201</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.115</v>
+        <v>0.125</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>

--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Barça.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Barça.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,212 +417,212 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>POSSind</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>POSSest</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>OER</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>DER</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>eFG%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>TOV%</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ORB%</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>FTR</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>TOpts</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2CPts</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>FastBPts</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>TOunf</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Rim FGM</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Rim FGA</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Rim_vol</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Paint FGM</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Paint FGA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Paint_vol</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>MR FGM</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>MR FGA</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>MR_vol</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Cor3 FGM</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Cor3 FGA</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Cor3_vol</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ATB3 FGM</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ATB3 FGA</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ATB3_vol</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Rim %</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Paint %</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>MR %</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Cor3 %</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ATB3 %</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Rim PPS</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>MR PPS</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>3P PPS</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>TOptsPPO</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>2CPtsPPO</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>FastBPtsPPO</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Ass/TO</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Sh/TO</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Gen/TO</t>
         </is>
@@ -647,127 +635,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>599.6</v>
+        <v>754.8800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>601.96</v>
+        <v>755.7400000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>124.2607482224733</v>
+        <v>120.6764231084764</v>
       </c>
       <c r="E2" t="n">
-        <v>112.9643165658848</v>
+        <v>115.9128800910366</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6023391812865497</v>
+        <v>0.59140625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1319300326119182</v>
+        <v>0.1383174918428146</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2976190476190476</v>
+        <v>0.2817337461300309</v>
       </c>
       <c r="I2" t="n">
-        <v>0.253411306042885</v>
+        <v>0.2421875</v>
       </c>
       <c r="J2" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="K2" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L2" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="M2" t="n">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="N2" t="n">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="O2" t="n">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="P2" t="n">
-        <v>0.304093567251462</v>
+        <v>0.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="R2" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="S2" t="n">
-        <v>0.189083820662768</v>
+        <v>0.175</v>
       </c>
       <c r="T2" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="U2" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1442495126705653</v>
+        <v>0.1375</v>
       </c>
       <c r="W2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.050682261208577</v>
+        <v>0.0625</v>
       </c>
       <c r="Z2" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="AA2" t="n">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3118908382066277</v>
+        <v>0.325</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.6794871794871795</v>
+        <v>0.671875</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4329896907216495</v>
+        <v>0.4553571428571428</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.472972972972973</v>
+        <v>0.4659090909090909</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.525</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.43125</v>
+        <v>0.4038461538461539</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.358974358974359</v>
+        <v>1.34375</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.9459459459459459</v>
+        <v>0.9318181818181818</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.354838709677419</v>
+        <v>1.270161290322581</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8765432098765432</v>
+        <v>0.8514851485148515</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.093333333333333</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.684210526315789</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.415730337078652</v>
+        <v>1.299145299145299</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.764044943820225</v>
+        <v>5.47008547008547</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.179775280898877</v>
+        <v>6.769230769230769</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +765,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.95</v>
+        <v>75.48800000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>75.245</v>
+        <v>75.57400000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>124.2607482224733</v>
+        <v>120.6764231084764</v>
       </c>
       <c r="E3" t="n">
-        <v>112.9643165658848</v>
+        <v>115.9128800910366</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6023391812865497</v>
+        <v>0.59140625</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1319300326119182</v>
+        <v>0.1383174918428146</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2976190476190476</v>
+        <v>0.281733746130031</v>
       </c>
       <c r="I3" t="n">
-        <v>0.253411306042885</v>
+        <v>0.2421875</v>
       </c>
       <c r="J3" t="n">
-        <v>8.875</v>
+        <v>8.6</v>
       </c>
       <c r="K3" t="n">
-        <v>10.25</v>
+        <v>9.1</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>9.875</v>
+        <v>10.5</v>
       </c>
       <c r="N3" t="n">
-        <v>13.25</v>
+        <v>12.9</v>
       </c>
       <c r="O3" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="P3" t="n">
-        <v>0.304093567251462</v>
+        <v>0.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="R3" t="n">
-        <v>12.125</v>
+        <v>11.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0.189083820662768</v>
+        <v>0.175</v>
       </c>
       <c r="T3" t="n">
-        <v>4.375</v>
+        <v>4.1</v>
       </c>
       <c r="U3" t="n">
-        <v>9.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1442495126705653</v>
+        <v>0.1375</v>
       </c>
       <c r="W3" t="n">
-        <v>1.875</v>
+        <v>2.1</v>
       </c>
       <c r="X3" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.050682261208577</v>
+        <v>0.0625</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.625</v>
+        <v>8.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3118908382066277</v>
+        <v>0.325</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.6794871794871795</v>
+        <v>0.671875</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4329896907216495</v>
+        <v>0.4553571428571428</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.472972972972973</v>
+        <v>0.4659090909090908</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.525</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.43125</v>
+        <v>0.4038461538461539</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.358974358974359</v>
+        <v>1.34375</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.9459459459459459</v>
+        <v>0.9318181818181817</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.354838709677419</v>
+        <v>1.270161290322581</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8765432098765432</v>
+        <v>0.8514851485148515</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.093333333333333</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.684210526315789</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.415730337078652</v>
+        <v>1.299145299145299</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.764044943820225</v>
+        <v>5.47008547008547</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.179775280898877</v>
+        <v>6.76923076923077</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +895,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>604.3200000000002</v>
+        <v>756.6000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>601.96</v>
+        <v>755.7400000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>112.9643165658848</v>
+        <v>115.9128800910366</v>
       </c>
       <c r="E4" t="n">
-        <v>124.2607482224733</v>
+        <v>120.6764231084764</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5264650283553876</v>
+        <v>0.5372023809523809</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1195889682867773</v>
+        <v>0.1179080084053234</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2570422535211268</v>
+        <v>0.2808988764044944</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2325141776937618</v>
+        <v>0.2291666666666667</v>
       </c>
       <c r="J4" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="K4" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L4" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="M4" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="N4" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="O4" t="n">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="P4" t="n">
-        <v>0.279773156899811</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="Q4" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="R4" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1512287334593573</v>
+        <v>0.1547619047619048</v>
       </c>
       <c r="T4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="U4" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.1636904761904762</v>
       </c>
       <c r="W4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="X4" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08128544423440454</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="Z4" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="AA4" t="n">
-        <v>166</v>
+        <v>206</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3137996219281664</v>
+        <v>0.3065476190476191</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.6891891891891891</v>
+        <v>0.6822916666666666</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5125</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3454545454545455</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4186046511627907</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3072289156626506</v>
+        <v>0.3203883495145631</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.378378378378378</v>
+        <v>1.364583333333333</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.6909090909090909</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.9904306220095693</v>
+        <v>1.037593984962406</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.9662921348314607</v>
+        <v>0.905982905982906</v>
       </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.62962962962963</v>
+        <v>1.647058823529412</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.493827160493827</v>
+        <v>1.534653465346535</v>
       </c>
       <c r="AO4" t="n">
-        <v>6.530864197530864</v>
+        <v>6.653465346534653</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.024691358024691</v>
+        <v>8.188118811881187</v>
       </c>
     </row>
     <row r="5">
@@ -1037,422 +1025,422 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75.54000000000002</v>
+        <v>75.66000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>75.245</v>
+        <v>75.57400000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>112.9643165658848</v>
+        <v>115.9128800910366</v>
       </c>
       <c r="E5" t="n">
-        <v>124.2607482224733</v>
+        <v>120.6764231084764</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5264650283553876</v>
+        <v>0.5372023809523809</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1195889682867773</v>
+        <v>0.1179080084053234</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2570422535211268</v>
+        <v>0.2808988764044943</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2325141776937618</v>
+        <v>0.2291666666666667</v>
       </c>
       <c r="J5" t="n">
-        <v>10.75</v>
+        <v>10.6</v>
       </c>
       <c r="K5" t="n">
-        <v>9.125</v>
+        <v>9.5</v>
       </c>
       <c r="L5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="N5" t="n">
-        <v>12.75</v>
+        <v>13.1</v>
       </c>
       <c r="O5" t="n">
-        <v>18.5</v>
+        <v>19.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0.279773156899811</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.125</v>
+        <v>5.4</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1512287334593573</v>
+        <v>0.1547619047619048</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.1636904761904762</v>
       </c>
       <c r="W5" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="X5" t="n">
-        <v>5.375</v>
+        <v>6</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08128544423440454</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.375</v>
+        <v>6.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.75</v>
+        <v>20.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3137996219281664</v>
+        <v>0.3065476190476191</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6891891891891891</v>
+        <v>0.6822916666666666</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5125</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3454545454545455</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4186046511627907</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3072289156626506</v>
+        <v>0.3203883495145631</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.378378378378378</v>
+        <v>1.364583333333333</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.6909090909090909</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9904306220095693</v>
+        <v>1.037593984962406</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.9662921348314607</v>
+        <v>0.905982905982906</v>
       </c>
       <c r="AL5" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.62962962962963</v>
+        <v>1.647058823529412</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.493827160493827</v>
+        <v>1.534653465346535</v>
       </c>
       <c r="AO5" t="n">
-        <v>6.530864197530864</v>
+        <v>6.653465346534654</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.024691358024691</v>
+        <v>8.188118811881189</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>2PM</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>2PA</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>3PM</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>3PA</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>FTM</t>
         </is>
       </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>FTA</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>AS</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>DRB</t>
         </is>
       </c>
-      <c r="L7" s="1" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>ORB</t>
         </is>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="N7" s="1" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>BLK</t>
         </is>
       </c>
-      <c r="O7" s="1" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>BLK A.</t>
         </is>
       </c>
-      <c r="P7" s="1" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="Q7" s="1" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>TOunf</t>
         </is>
       </c>
-      <c r="R7" s="1" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="S7" s="1" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>F+</t>
         </is>
       </c>
-      <c r="T7" s="1" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>EFI</t>
         </is>
       </c>
-      <c r="U7" s="1" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>TOpts</t>
         </is>
       </c>
-      <c r="V7" s="1" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>2CPts</t>
         </is>
       </c>
-      <c r="W7" s="1" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>FastBPts</t>
         </is>
       </c>
-      <c r="X7" s="1" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>FastB Opp</t>
         </is>
       </c>
-      <c r="Y7" s="1" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Rim FGM</t>
         </is>
       </c>
-      <c r="Z7" s="1" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Rim FGA</t>
         </is>
       </c>
-      <c r="AA7" s="1" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Rim %</t>
         </is>
       </c>
-      <c r="AB7" s="1" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Paint FGM</t>
         </is>
       </c>
-      <c r="AC7" s="1" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Paint FGA</t>
         </is>
       </c>
-      <c r="AD7" s="1" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Paint %</t>
         </is>
       </c>
-      <c r="AE7" s="1" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>MR FGM</t>
         </is>
       </c>
-      <c r="AF7" s="1" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>MR FGA</t>
         </is>
       </c>
-      <c r="AG7" s="1" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>MR %</t>
         </is>
       </c>
-      <c r="AH7" s="1" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>Cor3 FGM</t>
         </is>
       </c>
-      <c r="AI7" s="1" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>Cor3 FGA</t>
         </is>
       </c>
-      <c r="AJ7" s="1" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Cor3 %</t>
         </is>
       </c>
-      <c r="AK7" s="1" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>ATB3 FGM</t>
         </is>
       </c>
-      <c r="AL7" s="1" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>ATB3 FGA</t>
         </is>
       </c>
-      <c r="AM7" s="1" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>ATB3 %</t>
         </is>
       </c>
-      <c r="AN7" s="1" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="AO7" s="1" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>PLAYS</t>
         </is>
       </c>
-      <c r="AP7" s="1" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>eFG%</t>
         </is>
       </c>
-      <c r="AQ7" s="1" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>TS%</t>
         </is>
       </c>
-      <c r="AR7" s="1" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>PTS/PLAY</t>
         </is>
       </c>
-      <c r="AS7" s="1" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>TO%</t>
         </is>
       </c>
-      <c r="AT7" s="1" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>FTR</t>
         </is>
       </c>
-      <c r="AU7" s="1" t="inlineStr">
+      <c r="AU7" t="inlineStr">
         <is>
           <t>Ass/TO</t>
         </is>
       </c>
-      <c r="AV7" s="1" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>USG%</t>
         </is>
       </c>
-      <c r="AW7" s="1" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>OR%</t>
         </is>
       </c>
-      <c r="AX7" s="1" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>DR%</t>
         </is>
       </c>
-      <c r="AY7" s="1" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>pAST%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>#0 K. PUNTER</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L8" t="n">
         <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
@@ -1461,40 +1449,40 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="U8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="V8" t="n">
+        <v>9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>6</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y8" t="n">
         <v>7</v>
       </c>
-      <c r="W8" t="n">
-        <v>3</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>6</v>
-      </c>
       <c r="Z8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6</v>
+        <v>0.538</v>
       </c>
       <c r="AB8" t="n">
         <v>2</v>
@@ -1506,79 +1494,79 @@
         <v>0.167</v>
       </c>
       <c r="AE8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AF8" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.481</v>
+        <v>0.484</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="AK8" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AL8" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.455</v>
+        <v>0.531</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>184:51</t>
+          <t>240:56</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>94.59999999999999</v>
+        <v>118.04</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.493</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.533</v>
+        <v>0.589</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.93</v>
+        <v>1.008</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.127</v>
+        <v>0.144</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.171</v>
+        <v>0.149</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.333</v>
+        <v>1.118</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.247</v>
+        <v>0.235</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.028</v>
+        <v>0.021</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.062</v>
+        <v>0.066</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.068</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>#2 J. MARCOS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
         <v>22</v>
@@ -1724,23 +1712,23 @@
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.15</v>
+        <v>0.149</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.035</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>#3 M. CALE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
@@ -1752,25 +1740,25 @@
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
@@ -1785,16 +1773,16 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T10" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1845,91 +1833,91 @@
         <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>125:56</t>
+          <t>138:43</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>32.4</v>
+        <v>34.28</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.538</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.595</v>
+        <v>0.575</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.093</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.28</v>
+        <v>0.308</v>
       </c>
       <c r="AU10" t="n">
         <v>1.333</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.124</v>
+        <v>0.118</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.031</v>
+        <v>0.036</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.154</v>
+        <v>0.156</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>#6 J. VESELY</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -1938,25 +1926,25 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S11" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="T11" t="n">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
@@ -1965,31 +1953,31 @@
         <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="AB11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="AE11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -2001,76 +1989,76 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>149:01</t>
+          <t>194:26</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>53.8</v>
+        <v>73.2</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.619</v>
+        <v>0.598</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.679</v>
+        <v>0.665</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.283</v>
+        <v>1.257</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.056</v>
+        <v>0.055</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.405</v>
+        <v>0.446</v>
       </c>
       <c r="AU11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.174</v>
+        <v>0.18</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.078</v>
+        <v>0.097</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.131</v>
+        <v>0.129</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>#8 D. BRIZUELA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -2079,73 +2067,73 @@
         <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N12" t="n">
         <v>2</v>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S12" t="n">
         <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V12" t="n">
         <v>10</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="n">
         <v>0.8</v>
       </c>
       <c r="AB12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF12" t="n">
         <v>8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>6</v>
       </c>
       <c r="AG12" t="n">
         <v>0.5</v>
@@ -2154,100 +2142,100 @@
         <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.333</v>
+        <v>0.297</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>139:27</t>
+          <t>169:09</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>65.28</v>
+        <v>83.28</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.6</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.622</v>
+        <v>0.582</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.149</v>
+        <v>1.081</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.077</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.164</v>
+        <v>0.125</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.2</v>
+        <v>2.833</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.226</v>
+        <v>0.236</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.082</v>
+        <v>0.074</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.067</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>#13 T. SATORANSKY</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
+        <v>15</v>
+      </c>
+      <c r="H13" t="n">
         <v>10</v>
       </c>
-      <c r="H13" t="n">
-        <v>7</v>
-      </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J13" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K13" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L13" t="n">
         <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
@@ -2256,19 +2244,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T13" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="U13" t="n">
         <v>2</v>
@@ -2283,22 +2271,22 @@
         <v>4</v>
       </c>
       <c r="Y13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AB13" t="n">
         <v>1</v>
       </c>
       <c r="AC13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2310,97 +2298,97 @@
         <v>0.667</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AK13" t="n">
         <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.222</v>
+        <v>0.167</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>126:38</t>
+          <t>164:40</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>33.4</v>
+        <v>45.16</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.413</v>
+        <v>0.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.474</v>
+        <v>0.47</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.778</v>
+        <v>0.753</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.18</v>
+        <v>0.199</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.304</v>
+        <v>0.333</v>
       </c>
       <c r="AU13" t="n">
-        <v>3</v>
+        <v>2.667</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.127</v>
+        <v>0.131</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.031</v>
+        <v>0.023</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.145</v>
+        <v>0.131</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>#14 W. HERNANGÓMEZ</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" t="n">
+        <v>26</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>22</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
         <v>8</v>
       </c>
-      <c r="C14" t="n">
-        <v>23</v>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="n">
-        <v>21</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" t="n">
-        <v>6</v>
-      </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L14" t="n">
         <v>7</v>
@@ -2409,25 +2397,25 @@
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T14" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
@@ -2442,13 +2430,13 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.526</v>
+        <v>0.55</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2488,51 +2476,51 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>63:22</t>
+          <t>72:04</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>24.64</v>
+        <v>27.52</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.476</v>
+        <v>0.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.486</v>
+        <v>0.509</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.945</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.041</v>
+        <v>0.073</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.143</v>
+        <v>0.182</v>
       </c>
       <c r="AU14" t="n">
         <v>1</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.187</v>
+        <v>0.183</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.142</v>
+        <v>0.122</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.217</v>
+        <v>0.205</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>#17 J. NÚÑEZ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
         <v>2</v>
@@ -2547,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2556,10 +2544,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2583,10 +2571,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2640,27 +2628,27 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>04:03</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AR15" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AS15" t="n">
         <v>0</v>
@@ -2672,26 +2660,26 @@
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.238</v>
+        <v>0.185</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.283</v>
+        <v>0.294</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>#19 Y. FALL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
         <v>49</v>
@@ -2831,56 +2819,56 @@
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.165</v>
+        <v>0.164</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.128</v>
+        <v>0.124</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.247</v>
+        <v>0.245</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>#20 N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>4</v>
@@ -2892,19 +2880,19 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="T17" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="U17" t="n">
         <v>7</v>
@@ -2922,19 +2910,19 @@
         <v>7</v>
       </c>
       <c r="Z17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.778</v>
+        <v>0.636</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2946,85 +2934,85 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AK17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL17" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.533</v>
+        <v>0.45</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>118:08</t>
+          <t>157:41</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>67.12</v>
+        <v>88.88</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.756</v>
+        <v>0.661</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.281</v>
+        <v>1.148</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.209</v>
+        <v>0.203</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.488</v>
+        <v>0.407</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.786</v>
+        <v>1.611</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.274</v>
+        <v>0.27</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.077</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.103</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>#21 W. CLYBURN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E18" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H18" t="n">
         <v>16</v>
@@ -3033,40 +3021,40 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M18" t="n">
         <v>8</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="R18" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="S18" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="T18" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="U18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V18" t="n">
         <v>10</v>
@@ -3078,13 +3066,13 @@
         <v>2</v>
       </c>
       <c r="Y18" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.762</v>
+        <v>0.679</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -3105,127 +3093,127 @@
         <v>0.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.75</v>
+        <v>0.571</v>
       </c>
       <c r="AK18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL18" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.455</v>
+        <v>0.41</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>204:21</t>
+          <t>267:03</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>90.36</v>
+        <v>111.36</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.638</v>
+        <v>0.588</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.672</v>
+        <v>0.621</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.151</v>
+        <v>1.042</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.144</v>
+        <v>0.162</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.232</v>
+        <v>0.188</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.538</v>
+        <v>0.444</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.213</v>
+        <v>0.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.05</v>
+        <v>0.047</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.134</v>
+        <v>0.141</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>#23 T. SHENGELIA</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E19" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H19" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I19" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="J19" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K19" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R19" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S19" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="T19" t="n">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="U19" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V19" t="n">
         <v>17</v>
@@ -3237,112 +3225,112 @@
         <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="Z19" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.59</v>
+        <v>0.647</v>
       </c>
       <c r="AB19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK19" t="n">
         <v>3</v>
       </c>
-      <c r="AC19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
+      <c r="AL19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>239:29</t>
+        </is>
+      </c>
+      <c r="AO19" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="AU19" t="n">
         <v>2</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>175:51</t>
-        </is>
-      </c>
-      <c r="AO19" t="n">
-        <v>87.64</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.016</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.8</v>
       </c>
       <c r="AV19" t="n">
         <v>0.24</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.103</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.156</v>
+        <v>0.152</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.076</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>#44 J. PARRA</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H20" t="n">
         <v>5</v>
@@ -3354,13 +3342,13 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L20" t="n">
+        <v>11</v>
+      </c>
+      <c r="M20" t="n">
         <v>8</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6</v>
       </c>
       <c r="N20" t="n">
         <v>2</v>
@@ -3369,19 +3357,19 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
       </c>
       <c r="T20" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="U20" t="n">
         <v>5</v>
@@ -3390,10 +3378,10 @@
         <v>11</v>
       </c>
       <c r="W20" t="n">
+        <v>5</v>
+      </c>
+      <c r="X20" t="n">
         <v>2</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1</v>
       </c>
       <c r="Y20" t="n">
         <v>15</v>
@@ -3405,88 +3393,88 @@
         <v>0.789</v>
       </c>
       <c r="AB20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
         <v>6</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AI20" t="n">
         <v>9</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AJ20" t="n">
         <v>0.667</v>
       </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ20" t="n">
+      <c r="AK20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>216:50</t>
+        </is>
+      </c>
+      <c r="AO20" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.414</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AU20" t="n">
         <v>0.833</v>
       </c>
-      <c r="AK20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>176:33</t>
-        </is>
-      </c>
-      <c r="AO20" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.563</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1.667</v>
-      </c>
       <c r="AV20" t="n">
-        <v>0.14</v>
+        <v>0.148</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.058</v>
+        <v>0.064</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.091</v>
+        <v>0.1</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Equip</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -3513,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L21" t="n">
         <v>7</v>
@@ -3528,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3639,325 +3627,325 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C22" t="n">
-        <v>748</v>
+        <v>912</v>
       </c>
       <c r="D22" t="n">
-        <v>183</v>
+        <v>221</v>
       </c>
       <c r="E22" t="n">
-        <v>327</v>
+        <v>392</v>
       </c>
       <c r="F22" t="n">
+        <v>105</v>
+      </c>
+      <c r="G22" t="n">
+        <v>248</v>
+      </c>
+      <c r="H22" t="n">
+        <v>155</v>
+      </c>
+      <c r="I22" t="n">
+        <v>202</v>
+      </c>
+      <c r="J22" t="n">
+        <v>152</v>
+      </c>
+      <c r="K22" t="n">
+        <v>256</v>
+      </c>
+      <c r="L22" t="n">
+        <v>91</v>
+      </c>
+      <c r="M22" t="n">
+        <v>57</v>
+      </c>
+      <c r="N22" t="n">
+        <v>46</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>105</v>
+      </c>
+      <c r="R22" t="n">
+        <v>200</v>
+      </c>
+      <c r="S22" t="n">
+        <v>206</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1042</v>
+      </c>
+      <c r="U22" t="n">
+        <v>86</v>
+      </c>
+      <c r="V22" t="n">
+        <v>91</v>
+      </c>
+      <c r="W22" t="n">
+        <v>40</v>
+      </c>
+      <c r="X22" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>129</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>192</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>51</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>112</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>41</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>88</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AK22" t="n">
         <v>84</v>
       </c>
-      <c r="G22" t="n">
-        <v>186</v>
-      </c>
-      <c r="H22" t="n">
-        <v>130</v>
-      </c>
-      <c r="I22" t="n">
-        <v>165</v>
-      </c>
-      <c r="J22" t="n">
-        <v>126</v>
-      </c>
-      <c r="K22" t="n">
-        <v>211</v>
-      </c>
-      <c r="L22" t="n">
-        <v>75</v>
-      </c>
-      <c r="M22" t="n">
-        <v>45</v>
-      </c>
-      <c r="N22" t="n">
-        <v>41</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>89</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>79</v>
-      </c>
-      <c r="R22" t="n">
-        <v>164</v>
-      </c>
-      <c r="S22" t="n">
-        <v>166</v>
-      </c>
-      <c r="T22" t="n">
-        <v>878</v>
-      </c>
-      <c r="U22" t="n">
-        <v>71</v>
-      </c>
-      <c r="V22" t="n">
-        <v>82</v>
-      </c>
-      <c r="W22" t="n">
-        <v>32</v>
-      </c>
-      <c r="X22" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>106</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>156</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>97</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>74</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0.473</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>69</v>
-      </c>
       <c r="AL22" t="n">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.431</v>
+        <v>0.404</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>1625:00</t>
+          <t>2025:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>674.6</v>
+        <v>845.88</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.602</v>
+        <v>0.591</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.639</v>
+        <v>0.626</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.109</v>
+        <v>1.078</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.132</v>
+        <v>0.138</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.253</v>
+        <v>0.242</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.416</v>
+        <v>1.299</v>
       </c>
       <c r="AV22" t="n">
         <v>0.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.06</v>
+        <v>0.056</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.149</v>
+        <v>0.144</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Rival</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C23" t="n">
-        <v>680</v>
+        <v>876</v>
       </c>
       <c r="D23" t="n">
-        <v>175</v>
+        <v>223</v>
       </c>
       <c r="E23" t="n">
-        <v>320</v>
+        <v>406</v>
       </c>
       <c r="F23" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="G23" t="n">
-        <v>209</v>
+        <v>266</v>
       </c>
       <c r="H23" t="n">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="I23" t="n">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="J23" t="n">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="K23" t="n">
-        <v>177</v>
+        <v>232</v>
       </c>
       <c r="L23" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="M23" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="N23" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="Q23" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="R23" t="n">
-        <v>172</v>
+        <v>212</v>
       </c>
       <c r="S23" t="n">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="T23" t="n">
-        <v>733</v>
+        <v>963</v>
       </c>
       <c r="U23" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="V23" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="W23" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="X23" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Y23" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="Z23" t="n">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="AB23" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="AC23" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.512</v>
+        <v>0.519</v>
       </c>
       <c r="AE23" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AF23" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.348</v>
+        <v>0.345</v>
       </c>
       <c r="AH23" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AI23" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.419</v>
+        <v>0.433</v>
       </c>
       <c r="AK23" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="AL23" t="n">
-        <v>166</v>
+        <v>206</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.307</v>
+        <v>0.32</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>1625:00</t>
+          <t>2025:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>677.3200000000001</v>
+        <v>856.6</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.526</v>
+        <v>0.537</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.004</v>
+        <v>1.023</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.12</v>
+        <v>0.118</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.233</v>
+        <v>0.229</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.494</v>
+        <v>1.535</v>
       </c>
       <c r="AV23" t="n">
         <v>0.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.051</v>
+        <v>0.056</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.14</v>
+        <v>0.144</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>--- PER GAME STATS ---</t>
         </is>
@@ -4014,187 +4002,187 @@
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>#0 K. PUNTER (Per Game)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>11.9</v>
       </c>
       <c r="D25" t="n">
-        <v>2.625</v>
+        <v>2.4</v>
       </c>
       <c r="E25" t="n">
-        <v>6.125</v>
+        <v>5.6</v>
       </c>
       <c r="F25" t="n">
-        <v>1.375</v>
+        <v>1.9</v>
       </c>
       <c r="G25" t="n">
-        <v>3.375</v>
+        <v>3.8</v>
       </c>
       <c r="H25" t="n">
-        <v>1.625</v>
+        <v>1.4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.875</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K25" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M25" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="R25" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S25" t="n">
-        <v>1.875</v>
+        <v>1.9</v>
       </c>
       <c r="T25" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="V25" t="n">
-        <v>0.875</v>
+        <v>0.9</v>
       </c>
       <c r="W25" t="n">
-        <v>0.375</v>
+        <v>0.6</v>
       </c>
       <c r="X25" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.6</v>
+        <v>0.538</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AD25" t="n">
         <v>0.167</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.625</v>
+        <v>1.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>3.375</v>
+        <v>3.1</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.481</v>
+        <v>0.484</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.455</v>
+        <v>0.531</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>23:06</t>
+          <t>24:05</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>11.825</v>
+        <v>11.804</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.493</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.533</v>
+        <v>0.589</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.93</v>
+        <v>1.008</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.127</v>
+        <v>0.144</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.171</v>
+        <v>0.149</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.333</v>
+        <v>1.118</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.247</v>
+        <v>0.235</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.028</v>
+        <v>0.021</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.062</v>
+        <v>0.066</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.068</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>#2 J. MARCOS (Per Game)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26" t="n">
-        <v>2.75</v>
+        <v>2.444</v>
       </c>
       <c r="D26" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="E26" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="F26" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="G26" t="n">
-        <v>1.5</v>
+        <v>1.333</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -4203,40 +4191,40 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1.625</v>
+        <v>1.444</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="N26" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="R26" t="n">
-        <v>1.875</v>
+        <v>1.667</v>
       </c>
       <c r="S26" t="n">
-        <v>0.375</v>
+        <v>0.333</v>
       </c>
       <c r="T26" t="n">
         <v>22</v>
       </c>
       <c r="U26" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4248,10 +4236,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="AA26" t="n">
         <v>0.5</v>
@@ -4260,7 +4248,7 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.125</v>
+        <v>0.111</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -4269,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.125</v>
+        <v>0.111</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -4284,21 +4272,21 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.5</v>
+        <v>1.333</v>
       </c>
       <c r="AM26" t="n">
         <v>0.5</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>3</v>
+        <v>2.667</v>
       </c>
       <c r="AP26" t="n">
         <v>0.611</v>
@@ -4325,101 +4313,101 @@
         <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.15</v>
+        <v>0.149</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.035</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>#3 M. CALE (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C27" t="n">
-        <v>4.375</v>
+        <v>3.6</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E27" t="n">
-        <v>1.875</v>
+        <v>1.5</v>
       </c>
       <c r="F27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T27" t="n">
+        <v>43</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
         <v>0.5</v>
       </c>
-      <c r="G27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="X27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z27" t="n">
         <v>0.5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2.125</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="T27" t="n">
-        <v>40</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0.625</v>
       </c>
       <c r="AA27" t="n">
         <v>0.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.125</v>
+        <v>0.9</v>
       </c>
       <c r="AD27" t="n">
         <v>0.444</v>
@@ -4428,169 +4416,169 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AJ27" t="n">
         <v>0.333</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AL27" t="n">
         <v>0.5</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>4.05</v>
+        <v>3.428</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.538</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.595</v>
+        <v>0.575</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.093</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.28</v>
+        <v>0.308</v>
       </c>
       <c r="AU27" t="n">
         <v>1.333</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.124</v>
+        <v>0.118</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.031</v>
+        <v>0.036</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.154</v>
+        <v>0.156</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>#6 J. VESELY (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C28" t="n">
-        <v>8.625</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="H28" t="n">
-        <v>2.125</v>
+        <v>2.5</v>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>2.125</v>
+        <v>2.2</v>
       </c>
       <c r="L28" t="n">
-        <v>1.125</v>
+        <v>1.5</v>
       </c>
       <c r="M28" t="n">
         <v>0.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0.375</v>
+        <v>0.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="R28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S28" t="n">
         <v>2.5</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.375</v>
-      </c>
       <c r="T28" t="n">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="U28" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="V28" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="W28" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="X28" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.625</v>
+        <v>0.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.875</v>
+        <v>1.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.625</v>
+        <v>1.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF28" t="n">
         <v>2.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AH28" t="n">
         <v>0</v>
@@ -4602,388 +4590,388 @@
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AL28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AM28" t="n">
         <v>0.25</v>
       </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>6.725</v>
+        <v>7.32</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.619</v>
+        <v>0.598</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.679</v>
+        <v>0.665</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.283</v>
+        <v>1.257</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.056</v>
+        <v>0.055</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.405</v>
+        <v>0.446</v>
       </c>
       <c r="AU28" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.174</v>
+        <v>0.18</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.078</v>
+        <v>0.097</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.131</v>
+        <v>0.129</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>#8 D. BRIZUELA (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>9.375</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>1.875</v>
+        <v>2.1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>4.125</v>
+        <v>4.1</v>
       </c>
       <c r="H29" t="n">
-        <v>1.125</v>
+        <v>0.9</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="K29" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="M29" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="T29" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="U29" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="V29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="n">
         <v>0.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.375</v>
+        <v>1.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.727</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AG29" t="n">
         <v>0.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AL29" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.333</v>
+        <v>0.297</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>8.16</v>
+        <v>8.327999999999999</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.6</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.622</v>
+        <v>0.582</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.149</v>
+        <v>1.081</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.077</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.164</v>
+        <v>0.125</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.2</v>
+        <v>2.833</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.226</v>
+        <v>0.236</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.082</v>
+        <v>0.074</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.067</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>#13 T. SATORANSKY (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>3.714</v>
+        <v>3.778</v>
       </c>
       <c r="D30" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="E30" t="n">
-        <v>1.857</v>
+        <v>1.667</v>
       </c>
       <c r="F30" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="G30" t="n">
-        <v>1.429</v>
+        <v>1.667</v>
       </c>
       <c r="H30" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.556</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>1</v>
       </c>
-      <c r="I30" t="n">
-        <v>1.429</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.571</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2.286</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0.857</v>
-      </c>
       <c r="Q30" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>1.857</v>
+        <v>1.778</v>
       </c>
       <c r="S30" t="n">
-        <v>1.286</v>
+        <v>1.556</v>
       </c>
       <c r="T30" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="U30" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.571</v>
+        <v>0.444</v>
       </c>
       <c r="X30" t="n">
-        <v>0.571</v>
+        <v>0.444</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.143</v>
+        <v>0.111</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="AG30" t="n">
         <v>0.667</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.143</v>
+        <v>0.222</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.143</v>
+        <v>0.333</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.286</v>
+        <v>1.333</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.222</v>
+        <v>0.167</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>4.771</v>
+        <v>5.018</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.413</v>
+        <v>0.4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.474</v>
+        <v>0.47</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.778</v>
+        <v>0.753</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.18</v>
+        <v>0.199</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.304</v>
+        <v>0.333</v>
       </c>
       <c r="AU30" t="n">
-        <v>3</v>
+        <v>2.667</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.127</v>
+        <v>0.131</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.031</v>
+        <v>0.023</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.145</v>
+        <v>0.131</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.08</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>#14 W. HERNANGÓMEZ (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>2.875</v>
+        <v>2.6</v>
       </c>
       <c r="D31" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="E31" t="n">
-        <v>2.625</v>
+        <v>2.2</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4992,22 +4980,22 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="I31" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="K31" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="L31" t="n">
-        <v>0.875</v>
+        <v>0.7</v>
       </c>
       <c r="M31" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="N31" t="n">
         <v>0.5</v>
@@ -5016,46 +5004,46 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="R31" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="S31" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="T31" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="U31" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V31" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W31" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="X31" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.375</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.526</v>
+        <v>0.55</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -5089,66 +5077,66 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>3.08</v>
+        <v>2.752</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.476</v>
+        <v>0.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.486</v>
+        <v>0.509</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.945</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.041</v>
+        <v>0.073</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.143</v>
+        <v>0.182</v>
       </c>
       <c r="AU31" t="n">
         <v>1</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.187</v>
+        <v>0.183</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.142</v>
+        <v>0.122</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.217</v>
+        <v>0.205</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>#17 J. NÚÑEZ (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
         <v>1</v>
       </c>
-      <c r="C32" t="n">
-        <v>2</v>
-      </c>
       <c r="D32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E32" t="n">
         <v>1</v>
       </c>
-      <c r="E32" t="n">
-        <v>2</v>
-      </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -5169,7 +5157,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -5184,10 +5172,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="T32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -5202,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AA32" t="n">
         <v>1</v>
@@ -5214,7 +5202,7 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -5241,27 +5229,27 @@
         <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AM32" t="n">
         <v>0</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>04:03</t>
+          <t>03:52</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AR32" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AS32" t="n">
         <v>0</v>
@@ -5273,35 +5261,35 @@
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.238</v>
+        <v>0.185</v>
       </c>
       <c r="AW32" t="n">
         <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.283</v>
+        <v>0.294</v>
       </c>
       <c r="AY32" t="n">
         <v>0.031</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>#19 Y. FALL (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C33" t="n">
-        <v>6.125</v>
+        <v>4.9</v>
       </c>
       <c r="D33" t="n">
-        <v>2.625</v>
+        <v>2.1</v>
       </c>
       <c r="E33" t="n">
-        <v>3.625</v>
+        <v>2.9</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -5310,49 +5298,49 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.875</v>
+        <v>0.7</v>
       </c>
       <c r="I33" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="L33" t="n">
-        <v>1.375</v>
+        <v>1.1</v>
       </c>
       <c r="M33" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N33" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.375</v>
+        <v>0.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.375</v>
+        <v>0.3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="T33" t="n">
         <v>70</v>
       </c>
       <c r="U33" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.375</v>
+        <v>1.1</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -5361,28 +5349,28 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.375</v>
+        <v>1.1</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AA33" t="n">
         <v>0.917</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.125</v>
+        <v>0.9</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AD33" t="n">
         <v>0.643</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.375</v>
+        <v>0.3</v>
       </c>
       <c r="AG33" t="n">
         <v>0.333</v>
@@ -5407,11 +5395,11 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>4.77</v>
+        <v>3.816</v>
       </c>
       <c r="AP33" t="n">
         <v>0.724</v>
@@ -5432,218 +5420,218 @@
         <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.165</v>
+        <v>0.164</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.128</v>
+        <v>0.124</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.247</v>
+        <v>0.245</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>#20 N. LAPROVITTOLA (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C34" t="n">
-        <v>10.75</v>
+        <v>10.2</v>
       </c>
       <c r="D34" t="n">
-        <v>0.875</v>
+        <v>0.9</v>
       </c>
       <c r="E34" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F34" t="n">
-        <v>2.125</v>
+        <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>3.875</v>
+        <v>4.3</v>
       </c>
       <c r="H34" t="n">
-        <v>2.625</v>
+        <v>2.4</v>
       </c>
       <c r="I34" t="n">
-        <v>2.875</v>
+        <v>2.7</v>
       </c>
       <c r="J34" t="n">
-        <v>3.125</v>
+        <v>2.9</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="N34" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R34" t="n">
         <v>2</v>
       </c>
       <c r="S34" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="T34" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="U34" t="n">
-        <v>0.875</v>
+        <v>0.7</v>
       </c>
       <c r="V34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD34" t="n">
         <v>0.5</v>
       </c>
-      <c r="W34" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
       <c r="AE34" t="n">
         <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.125</v>
+        <v>0.3</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AK34" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AL34" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.533</v>
+        <v>0.45</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>8.390000000000001</v>
+        <v>8.888</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.756</v>
+        <v>0.661</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.281</v>
+        <v>1.148</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.209</v>
+        <v>0.203</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.488</v>
+        <v>0.407</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.786</v>
+        <v>1.611</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.274</v>
+        <v>0.27</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.077</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.103</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>#21 W. CLYBURN (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C35" t="n">
-        <v>13</v>
+        <v>11.6</v>
       </c>
       <c r="D35" t="n">
-        <v>2.125</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F35" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>4.625</v>
+        <v>4.6</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="I35" t="n">
-        <v>2.375</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
-        <v>0.875</v>
+        <v>0.8</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N35" t="n">
         <v>0.5</v>
@@ -5652,442 +5640,442 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.625</v>
+        <v>1.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.625</v>
+        <v>1.8</v>
       </c>
       <c r="R35" t="n">
-        <v>2.125</v>
+        <v>2.2</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T35" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="U35" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="X35" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Y35" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.625</v>
+        <v>2.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.762</v>
+        <v>0.679</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="AG35" t="n">
         <v>0.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.75</v>
+        <v>0.571</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.875</v>
+        <v>1.6</v>
       </c>
       <c r="AL35" t="n">
-        <v>4.125</v>
+        <v>3.9</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.455</v>
+        <v>0.41</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>25:32</t>
+          <t>26:42</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>11.295</v>
+        <v>11.136</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.638</v>
+        <v>0.588</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.672</v>
+        <v>0.621</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.151</v>
+        <v>1.042</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.144</v>
+        <v>0.162</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.232</v>
+        <v>0.188</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.538</v>
+        <v>0.444</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.213</v>
+        <v>0.2</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.05</v>
+        <v>0.047</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.134</v>
+        <v>0.141</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>#23 T. SHENGELIA (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C36" t="n">
-        <v>11.125</v>
+        <v>12.9</v>
       </c>
       <c r="D36" t="n">
-        <v>3.625</v>
+        <v>4.2</v>
       </c>
       <c r="E36" t="n">
-        <v>6.875</v>
+        <v>7.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="G36" t="n">
-        <v>1.125</v>
+        <v>1.5</v>
       </c>
       <c r="H36" t="n">
-        <v>3.125</v>
+        <v>3.3</v>
       </c>
       <c r="I36" t="n">
-        <v>3.875</v>
+        <v>4.5</v>
       </c>
       <c r="J36" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="K36" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="L36" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="M36" t="n">
-        <v>0.375</v>
+        <v>0.7</v>
       </c>
       <c r="N36" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="S36" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="T36" t="n">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="U36" t="n">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="V36" t="n">
-        <v>2.125</v>
+        <v>1.7</v>
       </c>
       <c r="W36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="AB36" t="n">
         <v>0.5</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.875</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>4.875</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0.375</v>
       </c>
       <c r="AC36" t="n">
         <v>1.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="AF36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>0.5</v>
       </c>
-      <c r="AG36" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
       <c r="AK36" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.125</v>
+        <v>1.3</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.222</v>
+        <v>0.231</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>21:58</t>
+          <t>23:56</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>10.955</v>
+        <v>11.98</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.5</v>
+        <v>0.552</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.573</v>
+        <v>0.604</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.016</v>
+        <v>1.077</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.114</v>
+        <v>0.109</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.391</v>
+        <v>0.379</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AV36" t="n">
         <v>0.24</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.103</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.156</v>
+        <v>0.152</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.076</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>#44 J. PARRA (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="D37" t="n">
-        <v>2.625</v>
+        <v>2.4</v>
       </c>
       <c r="E37" t="n">
-        <v>3.875</v>
+        <v>3.7</v>
       </c>
       <c r="F37" t="n">
-        <v>1.375</v>
+        <v>1.4</v>
       </c>
       <c r="G37" t="n">
-        <v>1.875</v>
+        <v>2.2</v>
       </c>
       <c r="H37" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="I37" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="K37" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M37" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="N37" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.375</v>
+        <v>0.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.375</v>
+        <v>0.6</v>
       </c>
       <c r="R37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>101</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y37" t="n">
         <v>1.5</v>
       </c>
-      <c r="S37" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="T37" t="n">
-        <v>91</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.875</v>
-      </c>
       <c r="Z37" t="n">
-        <v>2.375</v>
+        <v>1.9</v>
       </c>
       <c r="AA37" t="n">
         <v>0.789</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.125</v>
+        <v>1.4</v>
       </c>
       <c r="AD37" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AJ37" t="n">
         <v>0.667</v>
       </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AJ37" t="n">
+      <c r="AK37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="AO37" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.414</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AU37" t="n">
         <v>0.833</v>
       </c>
-      <c r="AK37" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>22:04</t>
-        </is>
-      </c>
-      <c r="AO37" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.563</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>1.667</v>
-      </c>
       <c r="AV37" t="n">
-        <v>0.14</v>
+        <v>0.148</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.058</v>
+        <v>0.064</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.091</v>
+        <v>0.1</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -6114,10 +6102,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2.625</v>
+        <v>2.5</v>
       </c>
       <c r="L38" t="n">
-        <v>0.875</v>
+        <v>0.7</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -6129,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6240,318 +6228,318 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C39" t="n">
-        <v>93.5</v>
+        <v>91.2</v>
       </c>
       <c r="D39" t="n">
-        <v>22.875</v>
+        <v>22.1</v>
       </c>
       <c r="E39" t="n">
-        <v>40.875</v>
+        <v>39.2</v>
       </c>
       <c r="F39" t="n">
         <v>10.5</v>
       </c>
       <c r="G39" t="n">
-        <v>23.25</v>
+        <v>24.8</v>
       </c>
       <c r="H39" t="n">
-        <v>16.25</v>
+        <v>15.5</v>
       </c>
       <c r="I39" t="n">
-        <v>20.625</v>
+        <v>20.2</v>
       </c>
       <c r="J39" t="n">
-        <v>15.75</v>
+        <v>15.2</v>
       </c>
       <c r="K39" t="n">
-        <v>26.375</v>
+        <v>25.6</v>
       </c>
       <c r="L39" t="n">
-        <v>9.375</v>
+        <v>9.1</v>
       </c>
       <c r="M39" t="n">
-        <v>5.625</v>
+        <v>5.7</v>
       </c>
       <c r="N39" t="n">
-        <v>5.125</v>
+        <v>4.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>11.125</v>
+        <v>11.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>9.875</v>
+        <v>10.5</v>
       </c>
       <c r="R39" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="S39" t="n">
-        <v>20.75</v>
+        <v>20.6</v>
       </c>
       <c r="T39" t="n">
-        <v>878</v>
+        <v>1042</v>
       </c>
       <c r="U39" t="n">
-        <v>8.875</v>
+        <v>8.6</v>
       </c>
       <c r="V39" t="n">
-        <v>10.25</v>
+        <v>9.1</v>
       </c>
       <c r="W39" t="n">
         <v>4</v>
       </c>
       <c r="X39" t="n">
-        <v>2.375</v>
+        <v>2.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>13.25</v>
+        <v>12.9</v>
       </c>
       <c r="Z39" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.679</v>
+        <v>0.672</v>
       </c>
       <c r="AB39" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AC39" t="n">
-        <v>12.125</v>
+        <v>11.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.433</v>
+        <v>0.455</v>
       </c>
       <c r="AE39" t="n">
-        <v>4.375</v>
+        <v>4.1</v>
       </c>
       <c r="AF39" t="n">
-        <v>9.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.473</v>
+        <v>0.466</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.875</v>
+        <v>2.1</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.577</v>
+        <v>0.525</v>
       </c>
       <c r="AK39" t="n">
-        <v>8.625</v>
+        <v>8.4</v>
       </c>
       <c r="AL39" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.431</v>
+        <v>0.404</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>203:07</t>
+          <t>202:30</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>84.325</v>
+        <v>84.58799999999999</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.602</v>
+        <v>0.591</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.639</v>
+        <v>0.626</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.109</v>
+        <v>1.078</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.132</v>
+        <v>0.138</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.253</v>
+        <v>0.242</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.416</v>
+        <v>1.299</v>
       </c>
       <c r="AV39" t="n">
         <v>0.2</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.06</v>
+        <v>0.056</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.149</v>
+        <v>0.144</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C40" t="n">
-        <v>85</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>21.875</v>
+        <v>22.3</v>
       </c>
       <c r="E40" t="n">
-        <v>40</v>
+        <v>40.6</v>
       </c>
       <c r="F40" t="n">
-        <v>8.625</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>26.125</v>
+        <v>26.6</v>
       </c>
       <c r="H40" t="n">
-        <v>15.375</v>
+        <v>15.4</v>
       </c>
       <c r="I40" t="n">
-        <v>19.125</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>15.125</v>
+        <v>15.5</v>
       </c>
       <c r="K40" t="n">
-        <v>22.125</v>
+        <v>23.2</v>
       </c>
       <c r="L40" t="n">
-        <v>9.125</v>
+        <v>10</v>
       </c>
       <c r="M40" t="n">
-        <v>5.75</v>
+        <v>6.2</v>
       </c>
       <c r="N40" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>10.125</v>
+        <v>10.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="R40" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="S40" t="n">
-        <v>20.5</v>
+        <v>19.9</v>
       </c>
       <c r="T40" t="n">
-        <v>733</v>
+        <v>963</v>
       </c>
       <c r="U40" t="n">
-        <v>10.75</v>
+        <v>10.6</v>
       </c>
       <c r="V40" t="n">
-        <v>9.125</v>
+        <v>9.5</v>
       </c>
       <c r="W40" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="X40" t="n">
-        <v>3.375</v>
+        <v>3.4</v>
       </c>
       <c r="Y40" t="n">
-        <v>12.75</v>
+        <v>13.1</v>
       </c>
       <c r="Z40" t="n">
-        <v>18.5</v>
+        <v>19.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="AB40" t="n">
-        <v>5.125</v>
+        <v>5.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.512</v>
+        <v>0.519</v>
       </c>
       <c r="AE40" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.348</v>
+        <v>0.345</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AI40" t="n">
-        <v>5.375</v>
+        <v>6</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.419</v>
+        <v>0.433</v>
       </c>
       <c r="AK40" t="n">
-        <v>6.375</v>
+        <v>6.6</v>
       </c>
       <c r="AL40" t="n">
-        <v>20.75</v>
+        <v>20.6</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.307</v>
+        <v>0.32</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>203:07</t>
+          <t>202:30</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>84.66500000000001</v>
+        <v>85.66</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.526</v>
+        <v>0.537</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.004</v>
+        <v>1.023</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.12</v>
+        <v>0.118</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.233</v>
+        <v>0.229</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.494</v>
+        <v>1.535</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.201</v>
+        <v>0.203</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.058</v>
+        <v>0.062</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.125</v>
+        <v>0.13</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>
